--- a/artfynd/A 28113-2026 artfynd.xlsx
+++ b/artfynd/A 28113-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111802213</v>
+        <v>135254148</v>
       </c>
       <c r="B2" t="n">
-        <v>93213</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597737</v>
+        <v>597655</v>
       </c>
       <c r="R2" t="n">
-        <v>7071647</v>
+        <v>7071781</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,29 +764,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111802220</v>
+        <v>135253662</v>
       </c>
       <c r="B3" t="n">
-        <v>93197</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,40 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597715</v>
+        <v>597687</v>
       </c>
       <c r="R3" t="n">
-        <v>7071639</v>
+        <v>7071870</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -844,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -858,51 +861,50 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111802223</v>
+        <v>111802213</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -915,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597726</v>
+        <v>597737</v>
       </c>
       <c r="R4" t="n">
-        <v>7071643</v>
+        <v>7071647</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,10 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119352061</v>
+        <v>111802220</v>
       </c>
       <c r="B5" t="n">
-        <v>57953</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,42 +991,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Kullberg, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597652</v>
+        <v>597715</v>
       </c>
       <c r="R5" t="n">
-        <v>7071974</v>
+        <v>7071639</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1048,22 +1048,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1072,21 +1062,5190 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135254269</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>597670</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7071721</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Kim Hultgren</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Kim Hultgren</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135254935</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>597691</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7071625</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135254970</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>597704</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7071626</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135261210</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>597710</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7071633</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135252916</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>597734</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7071921</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135253853</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>597701</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7071820</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135253965</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>597732</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7071814</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135254335</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>597680</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7071698</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135254748</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>597695</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7071733</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135254797</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>597759</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7071713</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135254865</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>597681</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7071663</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135254896</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>597697</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7071651</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135254907</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>597691</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7071625</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135255150</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>597738</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7071628</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135255347</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>597781</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7071649</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135255503</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>597801</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7071656</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135255763</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>597871</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7071582</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135255809</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>597883</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7071561</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135256006</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>597907</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7071543</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135261206</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>597650</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7071766</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135261208</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>597686</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7071732</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135261209</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>597692</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7071677</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135261211</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>597775</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7071632</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135261212</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>597811</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7071636</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135253692</v>
+      </c>
+      <c r="B30" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>597718</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7071826</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>111802223</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kullberg, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>597726</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7071643</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135257132</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>597810</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7071731</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135257174</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>597800</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7071779</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135261207</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80492</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>597651</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7071773</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>119352061</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>597652</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7071974</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135252357</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>597647</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7072042</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135252502</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>597650</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7071996</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135252549</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>597648</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7071988</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135252575</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>597654</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7071984</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135252599</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>597652</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7071981</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135252771</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>597694</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7071960</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135253769</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>597732</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7071814</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135257192</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>597798</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7071782</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135252291</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>597625</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7072015</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135253119</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>597685</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7071950</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135261205</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>597679</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7071921</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135254080</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>597664</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7071792</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135254180</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>597732</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7071814</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135254875</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>597688</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7071656</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135255066</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>597711</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7071632</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135255116</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>597691</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7071625</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135255849</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>597894</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7071564</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135255990</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>597890</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7071513</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135256152</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>597907</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7071543</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AY54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28113-2026 artfynd.xlsx
+++ b/artfynd/A 28113-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -879,51 +879,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111802213</v>
+        <v>135261475</v>
       </c>
       <c r="B4" t="n">
-        <v>93213</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597737</v>
+        <v>597668</v>
       </c>
       <c r="R4" t="n">
-        <v>7071647</v>
+        <v>7071982</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -947,12 +944,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -961,51 +968,50 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111802220</v>
+        <v>111802213</v>
       </c>
       <c r="B5" t="n">
-        <v>93197</v>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1018,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597715</v>
+        <v>597737</v>
       </c>
       <c r="R5" t="n">
-        <v>7071639</v>
+        <v>7071647</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1081,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135254269</v>
+        <v>111802220</v>
       </c>
       <c r="B6" t="n">
-        <v>93271</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,19 +1116,22 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Kullberg, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597670</v>
+        <v>597715</v>
       </c>
       <c r="R6" t="n">
-        <v>7071721</v>
+        <v>7071639</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1146,22 +1155,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>17:02</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>17:02</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,25 +1169,26 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135254935</v>
+        <v>135254269</v>
       </c>
       <c r="B7" t="n">
         <v>93271</v>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597691</v>
+        <v>597670</v>
       </c>
       <c r="R7" t="n">
-        <v>7071625</v>
+        <v>7071721</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1281,11 +1281,21 @@
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135254970</v>
+        <v>135254935</v>
       </c>
       <c r="B8" t="n">
         <v>93271</v>
@@ -1320,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597704</v>
+        <v>597691</v>
       </c>
       <c r="R8" t="n">
-        <v>7071626</v>
+        <v>7071625</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,7 +1365,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1365,7 +1375,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1380,19 +1390,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135261210</v>
+        <v>135254970</v>
       </c>
       <c r="B9" t="n">
         <v>93271</v>
@@ -1420,31 +1430,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597710</v>
+        <v>597704</v>
       </c>
       <c r="R9" t="n">
-        <v>7071633</v>
+        <v>7071626</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1473,7 +1472,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1483,7 +1482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1492,67 +1491,77 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135252916</v>
+        <v>135261210</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>93271</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597734</v>
+        <v>597710</v>
       </c>
       <c r="R10" t="n">
-        <v>7071921</v>
+        <v>7071633</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1581,7 +1590,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1591,7 +1600,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1600,15 +1609,26 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135253853</v>
+        <v>135252916</v>
       </c>
       <c r="B11" t="n">
         <v>79373</v>
@@ -1643,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597701</v>
+        <v>597734</v>
       </c>
       <c r="R11" t="n">
-        <v>7071820</v>
+        <v>7071921</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,7 +1698,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1688,7 +1708,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1703,19 +1723,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135253965</v>
+        <v>135253853</v>
       </c>
       <c r="B12" t="n">
         <v>79373</v>
@@ -1750,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597732</v>
+        <v>597701</v>
       </c>
       <c r="R12" t="n">
-        <v>7071814</v>
+        <v>7071820</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,7 +1805,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1795,7 +1815,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1808,11 +1828,21 @@
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135254335</v>
+        <v>135253965</v>
       </c>
       <c r="B13" t="n">
         <v>79373</v>
@@ -1847,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597680</v>
+        <v>597732</v>
       </c>
       <c r="R13" t="n">
-        <v>7071698</v>
+        <v>7071814</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1882,7 +1912,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1892,7 +1922,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1905,11 +1935,21 @@
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135254748</v>
+        <v>135254335</v>
       </c>
       <c r="B14" t="n">
         <v>79373</v>
@@ -1944,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597695</v>
+        <v>597680</v>
       </c>
       <c r="R14" t="n">
-        <v>7071733</v>
+        <v>7071698</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1979,7 +2019,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1989,7 +2029,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2004,19 +2044,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135254797</v>
+        <v>135254748</v>
       </c>
       <c r="B15" t="n">
         <v>79373</v>
@@ -2051,13 +2091,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597759</v>
+        <v>597695</v>
       </c>
       <c r="R15" t="n">
-        <v>7071713</v>
+        <v>7071733</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2084,9 +2124,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2101,19 +2151,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135254865</v>
+        <v>135254797</v>
       </c>
       <c r="B16" t="n">
         <v>79373</v>
@@ -2148,13 +2198,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597681</v>
+        <v>597759</v>
       </c>
       <c r="R16" t="n">
-        <v>7071663</v>
+        <v>7071713</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2181,19 +2231,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>17:33</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>17:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2208,19 +2248,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135254896</v>
+        <v>135254865</v>
       </c>
       <c r="B17" t="n">
         <v>79373</v>
@@ -2255,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597697</v>
+        <v>597681</v>
       </c>
       <c r="R17" t="n">
-        <v>7071651</v>
+        <v>7071663</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,7 +2330,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2300,7 +2340,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2327,7 +2367,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135254907</v>
+        <v>135254896</v>
       </c>
       <c r="B18" t="n">
         <v>79373</v>
@@ -2362,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597691</v>
+        <v>597697</v>
       </c>
       <c r="R18" t="n">
-        <v>7071625</v>
+        <v>7071651</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2397,7 +2437,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2407,7 +2447,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2420,11 +2460,21 @@
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135255150</v>
+        <v>135254907</v>
       </c>
       <c r="B19" t="n">
         <v>79373</v>
@@ -2459,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597738</v>
+        <v>597691</v>
       </c>
       <c r="R19" t="n">
-        <v>7071628</v>
+        <v>7071625</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2494,7 +2544,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2504,7 +2554,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2519,19 +2569,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135255347</v>
+        <v>135255150</v>
       </c>
       <c r="B20" t="n">
         <v>79373</v>
@@ -2566,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597781</v>
+        <v>597738</v>
       </c>
       <c r="R20" t="n">
-        <v>7071649</v>
+        <v>7071628</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2601,7 +2651,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2611,7 +2661,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2638,7 +2688,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135255503</v>
+        <v>135255347</v>
       </c>
       <c r="B21" t="n">
         <v>79373</v>
@@ -2673,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597801</v>
+        <v>597781</v>
       </c>
       <c r="R21" t="n">
-        <v>7071656</v>
+        <v>7071649</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2708,7 +2758,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2718,7 +2768,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2745,7 +2795,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135255763</v>
+        <v>135255503</v>
       </c>
       <c r="B22" t="n">
         <v>79373</v>
@@ -2780,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597871</v>
+        <v>597801</v>
       </c>
       <c r="R22" t="n">
-        <v>7071582</v>
+        <v>7071656</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2815,7 +2865,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2825,7 +2875,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2852,7 +2902,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135255809</v>
+        <v>135255763</v>
       </c>
       <c r="B23" t="n">
         <v>79373</v>
@@ -2887,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597883</v>
+        <v>597871</v>
       </c>
       <c r="R23" t="n">
-        <v>7071561</v>
+        <v>7071582</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2922,7 +2972,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2932,7 +2982,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2959,7 +3009,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135256006</v>
+        <v>135255809</v>
       </c>
       <c r="B24" t="n">
         <v>79373</v>
@@ -2994,10 +3044,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597907</v>
+        <v>597883</v>
       </c>
       <c r="R24" t="n">
-        <v>7071543</v>
+        <v>7071561</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3029,7 +3079,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3039,7 +3089,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3052,11 +3102,21 @@
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135261206</v>
+        <v>135256006</v>
       </c>
       <c r="B25" t="n">
         <v>79373</v>
@@ -3085,22 +3145,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597650</v>
+        <v>597907</v>
       </c>
       <c r="R25" t="n">
-        <v>7071766</v>
+        <v>7071543</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3129,7 +3186,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3139,7 +3196,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3148,41 +3205,25 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135261208</v>
+        <v>135261206</v>
       </c>
       <c r="B26" t="n">
         <v>79373</v>
@@ -3211,16 +3252,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597686</v>
+        <v>597650</v>
       </c>
       <c r="R26" t="n">
-        <v>7071732</v>
+        <v>7071766</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3252,7 +3296,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3262,7 +3306,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3271,8 +3315,24 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3289,7 +3349,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135261209</v>
+        <v>135261208</v>
       </c>
       <c r="B27" t="n">
         <v>79373</v>
@@ -3324,10 +3384,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597692</v>
+        <v>597686</v>
       </c>
       <c r="R27" t="n">
-        <v>7071677</v>
+        <v>7071732</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3359,7 +3419,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3369,7 +3429,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3396,7 +3456,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135261211</v>
+        <v>135261209</v>
       </c>
       <c r="B28" t="n">
         <v>79373</v>
@@ -3431,10 +3491,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>597775</v>
+        <v>597692</v>
       </c>
       <c r="R28" t="n">
-        <v>7071632</v>
+        <v>7071677</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3466,7 +3526,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3476,7 +3536,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3503,7 +3563,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135261212</v>
+        <v>135261211</v>
       </c>
       <c r="B29" t="n">
         <v>79373</v>
@@ -3538,10 +3598,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>597811</v>
+        <v>597775</v>
       </c>
       <c r="R29" t="n">
-        <v>7071636</v>
+        <v>7071632</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3573,7 +3633,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3583,7 +3643,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3610,48 +3670,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135253692</v>
+        <v>135261212</v>
       </c>
       <c r="B30" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>597718</v>
+        <v>597811</v>
       </c>
       <c r="R30" t="n">
-        <v>7071826</v>
+        <v>7071636</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3678,9 +3738,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3695,44 +3765,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111802223</v>
+        <v>135261476</v>
       </c>
       <c r="B31" t="n">
-        <v>79084</v>
+        <v>79373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3741,17 +3811,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>597726</v>
+        <v>597705</v>
       </c>
       <c r="R31" t="n">
-        <v>7071643</v>
+        <v>7071935</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3775,12 +3845,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3793,63 +3873,81 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135257132</v>
+        <v>135261480</v>
       </c>
       <c r="B32" t="n">
-        <v>79130</v>
+        <v>79373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>597810</v>
+        <v>597757</v>
       </c>
       <c r="R32" t="n">
-        <v>7071731</v>
+        <v>7071733</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3876,77 +3974,103 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135257174</v>
+        <v>135277134</v>
       </c>
       <c r="B33" t="n">
-        <v>79130</v>
+        <v>79373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>597800</v>
+        <v>597690</v>
       </c>
       <c r="R33" t="n">
-        <v>7071779</v>
+        <v>7071889</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3973,9 +4097,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3990,22 +4124,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135261207</v>
+        <v>135277128</v>
       </c>
       <c r="B34" t="n">
-        <v>80492</v>
+        <v>79397</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4013,37 +4147,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6461</v>
+        <v>6434</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>597651</v>
+        <v>597652</v>
       </c>
       <c r="R34" t="n">
-        <v>7071773</v>
+        <v>7072022</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4072,7 +4206,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4082,7 +4216,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4097,22 +4231,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119352061</v>
+        <v>135253692</v>
       </c>
       <c r="B35" t="n">
-        <v>57953</v>
+        <v>83358</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4120,42 +4254,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>597652</v>
+        <v>597718</v>
       </c>
       <c r="R35" t="n">
-        <v>7071974</v>
+        <v>7071826</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4179,22 +4308,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4209,22 +4328,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135252357</v>
+        <v>135277130</v>
       </c>
       <c r="B36" t="n">
-        <v>57975</v>
+        <v>83358</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4232,39 +4351,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>597647</v>
+        <v>597672</v>
       </c>
       <c r="R36" t="n">
-        <v>7072042</v>
+        <v>7072025</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4296,7 +4410,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4306,12 +4420,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4326,22 +4435,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135252502</v>
+        <v>135277135</v>
       </c>
       <c r="B37" t="n">
-        <v>57975</v>
+        <v>83358</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4349,39 +4458,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>597650</v>
+        <v>597696</v>
       </c>
       <c r="R37" t="n">
-        <v>7071996</v>
+        <v>7071877</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4413,7 +4517,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4423,12 +4527,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4443,22 +4542,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135252549</v>
+        <v>111802223</v>
       </c>
       <c r="B38" t="n">
-        <v>57975</v>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4466,42 +4565,40 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Kullberg, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>597648</v>
+        <v>597726</v>
       </c>
       <c r="R38" t="n">
-        <v>7071988</v>
+        <v>7071643</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4525,27 +4622,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4554,28 +4636,29 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135252575</v>
+        <v>135257132</v>
       </c>
       <c r="B39" t="n">
-        <v>57975</v>
+        <v>79130</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4583,42 +4666,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>597654</v>
+        <v>597810</v>
       </c>
       <c r="R39" t="n">
-        <v>7071984</v>
+        <v>7071731</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4645,24 +4723,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4677,22 +4740,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135252599</v>
+        <v>135257174</v>
       </c>
       <c r="B40" t="n">
-        <v>57975</v>
+        <v>79130</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4700,42 +4763,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>597652</v>
+        <v>597800</v>
       </c>
       <c r="R40" t="n">
-        <v>7071981</v>
+        <v>7071779</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4762,26 +4820,11 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4792,14 +4835,24 @@
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135252771</v>
+        <v>135261478</v>
       </c>
       <c r="B41" t="n">
-        <v>57975</v>
+        <v>79130</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4807,42 +4860,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>597694</v>
+        <v>597690</v>
       </c>
       <c r="R41" t="n">
-        <v>7071960</v>
+        <v>7071824</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4871,7 +4919,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4881,12 +4929,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4901,65 +4944,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135253769</v>
+        <v>135261207</v>
       </c>
       <c r="B42" t="n">
-        <v>57975</v>
+        <v>80492</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>597732</v>
+        <v>597651</v>
       </c>
       <c r="R42" t="n">
-        <v>7071814</v>
+        <v>7071773</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4988,7 +5026,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4998,12 +5036,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5016,14 +5049,24 @@
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135257192</v>
+        <v>119352061</v>
       </c>
       <c r="B43" t="n">
-        <v>58136</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5031,27 +5074,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5060,13 +5103,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>597798</v>
+        <v>597652</v>
       </c>
       <c r="R43" t="n">
-        <v>7071782</v>
+        <v>7071974</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5090,12 +5133,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5110,60 +5163,65 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135252291</v>
+        <v>135252357</v>
       </c>
       <c r="B44" t="n">
-        <v>99112</v>
+        <v>57975</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>597625</v>
+        <v>597647</v>
       </c>
       <c r="R44" t="n">
-        <v>7072015</v>
+        <v>7072042</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5190,9 +5248,24 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5207,60 +5280,65 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135253119</v>
+        <v>135252502</v>
       </c>
       <c r="B45" t="n">
-        <v>98060</v>
+        <v>57975</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>597685</v>
+        <v>597650</v>
       </c>
       <c r="R45" t="n">
-        <v>7071950</v>
+        <v>7071996</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5287,9 +5365,24 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5304,60 +5397,65 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135261205</v>
+        <v>135252549</v>
       </c>
       <c r="B46" t="n">
-        <v>98060</v>
+        <v>57975</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>597679</v>
+        <v>597648</v>
       </c>
       <c r="R46" t="n">
-        <v>7071921</v>
+        <v>7071988</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5386,7 +5484,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5396,7 +5494,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5411,22 +5514,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135254080</v>
+        <v>135252575</v>
       </c>
       <c r="B47" t="n">
-        <v>79131</v>
+        <v>57975</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5434,34 +5537,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>597664</v>
+        <v>597654</v>
       </c>
       <c r="R47" t="n">
-        <v>7071792</v>
+        <v>7071984</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5493,7 +5601,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5503,7 +5611,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5530,10 +5643,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135254180</v>
+        <v>135252599</v>
       </c>
       <c r="B48" t="n">
-        <v>79131</v>
+        <v>57975</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5541,34 +5654,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>597732</v>
+        <v>597652</v>
       </c>
       <c r="R48" t="n">
-        <v>7071814</v>
+        <v>7071981</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5600,7 +5718,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5610,7 +5728,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5623,14 +5746,24 @@
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135254875</v>
+        <v>135252771</v>
       </c>
       <c r="B49" t="n">
-        <v>79131</v>
+        <v>57975</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5638,34 +5771,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>597688</v>
+        <v>597694</v>
       </c>
       <c r="R49" t="n">
-        <v>7071656</v>
+        <v>7071960</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5697,7 +5835,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5707,7 +5845,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5734,10 +5877,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135255066</v>
+        <v>135253769</v>
       </c>
       <c r="B50" t="n">
-        <v>79131</v>
+        <v>57975</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5745,34 +5888,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>597711</v>
+        <v>597732</v>
       </c>
       <c r="R50" t="n">
-        <v>7071632</v>
+        <v>7071814</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5804,7 +5952,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5814,7 +5962,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5829,57 +5982,57 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135255116</v>
+        <v>135277138</v>
       </c>
       <c r="B51" t="n">
-        <v>79131</v>
+        <v>57162</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>597691</v>
+        <v>597826</v>
       </c>
       <c r="R51" t="n">
-        <v>7071625</v>
+        <v>7071709</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5911,7 +6064,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5921,7 +6074,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5934,14 +6087,24 @@
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135255849</v>
+        <v>135257192</v>
       </c>
       <c r="B52" t="n">
-        <v>79131</v>
+        <v>58136</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5949,37 +6112,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>597894</v>
+        <v>597798</v>
       </c>
       <c r="R52" t="n">
-        <v>7071564</v>
+        <v>7071782</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6006,19 +6174,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>18:19</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>18:19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6033,57 +6191,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135255990</v>
+        <v>135277129</v>
       </c>
       <c r="B53" t="n">
-        <v>79131</v>
+        <v>8449</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>106554</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>597890</v>
+        <v>597655</v>
       </c>
       <c r="R53" t="n">
-        <v>7071513</v>
+        <v>7072023</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6115,7 +6273,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6125,7 +6283,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6140,44 +6298,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135256152</v>
+        <v>135252291</v>
       </c>
       <c r="B54" t="n">
-        <v>79131</v>
+        <v>99112</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6187,65 +6345,1446 @@
         </is>
       </c>
       <c r="Q54" t="n">
+        <v>597625</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7072015</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135253119</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>597685</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7071950</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135261205</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>597679</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7071921</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135261477</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>597690</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7071861</v>
+      </c>
+      <c r="S57" t="n">
+        <v>3</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135254080</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>597664</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7071792</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135254180</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>597732</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7071814</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135254875</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>597688</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7071656</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135255066</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>597711</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7071632</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135255116</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>597691</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7071625</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135255849</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>597894</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7071564</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135255990</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>597890</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7071513</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135256152</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
         <v>597907</v>
       </c>
-      <c r="R54" t="n">
+      <c r="R65" t="n">
         <v>7071543</v>
       </c>
-      <c r="S54" t="n">
+      <c r="S65" t="n">
         <v>10</v>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>Västernorrland</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>Sollefteå</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="V65" t="inlineStr">
         <is>
           <t>Ångermanland</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>Junsele</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
         <is>
           <t>18:28</t>
         </is>
       </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
         <is>
           <t>18:28</t>
         </is>
       </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AY54" t="inlineStr"/>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135261479</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>597679</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7071753</v>
+      </c>
+      <c r="S66" t="n">
+        <v>3</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135277126</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>597628</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7072050</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28113-2026 artfynd.xlsx
+++ b/artfynd/A 28113-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135254148</v>
+        <v>135185577</v>
       </c>
       <c r="B2" t="n">
         <v>79039</v>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597655</v>
+        <v>597658</v>
       </c>
       <c r="R2" t="n">
-        <v>7071781</v>
+        <v>7071784</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:53</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:53</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135253662</v>
+        <v>135254148</v>
       </c>
       <c r="B3" t="n">
-        <v>91974</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597687</v>
+        <v>597655</v>
       </c>
       <c r="R3" t="n">
-        <v>7071870</v>
+        <v>7071781</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,9 +840,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,19 +867,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135261475</v>
+        <v>135252944</v>
       </c>
       <c r="B4" t="n">
         <v>91974</v>
@@ -910,17 +910,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597668</v>
+        <v>597690</v>
       </c>
       <c r="R4" t="n">
-        <v>7071982</v>
+        <v>7071932</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -947,19 +947,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,63 +964,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111802213</v>
+        <v>135253662</v>
       </c>
       <c r="B5" t="n">
-        <v>93213</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597737</v>
+        <v>597687</v>
       </c>
       <c r="R5" t="n">
-        <v>7071647</v>
+        <v>7071870</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1054,12 +1041,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,29 +1055,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111802220</v>
+        <v>135261475</v>
       </c>
       <c r="B6" t="n">
-        <v>93197</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,40 +1084,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597715</v>
+        <v>597668</v>
       </c>
       <c r="R6" t="n">
-        <v>7071639</v>
+        <v>7071982</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1155,12 +1138,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1169,67 +1162,69 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135254269</v>
+        <v>111802213</v>
       </c>
       <c r="B7" t="n">
-        <v>93271</v>
+        <v>93213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Kullberg, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597670</v>
+        <v>597737</v>
       </c>
       <c r="R7" t="n">
-        <v>7071721</v>
+        <v>7071647</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1253,22 +1248,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>17:02</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>17:02</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,28 +1262,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135254935</v>
+        <v>111802220</v>
       </c>
       <c r="B8" t="n">
-        <v>93271</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1324,19 +1310,22 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Kullberg, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597691</v>
+        <v>597715</v>
       </c>
       <c r="R8" t="n">
-        <v>7071625</v>
+        <v>7071639</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1360,22 +1349,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>17:40</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:40</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1384,25 +1363,26 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135254970</v>
+        <v>135254269</v>
       </c>
       <c r="B9" t="n">
         <v>93271</v>
@@ -1437,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597704</v>
+        <v>597670</v>
       </c>
       <c r="R9" t="n">
-        <v>7071626</v>
+        <v>7071721</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,7 +1452,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1482,7 +1462,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1509,7 +1489,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135261210</v>
+        <v>135254935</v>
       </c>
       <c r="B10" t="n">
         <v>93271</v>
@@ -1537,31 +1517,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597710</v>
+        <v>597691</v>
       </c>
       <c r="R10" t="n">
-        <v>7071633</v>
+        <v>7071625</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1590,7 +1559,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1600,7 +1569,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1609,51 +1578,50 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135252916</v>
+        <v>135254970</v>
       </c>
       <c r="B11" t="n">
-        <v>79373</v>
+        <v>93271</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1631,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597734</v>
+        <v>597704</v>
       </c>
       <c r="R11" t="n">
-        <v>7071921</v>
+        <v>7071626</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1666,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1708,7 +1676,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1723,60 +1691,71 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135253853</v>
+        <v>135261210</v>
       </c>
       <c r="B12" t="n">
-        <v>79373</v>
+        <v>93271</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597701</v>
+        <v>597710</v>
       </c>
       <c r="R12" t="n">
-        <v>7071820</v>
+        <v>7071633</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1805,7 +1784,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1815,7 +1794,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1824,50 +1803,51 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135253965</v>
+        <v>135253005</v>
       </c>
       <c r="B13" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,13 +1857,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597732</v>
+        <v>597700</v>
       </c>
       <c r="R13" t="n">
-        <v>7071814</v>
+        <v>7071941</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1910,19 +1890,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:44</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1937,44 +1907,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135254335</v>
+        <v>135253624</v>
       </c>
       <c r="B14" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,13 +1954,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597680</v>
+        <v>597702</v>
       </c>
       <c r="R14" t="n">
-        <v>7071698</v>
+        <v>7071879</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2017,19 +1987,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>17:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2044,19 +2004,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135254748</v>
+        <v>135252916</v>
       </c>
       <c r="B15" t="n">
         <v>79373</v>
@@ -2091,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597695</v>
+        <v>597734</v>
       </c>
       <c r="R15" t="n">
-        <v>7071733</v>
+        <v>7071921</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2086,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2136,7 +2096,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2151,19 +2111,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135254797</v>
+        <v>135253853</v>
       </c>
       <c r="B16" t="n">
         <v>79373</v>
@@ -2198,13 +2158,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597759</v>
+        <v>597701</v>
       </c>
       <c r="R16" t="n">
-        <v>7071713</v>
+        <v>7071820</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2231,9 +2191,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2248,19 +2218,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135254865</v>
+        <v>135253965</v>
       </c>
       <c r="B17" t="n">
         <v>79373</v>
@@ -2295,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597681</v>
+        <v>597732</v>
       </c>
       <c r="R17" t="n">
-        <v>7071663</v>
+        <v>7071814</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,7 +2300,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2340,7 +2310,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2355,19 +2325,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135254896</v>
+        <v>135254335</v>
       </c>
       <c r="B18" t="n">
         <v>79373</v>
@@ -2402,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597697</v>
+        <v>597680</v>
       </c>
       <c r="R18" t="n">
-        <v>7071651</v>
+        <v>7071698</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,7 +2407,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2447,7 +2417,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2462,19 +2432,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135254907</v>
+        <v>135254748</v>
       </c>
       <c r="B19" t="n">
         <v>79373</v>
@@ -2509,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597691</v>
+        <v>597695</v>
       </c>
       <c r="R19" t="n">
-        <v>7071625</v>
+        <v>7071733</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2544,7 +2514,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2554,7 +2524,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2569,19 +2539,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135255150</v>
+        <v>135254797</v>
       </c>
       <c r="B20" t="n">
         <v>79373</v>
@@ -2616,13 +2586,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597738</v>
+        <v>597759</v>
       </c>
       <c r="R20" t="n">
-        <v>7071628</v>
+        <v>7071713</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2649,19 +2619,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>17:49</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2676,19 +2636,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135255347</v>
+        <v>135254865</v>
       </c>
       <c r="B21" t="n">
         <v>79373</v>
@@ -2723,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597781</v>
+        <v>597681</v>
       </c>
       <c r="R21" t="n">
-        <v>7071649</v>
+        <v>7071663</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2758,7 +2718,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2768,7 +2728,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,7 +2755,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135255503</v>
+        <v>135254896</v>
       </c>
       <c r="B22" t="n">
         <v>79373</v>
@@ -2830,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597801</v>
+        <v>597697</v>
       </c>
       <c r="R22" t="n">
-        <v>7071656</v>
+        <v>7071651</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2865,7 +2825,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2875,7 +2835,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2902,7 +2862,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135255763</v>
+        <v>135254907</v>
       </c>
       <c r="B23" t="n">
         <v>79373</v>
@@ -2937,10 +2897,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597871</v>
+        <v>597691</v>
       </c>
       <c r="R23" t="n">
-        <v>7071582</v>
+        <v>7071625</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2972,7 +2932,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2982,7 +2942,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2997,19 +2957,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135255809</v>
+        <v>135255150</v>
       </c>
       <c r="B24" t="n">
         <v>79373</v>
@@ -3044,10 +3004,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597883</v>
+        <v>597738</v>
       </c>
       <c r="R24" t="n">
-        <v>7071561</v>
+        <v>7071628</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3079,7 +3039,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3089,7 +3049,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3116,7 +3076,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135256006</v>
+        <v>135255347</v>
       </c>
       <c r="B25" t="n">
         <v>79373</v>
@@ -3151,10 +3111,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597907</v>
+        <v>597781</v>
       </c>
       <c r="R25" t="n">
-        <v>7071543</v>
+        <v>7071649</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3186,7 +3146,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3196,7 +3156,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3211,19 +3171,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135261206</v>
+        <v>135255503</v>
       </c>
       <c r="B26" t="n">
         <v>79373</v>
@@ -3252,22 +3212,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597650</v>
+        <v>597801</v>
       </c>
       <c r="R26" t="n">
-        <v>7071766</v>
+        <v>7071656</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3296,7 +3253,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3306,7 +3263,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3315,41 +3272,25 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135261208</v>
+        <v>135255763</v>
       </c>
       <c r="B27" t="n">
         <v>79373</v>
@@ -3380,17 +3321,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597686</v>
+        <v>597871</v>
       </c>
       <c r="R27" t="n">
-        <v>7071732</v>
+        <v>7071582</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3419,7 +3360,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3429,7 +3370,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3444,19 +3385,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135261209</v>
+        <v>135255809</v>
       </c>
       <c r="B28" t="n">
         <v>79373</v>
@@ -3487,17 +3428,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>597692</v>
+        <v>597883</v>
       </c>
       <c r="R28" t="n">
-        <v>7071677</v>
+        <v>7071561</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3526,7 +3467,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3536,7 +3477,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3551,19 +3492,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135261211</v>
+        <v>135256006</v>
       </c>
       <c r="B29" t="n">
         <v>79373</v>
@@ -3594,17 +3535,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>597775</v>
+        <v>597907</v>
       </c>
       <c r="R29" t="n">
-        <v>7071632</v>
+        <v>7071543</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3633,7 +3574,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3643,7 +3584,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3658,19 +3599,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135261212</v>
+        <v>135261206</v>
       </c>
       <c r="B30" t="n">
         <v>79373</v>
@@ -3699,16 +3640,19 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>597811</v>
+        <v>597650</v>
       </c>
       <c r="R30" t="n">
-        <v>7071636</v>
+        <v>7071766</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3740,7 +3684,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3750,7 +3694,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3759,8 +3703,24 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3777,7 +3737,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135261476</v>
+        <v>135261208</v>
       </c>
       <c r="B31" t="n">
         <v>79373</v>
@@ -3806,22 +3766,19 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>597705</v>
+        <v>597686</v>
       </c>
       <c r="R31" t="n">
-        <v>7071935</v>
+        <v>7071732</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3850,7 +3807,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3860,7 +3817,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3869,41 +3826,25 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135261480</v>
+        <v>135261209</v>
       </c>
       <c r="B32" t="n">
         <v>79373</v>
@@ -3932,22 +3873,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>597757</v>
+        <v>597692</v>
       </c>
       <c r="R32" t="n">
-        <v>7071733</v>
+        <v>7071677</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3976,7 +3914,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3986,7 +3924,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3995,41 +3933,25 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135277134</v>
+        <v>135261211</v>
       </c>
       <c r="B33" t="n">
         <v>79373</v>
@@ -4060,17 +3982,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>597690</v>
+        <v>597775</v>
       </c>
       <c r="R33" t="n">
-        <v>7071889</v>
+        <v>7071632</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4099,7 +4021,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4109,7 +4031,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4124,60 +4046,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135277128</v>
+        <v>135261212</v>
       </c>
       <c r="B34" t="n">
-        <v>79397</v>
+        <v>79373</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>597652</v>
+        <v>597811</v>
       </c>
       <c r="R34" t="n">
-        <v>7072022</v>
+        <v>7071636</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4206,7 +4128,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4216,7 +4138,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4231,60 +4153,63 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135253692</v>
+        <v>135261476</v>
       </c>
       <c r="B35" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>597718</v>
+        <v>597705</v>
       </c>
       <c r="R35" t="n">
-        <v>7071826</v>
+        <v>7071935</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4311,77 +4236,106 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135277130</v>
+        <v>135261480</v>
       </c>
       <c r="B36" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>597672</v>
+        <v>597757</v>
       </c>
       <c r="R36" t="n">
-        <v>7072025</v>
+        <v>7071733</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4410,7 +4364,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4420,7 +4374,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4429,50 +4383,66 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135277135</v>
+        <v>135277134</v>
       </c>
       <c r="B37" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4482,10 +4452,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>597696</v>
+        <v>597690</v>
       </c>
       <c r="R37" t="n">
-        <v>7071877</v>
+        <v>7071889</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4517,7 +4487,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4527,7 +4497,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4554,51 +4524,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>111802223</v>
+        <v>135277128</v>
       </c>
       <c r="B38" t="n">
-        <v>79084</v>
+        <v>79397</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>597726</v>
+        <v>597652</v>
       </c>
       <c r="R38" t="n">
-        <v>7071643</v>
+        <v>7072022</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4622,12 +4589,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4636,29 +4613,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135257132</v>
+        <v>135185455</v>
       </c>
       <c r="B39" t="n">
-        <v>79130</v>
+        <v>78776</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4666,21 +4642,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4690,10 +4666,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>597810</v>
+        <v>597723</v>
       </c>
       <c r="R39" t="n">
-        <v>7071731</v>
+        <v>7071638</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4720,12 +4696,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4752,10 +4728,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135257174</v>
+        <v>135253692</v>
       </c>
       <c r="B40" t="n">
-        <v>79130</v>
+        <v>83358</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4763,21 +4739,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4787,10 +4763,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>597800</v>
+        <v>597718</v>
       </c>
       <c r="R40" t="n">
-        <v>7071779</v>
+        <v>7071826</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4849,10 +4825,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135261478</v>
+        <v>135277130</v>
       </c>
       <c r="B41" t="n">
-        <v>79130</v>
+        <v>83358</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4860,37 +4836,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>597690</v>
+        <v>597672</v>
       </c>
       <c r="R41" t="n">
-        <v>7071824</v>
+        <v>7072025</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4919,7 +4895,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4929,7 +4905,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4944,60 +4920,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135261207</v>
+        <v>135277135</v>
       </c>
       <c r="B42" t="n">
-        <v>80492</v>
+        <v>83358</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6461</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>597651</v>
+        <v>597696</v>
       </c>
       <c r="R42" t="n">
-        <v>7071773</v>
+        <v>7071877</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5026,7 +5002,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5036,7 +5012,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5051,22 +5027,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119352061</v>
+        <v>111802223</v>
       </c>
       <c r="B43" t="n">
-        <v>57953</v>
+        <v>79084</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5074,42 +5050,40 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Kullberg, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>597652</v>
+        <v>597726</v>
       </c>
       <c r="R43" t="n">
-        <v>7071974</v>
+        <v>7071643</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5133,22 +5107,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5157,28 +5121,29 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135252357</v>
+        <v>135257132</v>
       </c>
       <c r="B44" t="n">
-        <v>57975</v>
+        <v>79130</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5186,42 +5151,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>597647</v>
+        <v>597810</v>
       </c>
       <c r="R44" t="n">
-        <v>7072042</v>
+        <v>7071731</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5248,24 +5208,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5280,22 +5225,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135252502</v>
+        <v>135257174</v>
       </c>
       <c r="B45" t="n">
-        <v>57975</v>
+        <v>79130</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5303,42 +5248,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>597650</v>
+        <v>597800</v>
       </c>
       <c r="R45" t="n">
-        <v>7071996</v>
+        <v>7071779</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5365,24 +5305,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:37</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5397,22 +5322,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135252549</v>
+        <v>135261478</v>
       </c>
       <c r="B46" t="n">
-        <v>57975</v>
+        <v>79130</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5420,42 +5345,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>597648</v>
+        <v>597690</v>
       </c>
       <c r="R46" t="n">
-        <v>7071988</v>
+        <v>7071824</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5484,7 +5404,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5494,12 +5414,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5514,22 +5429,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135252575</v>
+        <v>135185445</v>
       </c>
       <c r="B47" t="n">
-        <v>57975</v>
+        <v>79992</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5537,42 +5452,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>597654</v>
+        <v>597724</v>
       </c>
       <c r="R47" t="n">
-        <v>7071984</v>
+        <v>7071639</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5596,27 +5506,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>15:41</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5631,65 +5526,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135252599</v>
+        <v>135261207</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>80492</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>597652</v>
+        <v>597651</v>
       </c>
       <c r="R48" t="n">
-        <v>7071981</v>
+        <v>7071773</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5718,7 +5608,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5728,12 +5618,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5748,39 +5633,39 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135252771</v>
+        <v>135253925</v>
       </c>
       <c r="B49" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5800,13 +5685,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>597694</v>
+        <v>597717</v>
       </c>
       <c r="R49" t="n">
-        <v>7071960</v>
+        <v>7071813</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5833,24 +5718,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5865,22 +5735,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135253769</v>
+        <v>119352061</v>
       </c>
       <c r="B50" t="n">
-        <v>57975</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5917,10 +5787,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>597732</v>
+        <v>597652</v>
       </c>
       <c r="R50" t="n">
-        <v>7071814</v>
+        <v>7071974</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5947,27 +5817,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5982,60 +5847,65 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135277138</v>
+        <v>135185510</v>
       </c>
       <c r="B51" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>597826</v>
+        <v>597653</v>
       </c>
       <c r="R51" t="n">
-        <v>7071709</v>
+        <v>7071687</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6059,22 +5929,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>17:32</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>17:32</t>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6089,22 +5954,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135257192</v>
+        <v>135185592</v>
       </c>
       <c r="B52" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6112,27 +5977,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6141,10 +6006,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>597798</v>
+        <v>597662</v>
       </c>
       <c r="R52" t="n">
-        <v>7071782</v>
+        <v>7071777</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6171,12 +6036,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6203,45 +6073,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135277129</v>
+        <v>135252357</v>
       </c>
       <c r="B53" t="n">
-        <v>8449</v>
+        <v>57975</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106554</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>597655</v>
+        <v>597647</v>
       </c>
       <c r="R53" t="n">
-        <v>7072023</v>
+        <v>7072042</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6273,7 +6148,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6283,7 +6158,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6298,60 +6178,65 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135252291</v>
+        <v>135252502</v>
       </c>
       <c r="B54" t="n">
-        <v>99112</v>
+        <v>57975</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>597625</v>
+        <v>597650</v>
       </c>
       <c r="R54" t="n">
-        <v>7072015</v>
+        <v>7071996</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6378,9 +6263,24 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6395,60 +6295,65 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135253119</v>
+        <v>135252549</v>
       </c>
       <c r="B55" t="n">
-        <v>98060</v>
+        <v>57975</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>597685</v>
+        <v>597648</v>
       </c>
       <c r="R55" t="n">
-        <v>7071950</v>
+        <v>7071988</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6475,9 +6380,24 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6492,60 +6412,65 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135261205</v>
+        <v>135252575</v>
       </c>
       <c r="B56" t="n">
-        <v>98060</v>
+        <v>57975</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>597679</v>
+        <v>597654</v>
       </c>
       <c r="R56" t="n">
-        <v>7071921</v>
+        <v>7071984</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6574,7 +6499,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6584,7 +6509,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6599,60 +6529,65 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135261477</v>
+        <v>135252599</v>
       </c>
       <c r="B57" t="n">
-        <v>98060</v>
+        <v>57975</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>597690</v>
+        <v>597652</v>
       </c>
       <c r="R57" t="n">
-        <v>7071861</v>
+        <v>7071981</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6681,7 +6616,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6691,7 +6626,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6706,22 +6646,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135254080</v>
+        <v>135252771</v>
       </c>
       <c r="B58" t="n">
-        <v>79131</v>
+        <v>57975</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6729,34 +6669,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>597664</v>
+        <v>597694</v>
       </c>
       <c r="R58" t="n">
-        <v>7071792</v>
+        <v>7071960</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6788,7 +6733,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6798,7 +6743,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6825,10 +6775,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135254180</v>
+        <v>135253769</v>
       </c>
       <c r="B59" t="n">
-        <v>79131</v>
+        <v>57975</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6836,24 +6786,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
@@ -6895,7 +6850,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6905,7 +6860,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6932,48 +6892,58 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135254875</v>
+        <v>135254862</v>
       </c>
       <c r="B60" t="n">
-        <v>79131</v>
+        <v>57162</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>597688</v>
+        <v>597826</v>
       </c>
       <c r="R60" t="n">
-        <v>7071656</v>
+        <v>7071713</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7000,19 +6970,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>17:35</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7027,57 +6987,57 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135255066</v>
+        <v>135277138</v>
       </c>
       <c r="B61" t="n">
-        <v>79131</v>
+        <v>57162</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>597711</v>
+        <v>597826</v>
       </c>
       <c r="R61" t="n">
-        <v>7071632</v>
+        <v>7071709</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7109,7 +7069,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7119,7 +7079,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7134,22 +7094,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135255116</v>
+        <v>135185420</v>
       </c>
       <c r="B62" t="n">
-        <v>79131</v>
+        <v>58136</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7157,37 +7117,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>597691</v>
+        <v>597731</v>
       </c>
       <c r="R62" t="n">
-        <v>7071625</v>
+        <v>7071656</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7211,22 +7176,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>17:47</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>17:47</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7241,22 +7196,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135255849</v>
+        <v>135257192</v>
       </c>
       <c r="B63" t="n">
-        <v>79131</v>
+        <v>58136</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7264,37 +7219,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>597894</v>
+        <v>597798</v>
       </c>
       <c r="R63" t="n">
-        <v>7071564</v>
+        <v>7071782</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7321,19 +7281,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>18:19</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>18:19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7348,57 +7298,57 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135255990</v>
+        <v>135277129</v>
       </c>
       <c r="B64" t="n">
-        <v>79131</v>
+        <v>8449</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>106554</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>597890</v>
+        <v>597655</v>
       </c>
       <c r="R64" t="n">
-        <v>7071513</v>
+        <v>7072023</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7430,7 +7380,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7440,7 +7390,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7455,44 +7405,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135256152</v>
+        <v>135252291</v>
       </c>
       <c r="B65" t="n">
-        <v>79131</v>
+        <v>99112</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7502,13 +7452,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>597907</v>
+        <v>597625</v>
       </c>
       <c r="R65" t="n">
-        <v>7071543</v>
+        <v>7072015</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7535,19 +7485,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>18:28</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7562,60 +7502,60 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135261479</v>
+        <v>135253119</v>
       </c>
       <c r="B66" t="n">
-        <v>79131</v>
+        <v>98060</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>597679</v>
+        <v>597685</v>
       </c>
       <c r="R66" t="n">
-        <v>7071753</v>
+        <v>7071950</v>
       </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7642,19 +7582,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>17:13</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>17:13</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7669,60 +7599,60 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135277126</v>
+        <v>135261205</v>
       </c>
       <c r="B67" t="n">
-        <v>79963</v>
+        <v>98060</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>597628</v>
+        <v>597679</v>
       </c>
       <c r="R67" t="n">
-        <v>7072050</v>
+        <v>7071921</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7751,7 +7681,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7761,7 +7691,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7776,15 +7706,1192 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135261477</v>
+      </c>
+      <c r="B68" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>597690</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7071861</v>
+      </c>
+      <c r="S68" t="n">
+        <v>3</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135254080</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>597664</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7071792</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135254180</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>597732</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7071814</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135254875</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>597688</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7071656</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135255066</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>597711</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7071632</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135255116</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>597691</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7071625</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135255849</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>597894</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7071564</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135255990</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>597890</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7071513</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135256152</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>597907</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7071543</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135261479</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>597679</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7071753</v>
+      </c>
+      <c r="S77" t="n">
+        <v>3</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135277126</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>597628</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7072050</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
           <t>Anne-Katrin Würthele</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
+      <c r="AX78" t="inlineStr">
         <is>
           <t>Anne-Katrin Würthele</t>
         </is>
       </c>
-      <c r="AY67" t="inlineStr"/>
+      <c r="AY78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28113-2026 artfynd.xlsx
+++ b/artfynd/A 28113-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1073,48 +1073,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135261475</v>
+        <v>111802213</v>
       </c>
       <c r="B6" t="n">
-        <v>91974</v>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Kullberg, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597668</v>
+        <v>597737</v>
       </c>
       <c r="R6" t="n">
-        <v>7071982</v>
+        <v>7071647</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1138,22 +1141,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1162,50 +1155,51 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111802213</v>
+        <v>111802220</v>
       </c>
       <c r="B7" t="n">
-        <v>93213</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1218,10 +1212,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597737</v>
+        <v>597715</v>
       </c>
       <c r="R7" t="n">
-        <v>7071647</v>
+        <v>7071639</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1281,10 +1275,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111802220</v>
+        <v>135254269</v>
       </c>
       <c r="B8" t="n">
-        <v>93197</v>
+        <v>93271</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1310,22 +1304,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597715</v>
+        <v>597670</v>
       </c>
       <c r="R8" t="n">
-        <v>7071639</v>
+        <v>7071721</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1349,12 +1340,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1363,26 +1364,25 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135254269</v>
+        <v>135254935</v>
       </c>
       <c r="B9" t="n">
         <v>93271</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597670</v>
+        <v>597691</v>
       </c>
       <c r="R9" t="n">
-        <v>7071721</v>
+        <v>7071625</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1477,19 +1477,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135254935</v>
+        <v>135254970</v>
       </c>
       <c r="B10" t="n">
         <v>93271</v>
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597691</v>
+        <v>597704</v>
       </c>
       <c r="R10" t="n">
-        <v>7071625</v>
+        <v>7071626</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1584,19 +1584,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135254970</v>
+        <v>135261210</v>
       </c>
       <c r="B11" t="n">
         <v>93271</v>
@@ -1624,20 +1624,31 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597704</v>
+        <v>597710</v>
       </c>
       <c r="R11" t="n">
-        <v>7071626</v>
+        <v>7071633</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1666,7 +1677,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1676,7 +1687,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,77 +1696,67 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135261210</v>
+        <v>135253005</v>
       </c>
       <c r="B12" t="n">
-        <v>93271</v>
+        <v>91937</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597710</v>
+        <v>597700</v>
       </c>
       <c r="R12" t="n">
-        <v>7071633</v>
+        <v>7071941</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1782,47 +1783,36 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>17:44</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>17:44</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135253005</v>
+        <v>135253624</v>
       </c>
       <c r="B13" t="n">
         <v>91937</v>
@@ -1857,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597700</v>
+        <v>597702</v>
       </c>
       <c r="R13" t="n">
-        <v>7071941</v>
+        <v>7071879</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1919,32 +1909,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135253624</v>
+        <v>135252916</v>
       </c>
       <c r="B14" t="n">
-        <v>91937</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,13 +1944,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597702</v>
+        <v>597734</v>
       </c>
       <c r="R14" t="n">
-        <v>7071879</v>
+        <v>7071921</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1987,9 +1977,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2004,19 +2004,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135252916</v>
+        <v>135253853</v>
       </c>
       <c r="B15" t="n">
         <v>79373</v>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597734</v>
+        <v>597701</v>
       </c>
       <c r="R15" t="n">
-        <v>7071921</v>
+        <v>7071820</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2111,19 +2111,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135253853</v>
+        <v>135253965</v>
       </c>
       <c r="B16" t="n">
         <v>79373</v>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597701</v>
+        <v>597732</v>
       </c>
       <c r="R16" t="n">
-        <v>7071820</v>
+        <v>7071814</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2218,19 +2218,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135253965</v>
+        <v>135254335</v>
       </c>
       <c r="B17" t="n">
         <v>79373</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597732</v>
+        <v>597680</v>
       </c>
       <c r="R17" t="n">
-        <v>7071814</v>
+        <v>7071698</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2337,7 +2337,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135254335</v>
+        <v>135254748</v>
       </c>
       <c r="B18" t="n">
         <v>79373</v>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597680</v>
+        <v>597695</v>
       </c>
       <c r="R18" t="n">
-        <v>7071698</v>
+        <v>7071733</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2432,19 +2432,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135254748</v>
+        <v>135254797</v>
       </c>
       <c r="B19" t="n">
         <v>79373</v>
@@ -2479,13 +2479,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597695</v>
+        <v>597759</v>
       </c>
       <c r="R19" t="n">
-        <v>7071733</v>
+        <v>7071713</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2512,19 +2512,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>17:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2539,19 +2529,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135254797</v>
+        <v>135254865</v>
       </c>
       <c r="B20" t="n">
         <v>79373</v>
@@ -2586,13 +2576,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597759</v>
+        <v>597681</v>
       </c>
       <c r="R20" t="n">
-        <v>7071713</v>
+        <v>7071663</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2619,9 +2609,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2636,19 +2636,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135254865</v>
+        <v>135254896</v>
       </c>
       <c r="B21" t="n">
         <v>79373</v>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597681</v>
+        <v>597697</v>
       </c>
       <c r="R21" t="n">
-        <v>7071663</v>
+        <v>7071651</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2755,7 +2755,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135254896</v>
+        <v>135254907</v>
       </c>
       <c r="B22" t="n">
         <v>79373</v>
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597697</v>
+        <v>597691</v>
       </c>
       <c r="R22" t="n">
-        <v>7071651</v>
+        <v>7071625</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2850,19 +2850,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135254907</v>
+        <v>135255150</v>
       </c>
       <c r="B23" t="n">
         <v>79373</v>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597691</v>
+        <v>597738</v>
       </c>
       <c r="R23" t="n">
-        <v>7071625</v>
+        <v>7071628</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2957,19 +2957,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135255150</v>
+        <v>135255347</v>
       </c>
       <c r="B24" t="n">
         <v>79373</v>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597738</v>
+        <v>597781</v>
       </c>
       <c r="R24" t="n">
-        <v>7071628</v>
+        <v>7071649</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3076,7 +3076,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135255347</v>
+        <v>135255503</v>
       </c>
       <c r="B25" t="n">
         <v>79373</v>
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597781</v>
+        <v>597801</v>
       </c>
       <c r="R25" t="n">
-        <v>7071649</v>
+        <v>7071656</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,7 +3183,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135255503</v>
+        <v>135255763</v>
       </c>
       <c r="B26" t="n">
         <v>79373</v>
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597801</v>
+        <v>597871</v>
       </c>
       <c r="R26" t="n">
-        <v>7071656</v>
+        <v>7071582</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3290,7 +3290,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135255763</v>
+        <v>135255809</v>
       </c>
       <c r="B27" t="n">
         <v>79373</v>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597871</v>
+        <v>597883</v>
       </c>
       <c r="R27" t="n">
-        <v>7071582</v>
+        <v>7071561</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3397,7 +3397,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135255809</v>
+        <v>135256006</v>
       </c>
       <c r="B28" t="n">
         <v>79373</v>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>597883</v>
+        <v>597907</v>
       </c>
       <c r="R28" t="n">
-        <v>7071561</v>
+        <v>7071543</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3492,19 +3492,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135256006</v>
+        <v>135261206</v>
       </c>
       <c r="B29" t="n">
         <v>79373</v>
@@ -3533,19 +3533,22 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>597907</v>
+        <v>597650</v>
       </c>
       <c r="R29" t="n">
-        <v>7071543</v>
+        <v>7071766</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3574,7 +3577,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3584,7 +3587,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3593,25 +3596,41 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135261206</v>
+        <v>135261208</v>
       </c>
       <c r="B30" t="n">
         <v>79373</v>
@@ -3640,19 +3659,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>597650</v>
+        <v>597686</v>
       </c>
       <c r="R30" t="n">
-        <v>7071766</v>
+        <v>7071732</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3684,7 +3700,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3694,7 +3710,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3703,24 +3719,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3737,7 +3737,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135261208</v>
+        <v>135261209</v>
       </c>
       <c r="B31" t="n">
         <v>79373</v>
@@ -3772,10 +3772,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>597686</v>
+        <v>597692</v>
       </c>
       <c r="R31" t="n">
-        <v>7071732</v>
+        <v>7071677</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3844,7 +3844,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135261209</v>
+        <v>135261211</v>
       </c>
       <c r="B32" t="n">
         <v>79373</v>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>597692</v>
+        <v>597775</v>
       </c>
       <c r="R32" t="n">
-        <v>7071677</v>
+        <v>7071632</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3951,7 +3951,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135261211</v>
+        <v>135261212</v>
       </c>
       <c r="B33" t="n">
         <v>79373</v>
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>597775</v>
+        <v>597811</v>
       </c>
       <c r="R33" t="n">
-        <v>7071632</v>
+        <v>7071636</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4058,7 +4058,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135261212</v>
+        <v>135277134</v>
       </c>
       <c r="B34" t="n">
         <v>79373</v>
@@ -4089,17 +4089,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>597811</v>
+        <v>597690</v>
       </c>
       <c r="R34" t="n">
-        <v>7071636</v>
+        <v>7071889</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4153,63 +4153,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135261476</v>
+        <v>135277128</v>
       </c>
       <c r="B35" t="n">
-        <v>79373</v>
+        <v>79397</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>597705</v>
+        <v>597652</v>
       </c>
       <c r="R35" t="n">
-        <v>7071935</v>
+        <v>7072022</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4238,7 +4235,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4248,7 +4245,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4257,85 +4254,66 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135261480</v>
+        <v>135185455</v>
       </c>
       <c r="B36" t="n">
-        <v>79373</v>
+        <v>78776</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>597757</v>
+        <v>597723</v>
       </c>
       <c r="R36" t="n">
-        <v>7071733</v>
+        <v>7071638</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4359,22 +4337,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>17:27</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>17:27</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4383,82 +4351,66 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135277134</v>
+        <v>135253692</v>
       </c>
       <c r="B37" t="n">
-        <v>79373</v>
+        <v>83358</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>597690</v>
+        <v>597718</v>
       </c>
       <c r="R37" t="n">
-        <v>7071889</v>
+        <v>7071826</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4485,19 +4437,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4512,44 +4454,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135277128</v>
+        <v>135277130</v>
       </c>
       <c r="B38" t="n">
-        <v>79397</v>
+        <v>83358</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6434</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4559,10 +4501,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>597652</v>
+        <v>597672</v>
       </c>
       <c r="R38" t="n">
-        <v>7072022</v>
+        <v>7072025</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4594,7 +4536,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4604,7 +4546,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4631,10 +4573,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135185455</v>
+        <v>135277135</v>
       </c>
       <c r="B39" t="n">
-        <v>78776</v>
+        <v>83358</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4642,37 +4584,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>597723</v>
+        <v>597696</v>
       </c>
       <c r="R39" t="n">
-        <v>7071638</v>
+        <v>7071877</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4696,12 +4638,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4716,22 +4668,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135253692</v>
+        <v>111802223</v>
       </c>
       <c r="B40" t="n">
-        <v>83358</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4739,37 +4691,40 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Kullberg, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>597718</v>
+        <v>597726</v>
       </c>
       <c r="R40" t="n">
-        <v>7071826</v>
+        <v>7071643</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4793,12 +4748,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4807,28 +4762,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135277130</v>
+        <v>135257132</v>
       </c>
       <c r="B41" t="n">
-        <v>83358</v>
+        <v>79130</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4836,37 +4792,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>597672</v>
+        <v>597810</v>
       </c>
       <c r="R41" t="n">
-        <v>7072025</v>
+        <v>7071731</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4893,19 +4849,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:36</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4920,22 +4866,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135277135</v>
+        <v>135257174</v>
       </c>
       <c r="B42" t="n">
-        <v>83358</v>
+        <v>79130</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4943,37 +4889,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>597696</v>
+        <v>597800</v>
       </c>
       <c r="R42" t="n">
-        <v>7071877</v>
+        <v>7071779</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5000,19 +4946,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>16:33</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>16:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5027,22 +4963,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>111802223</v>
+        <v>135185445</v>
       </c>
       <c r="B43" t="n">
-        <v>79084</v>
+        <v>79992</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5050,40 +4986,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>597726</v>
+        <v>597724</v>
       </c>
       <c r="R43" t="n">
-        <v>7071643</v>
+        <v>7071639</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5107,12 +5040,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5121,67 +5054,66 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135257132</v>
+        <v>135261207</v>
       </c>
       <c r="B44" t="n">
-        <v>79130</v>
+        <v>80492</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>597810</v>
+        <v>597651</v>
       </c>
       <c r="R44" t="n">
-        <v>7071731</v>
+        <v>7071773</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5208,9 +5140,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5225,57 +5167,62 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135257174</v>
+        <v>135253925</v>
       </c>
       <c r="B45" t="n">
-        <v>79130</v>
+        <v>57972</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>597800</v>
+        <v>597717</v>
       </c>
       <c r="R45" t="n">
-        <v>7071779</v>
+        <v>7071813</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5334,10 +5281,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135261478</v>
+        <v>119352061</v>
       </c>
       <c r="B46" t="n">
-        <v>79130</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5345,37 +5292,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>597690</v>
+        <v>597652</v>
       </c>
       <c r="R46" t="n">
-        <v>7071824</v>
+        <v>7071974</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5399,22 +5351,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5429,22 +5381,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135185445</v>
+        <v>135185510</v>
       </c>
       <c r="B47" t="n">
-        <v>79992</v>
+        <v>57975</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5452,34 +5404,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>597724</v>
+        <v>597653</v>
       </c>
       <c r="R47" t="n">
-        <v>7071639</v>
+        <v>7071687</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5512,6 +5469,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5538,48 +5500,53 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135261207</v>
+        <v>135185592</v>
       </c>
       <c r="B48" t="n">
-        <v>80492</v>
+        <v>57975</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>597651</v>
+        <v>597662</v>
       </c>
       <c r="R48" t="n">
-        <v>7071773</v>
+        <v>7071777</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5603,22 +5570,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>17:01</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>17:01</t>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5633,39 +5595,39 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135253925</v>
+        <v>135252357</v>
       </c>
       <c r="B49" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5676,7 +5638,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5685,13 +5647,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>597717</v>
+        <v>597647</v>
       </c>
       <c r="R49" t="n">
-        <v>7071813</v>
+        <v>7072042</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5718,9 +5680,24 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5735,22 +5712,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119352061</v>
+        <v>135252502</v>
       </c>
       <c r="B50" t="n">
-        <v>57953</v>
+        <v>57975</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5787,10 +5764,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>597652</v>
+        <v>597650</v>
       </c>
       <c r="R50" t="n">
-        <v>7071974</v>
+        <v>7071996</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5817,22 +5794,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5859,7 +5841,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135185510</v>
+        <v>135252549</v>
       </c>
       <c r="B51" t="n">
         <v>57975</v>
@@ -5890,7 +5872,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5899,13 +5881,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>597653</v>
+        <v>597648</v>
       </c>
       <c r="R51" t="n">
-        <v>7071687</v>
+        <v>7071988</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5929,17 +5911,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5954,19 +5946,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135185592</v>
+        <v>135252575</v>
       </c>
       <c r="B52" t="n">
         <v>57975</v>
@@ -6006,13 +5998,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>597662</v>
+        <v>597654</v>
       </c>
       <c r="R52" t="n">
-        <v>7071777</v>
+        <v>7071984</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6036,17 +6028,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6061,19 +6063,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135252357</v>
+        <v>135252599</v>
       </c>
       <c r="B53" t="n">
         <v>57975</v>
@@ -6104,7 +6106,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6113,10 +6115,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>597647</v>
+        <v>597652</v>
       </c>
       <c r="R53" t="n">
-        <v>7072042</v>
+        <v>7071981</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6148,7 +6150,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6158,12 +6160,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6178,19 +6180,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135252502</v>
+        <v>135252771</v>
       </c>
       <c r="B54" t="n">
         <v>57975</v>
@@ -6230,10 +6232,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>597650</v>
+        <v>597694</v>
       </c>
       <c r="R54" t="n">
-        <v>7071996</v>
+        <v>7071960</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6265,7 +6267,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6275,7 +6277,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -6307,7 +6309,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135252549</v>
+        <v>135253769</v>
       </c>
       <c r="B55" t="n">
         <v>57975</v>
@@ -6347,10 +6349,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>597648</v>
+        <v>597732</v>
       </c>
       <c r="R55" t="n">
-        <v>7071988</v>
+        <v>7071814</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6382,7 +6384,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6392,7 +6394,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -6412,50 +6414,55 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135252575</v>
+        <v>135254862</v>
       </c>
       <c r="B56" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6464,13 +6471,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>597654</v>
+        <v>597826</v>
       </c>
       <c r="R56" t="n">
-        <v>7071984</v>
+        <v>7071713</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6497,24 +6504,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6529,62 +6521,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135252599</v>
+        <v>135277138</v>
       </c>
       <c r="B57" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>597652</v>
+        <v>597826</v>
       </c>
       <c r="R57" t="n">
-        <v>7071981</v>
+        <v>7071709</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6616,7 +6603,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6626,12 +6613,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6646,22 +6628,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135252771</v>
+        <v>135185420</v>
       </c>
       <c r="B58" t="n">
-        <v>57975</v>
+        <v>58136</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6669,27 +6651,27 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6698,13 +6680,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>597694</v>
+        <v>597731</v>
       </c>
       <c r="R58" t="n">
-        <v>7071960</v>
+        <v>7071656</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6728,27 +6710,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>15:55</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6763,22 +6730,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135253769</v>
+        <v>135257192</v>
       </c>
       <c r="B59" t="n">
-        <v>57975</v>
+        <v>58136</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6786,27 +6753,27 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6815,13 +6782,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>597732</v>
+        <v>597798</v>
       </c>
       <c r="R59" t="n">
-        <v>7071814</v>
+        <v>7071782</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6848,24 +6815,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>16:36</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6880,22 +6832,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135254862</v>
+        <v>135277129</v>
       </c>
       <c r="B60" t="n">
-        <v>57162</v>
+        <v>8449</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6903,47 +6855,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>597826</v>
+        <v>597655</v>
       </c>
       <c r="R60" t="n">
-        <v>7071713</v>
+        <v>7072023</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6970,9 +6912,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6987,22 +6939,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135277138</v>
+        <v>135252291</v>
       </c>
       <c r="B61" t="n">
-        <v>57162</v>
+        <v>99112</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7010,37 +6962,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>597826</v>
+        <v>597625</v>
       </c>
       <c r="R61" t="n">
-        <v>7071709</v>
+        <v>7072015</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7067,19 +7019,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>17:32</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>17:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7094,62 +7036,57 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135185420</v>
+        <v>135253119</v>
       </c>
       <c r="B62" t="n">
-        <v>58136</v>
+        <v>98060</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>597731</v>
+        <v>597685</v>
       </c>
       <c r="R62" t="n">
-        <v>7071656</v>
+        <v>7071950</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7176,12 +7113,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7208,53 +7145,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135257192</v>
+        <v>135261205</v>
       </c>
       <c r="B63" t="n">
-        <v>58136</v>
+        <v>98060</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>597798</v>
+        <v>597679</v>
       </c>
       <c r="R63" t="n">
-        <v>7071782</v>
+        <v>7071921</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7281,9 +7213,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7298,57 +7240,57 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135277129</v>
+        <v>135254080</v>
       </c>
       <c r="B64" t="n">
-        <v>8449</v>
+        <v>79131</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106554</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>597655</v>
+        <v>597664</v>
       </c>
       <c r="R64" t="n">
-        <v>7072023</v>
+        <v>7071792</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7380,7 +7322,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7390,7 +7332,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7405,44 +7347,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135252291</v>
+        <v>135254180</v>
       </c>
       <c r="B65" t="n">
-        <v>99112</v>
+        <v>79131</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7452,13 +7394,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>597625</v>
+        <v>597732</v>
       </c>
       <c r="R65" t="n">
-        <v>7072015</v>
+        <v>7071814</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7485,9 +7427,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7502,44 +7454,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135253119</v>
+        <v>135254875</v>
       </c>
       <c r="B66" t="n">
-        <v>98060</v>
+        <v>79131</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7549,13 +7501,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>597685</v>
+        <v>597688</v>
       </c>
       <c r="R66" t="n">
-        <v>7071950</v>
+        <v>7071656</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7582,9 +7534,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7599,60 +7561,60 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135261205</v>
+        <v>135255066</v>
       </c>
       <c r="B67" t="n">
-        <v>98060</v>
+        <v>79131</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>597679</v>
+        <v>597711</v>
       </c>
       <c r="R67" t="n">
-        <v>7071921</v>
+        <v>7071632</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7681,7 +7643,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7691,7 +7653,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7706,60 +7668,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135261477</v>
+        <v>135255116</v>
       </c>
       <c r="B68" t="n">
-        <v>98060</v>
+        <v>79131</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>597690</v>
+        <v>597691</v>
       </c>
       <c r="R68" t="n">
-        <v>7071861</v>
+        <v>7071625</v>
       </c>
       <c r="S68" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7788,7 +7750,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7798,7 +7760,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7813,19 +7775,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135254080</v>
+        <v>135255849</v>
       </c>
       <c r="B69" t="n">
         <v>79131</v>
@@ -7860,10 +7822,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>597664</v>
+        <v>597894</v>
       </c>
       <c r="R69" t="n">
-        <v>7071792</v>
+        <v>7071564</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7895,7 +7857,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7905,7 +7867,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7932,7 +7894,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135254180</v>
+        <v>135255990</v>
       </c>
       <c r="B70" t="n">
         <v>79131</v>
@@ -7963,14 +7925,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>597732</v>
+        <v>597890</v>
       </c>
       <c r="R70" t="n">
-        <v>7071814</v>
+        <v>7071513</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8002,7 +7964,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8012,7 +7974,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8027,19 +7989,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135254875</v>
+        <v>135256152</v>
       </c>
       <c r="B71" t="n">
         <v>79131</v>
@@ -8074,10 +8036,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>597688</v>
+        <v>597907</v>
       </c>
       <c r="R71" t="n">
-        <v>7071656</v>
+        <v>7071543</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8109,7 +8071,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8119,7 +8081,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8134,22 +8096,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135255066</v>
+        <v>135277126</v>
       </c>
       <c r="B72" t="n">
-        <v>79131</v>
+        <v>79963</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8157,34 +8119,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>597711</v>
+        <v>597628</v>
       </c>
       <c r="R72" t="n">
-        <v>7071632</v>
+        <v>7072050</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8216,7 +8178,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8226,7 +8188,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8241,657 +8203,15 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>135255116</v>
-      </c>
-      <c r="B73" t="n">
-        <v>79131</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>597691</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7071625</v>
-      </c>
-      <c r="S73" t="n">
-        <v>10</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>17:47</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>17:47</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Johanna Liljegren</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Johanna Liljegren</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>135255849</v>
-      </c>
-      <c r="B74" t="n">
-        <v>79131</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>597894</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7071564</v>
-      </c>
-      <c r="S74" t="n">
-        <v>10</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>18:19</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>18:19</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>135255990</v>
-      </c>
-      <c r="B75" t="n">
-        <v>79131</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>597890</v>
-      </c>
-      <c r="R75" t="n">
-        <v>7071513</v>
-      </c>
-      <c r="S75" t="n">
-        <v>10</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>18:23</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>18:23</t>
-        </is>
-      </c>
-      <c r="AD75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>135256152</v>
-      </c>
-      <c r="B76" t="n">
-        <v>79131</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>597907</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7071543</v>
-      </c>
-      <c r="S76" t="n">
-        <v>10</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Johanna Liljegren</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Johanna Liljegren</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>135261479</v>
-      </c>
-      <c r="B77" t="n">
-        <v>79131</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Lill-kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q77" t="n">
-        <v>597679</v>
-      </c>
-      <c r="R77" t="n">
-        <v>7071753</v>
-      </c>
-      <c r="S77" t="n">
-        <v>3</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>17:13</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>17:13</t>
-        </is>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT77" t="inlineStr"/>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>135277126</v>
-      </c>
-      <c r="B78" t="n">
-        <v>79963</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
-        </is>
-      </c>
-      <c r="Q78" t="n">
-        <v>597628</v>
-      </c>
-      <c r="R78" t="n">
-        <v>7072050</v>
-      </c>
-      <c r="S78" t="n">
-        <v>10</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AD78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT78" t="inlineStr"/>
-      <c r="AW78" t="inlineStr">
-        <is>
-          <t>Anne-Katrin Würthele</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>Anne-Katrin Würthele</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28113-2026 artfynd.xlsx
+++ b/artfynd/A 28113-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AY78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1073,51 +1073,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111802213</v>
+        <v>135261475</v>
       </c>
       <c r="B6" t="n">
-        <v>93213</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597737</v>
+        <v>597668</v>
       </c>
       <c r="R6" t="n">
-        <v>7071647</v>
+        <v>7071982</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1141,12 +1138,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1155,51 +1162,50 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111802220</v>
+        <v>111802213</v>
       </c>
       <c r="B7" t="n">
-        <v>93197</v>
+        <v>93213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1212,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597715</v>
+        <v>597737</v>
       </c>
       <c r="R7" t="n">
-        <v>7071639</v>
+        <v>7071647</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1275,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135254269</v>
+        <v>111802220</v>
       </c>
       <c r="B8" t="n">
-        <v>93271</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1304,19 +1310,22 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Kullberg, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597670</v>
+        <v>597715</v>
       </c>
       <c r="R8" t="n">
-        <v>7071721</v>
+        <v>7071639</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1340,22 +1349,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>17:02</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:02</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,25 +1363,26 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135254935</v>
+        <v>135254269</v>
       </c>
       <c r="B9" t="n">
         <v>93271</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597691</v>
+        <v>597670</v>
       </c>
       <c r="R9" t="n">
-        <v>7071625</v>
+        <v>7071721</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1477,19 +1477,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135254970</v>
+        <v>135254935</v>
       </c>
       <c r="B10" t="n">
         <v>93271</v>
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597704</v>
+        <v>597691</v>
       </c>
       <c r="R10" t="n">
-        <v>7071626</v>
+        <v>7071625</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1584,19 +1584,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135261210</v>
+        <v>135254970</v>
       </c>
       <c r="B11" t="n">
         <v>93271</v>
@@ -1624,31 +1624,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597710</v>
+        <v>597704</v>
       </c>
       <c r="R11" t="n">
-        <v>7071633</v>
+        <v>7071626</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1677,7 +1666,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1687,7 +1676,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1696,67 +1685,77 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135253005</v>
+        <v>135261210</v>
       </c>
       <c r="B12" t="n">
-        <v>91937</v>
+        <v>93271</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597700</v>
+        <v>597710</v>
       </c>
       <c r="R12" t="n">
-        <v>7071941</v>
+        <v>7071633</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1783,36 +1782,47 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135253624</v>
+        <v>135253005</v>
       </c>
       <c r="B13" t="n">
         <v>91937</v>
@@ -1847,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597702</v>
+        <v>597700</v>
       </c>
       <c r="R13" t="n">
-        <v>7071879</v>
+        <v>7071941</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1909,32 +1919,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135252916</v>
+        <v>135253624</v>
       </c>
       <c r="B14" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,13 +1954,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597734</v>
+        <v>597702</v>
       </c>
       <c r="R14" t="n">
-        <v>7071921</v>
+        <v>7071879</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1977,19 +1987,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2004,19 +2004,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135253853</v>
+        <v>135252916</v>
       </c>
       <c r="B15" t="n">
         <v>79373</v>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597701</v>
+        <v>597734</v>
       </c>
       <c r="R15" t="n">
-        <v>7071820</v>
+        <v>7071921</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2111,19 +2111,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135253965</v>
+        <v>135253853</v>
       </c>
       <c r="B16" t="n">
         <v>79373</v>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597732</v>
+        <v>597701</v>
       </c>
       <c r="R16" t="n">
-        <v>7071814</v>
+        <v>7071820</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2218,19 +2218,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135254335</v>
+        <v>135253965</v>
       </c>
       <c r="B17" t="n">
         <v>79373</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597680</v>
+        <v>597732</v>
       </c>
       <c r="R17" t="n">
-        <v>7071698</v>
+        <v>7071814</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2337,7 +2337,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135254748</v>
+        <v>135254335</v>
       </c>
       <c r="B18" t="n">
         <v>79373</v>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597695</v>
+        <v>597680</v>
       </c>
       <c r="R18" t="n">
-        <v>7071733</v>
+        <v>7071698</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2432,19 +2432,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135254797</v>
+        <v>135254748</v>
       </c>
       <c r="B19" t="n">
         <v>79373</v>
@@ -2479,13 +2479,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597759</v>
+        <v>597695</v>
       </c>
       <c r="R19" t="n">
-        <v>7071713</v>
+        <v>7071733</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2512,9 +2512,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2529,19 +2539,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135254865</v>
+        <v>135254797</v>
       </c>
       <c r="B20" t="n">
         <v>79373</v>
@@ -2576,13 +2586,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597681</v>
+        <v>597759</v>
       </c>
       <c r="R20" t="n">
-        <v>7071663</v>
+        <v>7071713</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2609,19 +2619,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>17:33</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2636,19 +2636,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135254896</v>
+        <v>135254865</v>
       </c>
       <c r="B21" t="n">
         <v>79373</v>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597697</v>
+        <v>597681</v>
       </c>
       <c r="R21" t="n">
-        <v>7071651</v>
+        <v>7071663</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2755,7 +2755,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135254907</v>
+        <v>135254896</v>
       </c>
       <c r="B22" t="n">
         <v>79373</v>
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597691</v>
+        <v>597697</v>
       </c>
       <c r="R22" t="n">
-        <v>7071625</v>
+        <v>7071651</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2850,19 +2850,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135255150</v>
+        <v>135254907</v>
       </c>
       <c r="B23" t="n">
         <v>79373</v>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597738</v>
+        <v>597691</v>
       </c>
       <c r="R23" t="n">
-        <v>7071628</v>
+        <v>7071625</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2957,19 +2957,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135255347</v>
+        <v>135255150</v>
       </c>
       <c r="B24" t="n">
         <v>79373</v>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597781</v>
+        <v>597738</v>
       </c>
       <c r="R24" t="n">
-        <v>7071649</v>
+        <v>7071628</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3076,7 +3076,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135255503</v>
+        <v>135255347</v>
       </c>
       <c r="B25" t="n">
         <v>79373</v>
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597801</v>
+        <v>597781</v>
       </c>
       <c r="R25" t="n">
-        <v>7071656</v>
+        <v>7071649</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,7 +3183,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135255763</v>
+        <v>135255503</v>
       </c>
       <c r="B26" t="n">
         <v>79373</v>
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597871</v>
+        <v>597801</v>
       </c>
       <c r="R26" t="n">
-        <v>7071582</v>
+        <v>7071656</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3290,7 +3290,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135255809</v>
+        <v>135255763</v>
       </c>
       <c r="B27" t="n">
         <v>79373</v>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597883</v>
+        <v>597871</v>
       </c>
       <c r="R27" t="n">
-        <v>7071561</v>
+        <v>7071582</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3397,7 +3397,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135256006</v>
+        <v>135255809</v>
       </c>
       <c r="B28" t="n">
         <v>79373</v>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>597907</v>
+        <v>597883</v>
       </c>
       <c r="R28" t="n">
-        <v>7071543</v>
+        <v>7071561</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3492,19 +3492,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135261206</v>
+        <v>135256006</v>
       </c>
       <c r="B29" t="n">
         <v>79373</v>
@@ -3533,22 +3533,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>597650</v>
+        <v>597907</v>
       </c>
       <c r="R29" t="n">
-        <v>7071766</v>
+        <v>7071543</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3577,7 +3574,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3587,7 +3584,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3596,41 +3593,25 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135261208</v>
+        <v>135261206</v>
       </c>
       <c r="B30" t="n">
         <v>79373</v>
@@ -3659,16 +3640,19 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>597686</v>
+        <v>597650</v>
       </c>
       <c r="R30" t="n">
-        <v>7071732</v>
+        <v>7071766</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3700,7 +3684,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3710,7 +3694,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3719,8 +3703,24 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3737,7 +3737,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135261209</v>
+        <v>135261208</v>
       </c>
       <c r="B31" t="n">
         <v>79373</v>
@@ -3772,10 +3772,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>597692</v>
+        <v>597686</v>
       </c>
       <c r="R31" t="n">
-        <v>7071677</v>
+        <v>7071732</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3844,7 +3844,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135261211</v>
+        <v>135261209</v>
       </c>
       <c r="B32" t="n">
         <v>79373</v>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>597775</v>
+        <v>597692</v>
       </c>
       <c r="R32" t="n">
-        <v>7071632</v>
+        <v>7071677</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3951,7 +3951,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135261212</v>
+        <v>135261211</v>
       </c>
       <c r="B33" t="n">
         <v>79373</v>
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>597811</v>
+        <v>597775</v>
       </c>
       <c r="R33" t="n">
-        <v>7071636</v>
+        <v>7071632</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4058,7 +4058,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135277134</v>
+        <v>135261212</v>
       </c>
       <c r="B34" t="n">
         <v>79373</v>
@@ -4089,17 +4089,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>597690</v>
+        <v>597811</v>
       </c>
       <c r="R34" t="n">
-        <v>7071889</v>
+        <v>7071636</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4153,60 +4153,63 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135277128</v>
+        <v>135261476</v>
       </c>
       <c r="B35" t="n">
-        <v>79397</v>
+        <v>79373</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>597652</v>
+        <v>597705</v>
       </c>
       <c r="R35" t="n">
-        <v>7072022</v>
+        <v>7071935</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4235,7 +4238,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4245,7 +4248,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4254,66 +4257,85 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135185455</v>
+        <v>135261480</v>
       </c>
       <c r="B36" t="n">
-        <v>78776</v>
+        <v>79373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>597723</v>
+        <v>597757</v>
       </c>
       <c r="R36" t="n">
-        <v>7071638</v>
+        <v>7071733</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4337,12 +4359,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4351,66 +4383,82 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135253692</v>
+        <v>135277134</v>
       </c>
       <c r="B37" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>597718</v>
+        <v>597690</v>
       </c>
       <c r="R37" t="n">
-        <v>7071826</v>
+        <v>7071889</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4437,9 +4485,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4454,44 +4512,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135277130</v>
+        <v>135277128</v>
       </c>
       <c r="B38" t="n">
-        <v>83358</v>
+        <v>79397</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6434</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4501,10 +4559,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>597672</v>
+        <v>597652</v>
       </c>
       <c r="R38" t="n">
-        <v>7072025</v>
+        <v>7072022</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4536,7 +4594,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4546,7 +4604,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4573,10 +4631,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135277135</v>
+        <v>135185455</v>
       </c>
       <c r="B39" t="n">
-        <v>83358</v>
+        <v>78776</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4584,37 +4642,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>597696</v>
+        <v>597723</v>
       </c>
       <c r="R39" t="n">
-        <v>7071877</v>
+        <v>7071638</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4638,22 +4696,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>16:33</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>16:33</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4668,22 +4716,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>111802223</v>
+        <v>135253692</v>
       </c>
       <c r="B40" t="n">
-        <v>79084</v>
+        <v>83358</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4691,40 +4739,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>597726</v>
+        <v>597718</v>
       </c>
       <c r="R40" t="n">
-        <v>7071643</v>
+        <v>7071826</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4748,12 +4793,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4762,29 +4807,28 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135257132</v>
+        <v>135277130</v>
       </c>
       <c r="B41" t="n">
-        <v>79130</v>
+        <v>83358</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4792,37 +4836,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>597810</v>
+        <v>597672</v>
       </c>
       <c r="R41" t="n">
-        <v>7071731</v>
+        <v>7072025</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4849,9 +4893,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4866,22 +4920,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135257174</v>
+        <v>135277135</v>
       </c>
       <c r="B42" t="n">
-        <v>79130</v>
+        <v>83358</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4889,37 +4943,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>597800</v>
+        <v>597696</v>
       </c>
       <c r="R42" t="n">
-        <v>7071779</v>
+        <v>7071877</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4946,9 +5000,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4963,22 +5027,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135185445</v>
+        <v>111802223</v>
       </c>
       <c r="B43" t="n">
-        <v>79992</v>
+        <v>79084</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4986,37 +5050,40 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Kullberg, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>597724</v>
+        <v>597726</v>
       </c>
       <c r="R43" t="n">
-        <v>7071639</v>
+        <v>7071643</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5040,12 +5107,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5054,66 +5121,67 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135261207</v>
+        <v>135257132</v>
       </c>
       <c r="B44" t="n">
-        <v>80492</v>
+        <v>79130</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>597651</v>
+        <v>597810</v>
       </c>
       <c r="R44" t="n">
-        <v>7071773</v>
+        <v>7071731</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5140,19 +5208,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>17:01</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>17:01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5167,62 +5225,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135253925</v>
+        <v>135257174</v>
       </c>
       <c r="B45" t="n">
-        <v>57972</v>
+        <v>79130</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>597717</v>
+        <v>597800</v>
       </c>
       <c r="R45" t="n">
-        <v>7071813</v>
+        <v>7071779</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5281,10 +5334,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119352061</v>
+        <v>135261478</v>
       </c>
       <c r="B46" t="n">
-        <v>57953</v>
+        <v>79130</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5292,42 +5345,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>597652</v>
+        <v>597690</v>
       </c>
       <c r="R46" t="n">
-        <v>7071974</v>
+        <v>7071824</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5351,22 +5399,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5381,22 +5429,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135185510</v>
+        <v>135185445</v>
       </c>
       <c r="B47" t="n">
-        <v>57975</v>
+        <v>79992</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5404,39 +5452,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>597653</v>
+        <v>597724</v>
       </c>
       <c r="R47" t="n">
-        <v>7071687</v>
+        <v>7071639</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5469,11 +5512,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5500,53 +5538,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135185592</v>
+        <v>135261207</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>80492</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>597662</v>
+        <v>597651</v>
       </c>
       <c r="R48" t="n">
-        <v>7071777</v>
+        <v>7071773</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5570,17 +5603,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5595,39 +5633,39 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135252357</v>
+        <v>135253925</v>
       </c>
       <c r="B49" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5638,7 +5676,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5647,13 +5685,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>597647</v>
+        <v>597717</v>
       </c>
       <c r="R49" t="n">
-        <v>7072042</v>
+        <v>7071813</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5680,24 +5718,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5712,22 +5735,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135252502</v>
+        <v>119352061</v>
       </c>
       <c r="B50" t="n">
-        <v>57975</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5764,10 +5787,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>597650</v>
+        <v>597652</v>
       </c>
       <c r="R50" t="n">
-        <v>7071996</v>
+        <v>7071974</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5794,27 +5817,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5841,7 +5859,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135252549</v>
+        <v>135185510</v>
       </c>
       <c r="B51" t="n">
         <v>57975</v>
@@ -5872,7 +5890,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5881,13 +5899,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>597648</v>
+        <v>597653</v>
       </c>
       <c r="R51" t="n">
-        <v>7071988</v>
+        <v>7071687</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5911,27 +5929,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5946,19 +5954,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135252575</v>
+        <v>135185592</v>
       </c>
       <c r="B52" t="n">
         <v>57975</v>
@@ -5998,13 +6006,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>597654</v>
+        <v>597662</v>
       </c>
       <c r="R52" t="n">
-        <v>7071984</v>
+        <v>7071777</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6028,27 +6036,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:41</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:41</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6063,19 +6061,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135252599</v>
+        <v>135252357</v>
       </c>
       <c r="B53" t="n">
         <v>57975</v>
@@ -6106,7 +6104,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6115,10 +6113,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>597652</v>
+        <v>597647</v>
       </c>
       <c r="R53" t="n">
-        <v>7071981</v>
+        <v>7072042</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6150,7 +6148,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6160,12 +6158,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6180,19 +6178,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135252771</v>
+        <v>135252502</v>
       </c>
       <c r="B54" t="n">
         <v>57975</v>
@@ -6232,10 +6230,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>597694</v>
+        <v>597650</v>
       </c>
       <c r="R54" t="n">
-        <v>7071960</v>
+        <v>7071996</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6267,7 +6265,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6277,7 +6275,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -6309,7 +6307,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135253769</v>
+        <v>135252549</v>
       </c>
       <c r="B55" t="n">
         <v>57975</v>
@@ -6349,10 +6347,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>597732</v>
+        <v>597648</v>
       </c>
       <c r="R55" t="n">
-        <v>7071814</v>
+        <v>7071988</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6384,7 +6382,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6394,7 +6392,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -6414,55 +6412,50 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135254862</v>
+        <v>135252575</v>
       </c>
       <c r="B56" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6471,13 +6464,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>597826</v>
+        <v>597654</v>
       </c>
       <c r="R56" t="n">
-        <v>7071713</v>
+        <v>7071984</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6504,9 +6497,24 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6521,57 +6529,62 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135277138</v>
+        <v>135252599</v>
       </c>
       <c r="B57" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>597826</v>
+        <v>597652</v>
       </c>
       <c r="R57" t="n">
-        <v>7071709</v>
+        <v>7071981</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6603,7 +6616,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6613,7 +6626,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6628,22 +6646,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135185420</v>
+        <v>135252771</v>
       </c>
       <c r="B58" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6651,27 +6669,27 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6680,13 +6698,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>597731</v>
+        <v>597694</v>
       </c>
       <c r="R58" t="n">
-        <v>7071656</v>
+        <v>7071960</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6710,12 +6728,27 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6730,22 +6763,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135257192</v>
+        <v>135253769</v>
       </c>
       <c r="B59" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6753,27 +6786,27 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6782,13 +6815,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>597798</v>
+        <v>597732</v>
       </c>
       <c r="R59" t="n">
-        <v>7071782</v>
+        <v>7071814</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6815,9 +6848,24 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6832,22 +6880,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135277129</v>
+        <v>135254862</v>
       </c>
       <c r="B60" t="n">
-        <v>8449</v>
+        <v>57162</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6855,37 +6903,47 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>597655</v>
+        <v>597826</v>
       </c>
       <c r="R60" t="n">
-        <v>7072023</v>
+        <v>7071713</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6912,19 +6970,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>15:32</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6939,22 +6987,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135252291</v>
+        <v>135277138</v>
       </c>
       <c r="B61" t="n">
-        <v>99112</v>
+        <v>57162</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6962,37 +7010,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>597625</v>
+        <v>597826</v>
       </c>
       <c r="R61" t="n">
-        <v>7072015</v>
+        <v>7071709</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7019,9 +7067,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7036,57 +7094,62 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135253119</v>
+        <v>135185420</v>
       </c>
       <c r="B62" t="n">
-        <v>98060</v>
+        <v>58136</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>597685</v>
+        <v>597731</v>
       </c>
       <c r="R62" t="n">
-        <v>7071950</v>
+        <v>7071656</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7113,12 +7176,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7145,48 +7208,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135261205</v>
+        <v>135257192</v>
       </c>
       <c r="B63" t="n">
-        <v>98060</v>
+        <v>58136</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>597679</v>
+        <v>597798</v>
       </c>
       <c r="R63" t="n">
-        <v>7071921</v>
+        <v>7071782</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7213,19 +7281,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>16:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7240,57 +7298,57 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135254080</v>
+        <v>135277129</v>
       </c>
       <c r="B64" t="n">
-        <v>79131</v>
+        <v>8449</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>106554</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>597664</v>
+        <v>597655</v>
       </c>
       <c r="R64" t="n">
-        <v>7071792</v>
+        <v>7072023</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7322,7 +7380,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7332,7 +7390,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7347,44 +7405,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135254180</v>
+        <v>135252291</v>
       </c>
       <c r="B65" t="n">
-        <v>79131</v>
+        <v>99112</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7394,13 +7452,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>597732</v>
+        <v>597625</v>
       </c>
       <c r="R65" t="n">
-        <v>7071814</v>
+        <v>7072015</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7427,19 +7485,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>16:55</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7454,44 +7502,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135254875</v>
+        <v>135253119</v>
       </c>
       <c r="B66" t="n">
-        <v>79131</v>
+        <v>98060</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7501,13 +7549,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>597688</v>
+        <v>597685</v>
       </c>
       <c r="R66" t="n">
-        <v>7071656</v>
+        <v>7071950</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7534,19 +7582,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>17:35</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7561,60 +7599,60 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135255066</v>
+        <v>135261205</v>
       </c>
       <c r="B67" t="n">
-        <v>79131</v>
+        <v>98060</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>597711</v>
+        <v>597679</v>
       </c>
       <c r="R67" t="n">
-        <v>7071632</v>
+        <v>7071921</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7643,7 +7681,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7653,7 +7691,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7668,60 +7706,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135255116</v>
+        <v>135261477</v>
       </c>
       <c r="B68" t="n">
-        <v>79131</v>
+        <v>98060</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>597691</v>
+        <v>597690</v>
       </c>
       <c r="R68" t="n">
-        <v>7071625</v>
+        <v>7071861</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7750,7 +7788,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7760,7 +7798,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7775,19 +7813,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135255849</v>
+        <v>135254080</v>
       </c>
       <c r="B69" t="n">
         <v>79131</v>
@@ -7822,10 +7860,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>597894</v>
+        <v>597664</v>
       </c>
       <c r="R69" t="n">
-        <v>7071564</v>
+        <v>7071792</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7857,7 +7895,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7867,7 +7905,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7894,7 +7932,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135255990</v>
+        <v>135254180</v>
       </c>
       <c r="B70" t="n">
         <v>79131</v>
@@ -7925,14 +7963,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>597890</v>
+        <v>597732</v>
       </c>
       <c r="R70" t="n">
-        <v>7071513</v>
+        <v>7071814</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7964,7 +8002,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7974,7 +8012,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7989,19 +8027,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135256152</v>
+        <v>135254875</v>
       </c>
       <c r="B71" t="n">
         <v>79131</v>
@@ -8036,10 +8074,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>597907</v>
+        <v>597688</v>
       </c>
       <c r="R71" t="n">
-        <v>7071543</v>
+        <v>7071656</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8071,7 +8109,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8081,7 +8119,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8096,22 +8134,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135277126</v>
+        <v>135255066</v>
       </c>
       <c r="B72" t="n">
-        <v>79963</v>
+        <v>79131</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8119,34 +8157,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>597628</v>
+        <v>597711</v>
       </c>
       <c r="R72" t="n">
-        <v>7072050</v>
+        <v>7071632</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8178,7 +8216,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8188,7 +8226,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8203,15 +8241,657 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135255116</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>597691</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7071625</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135255849</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>597894</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7071564</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135255990</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>597890</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7071513</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135256152</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>597907</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7071543</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135261479</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>597679</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7071753</v>
+      </c>
+      <c r="S77" t="n">
+        <v>3</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135277126</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>597628</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7072050</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
           <t>Anne-Katrin Würthele</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
+      <c r="AX78" t="inlineStr">
         <is>
           <t>Anne-Katrin Würthele</t>
         </is>
       </c>
-      <c r="AY72" t="inlineStr"/>
+      <c r="AY78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28113-2026 artfynd.xlsx
+++ b/artfynd/A 28113-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AZ72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135185577</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254148</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252944</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,51 +1090,59 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135253662</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135261475</v>
+        <v>111802213</v>
       </c>
       <c r="B6" t="n">
-        <v>91974</v>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Kullberg, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597668</v>
+        <v>597737</v>
       </c>
       <c r="R6" t="n">
-        <v>7071982</v>
+        <v>7071647</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1138,22 +1166,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1162,50 +1180,56 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111802213</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111802213</v>
+        <v>111802220</v>
       </c>
       <c r="B7" t="n">
-        <v>93213</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1218,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597737</v>
+        <v>597715</v>
       </c>
       <c r="R7" t="n">
-        <v>7071647</v>
+        <v>7071639</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1278,13 +1302,18 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111802220</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111802220</v>
+        <v>135254269</v>
       </c>
       <c r="B8" t="n">
-        <v>93197</v>
+        <v>93271</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1310,22 +1339,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597715</v>
+        <v>597670</v>
       </c>
       <c r="R8" t="n">
-        <v>7071639</v>
+        <v>7071721</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1349,12 +1375,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1363,26 +1399,30 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254269</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135254269</v>
+        <v>135254935</v>
       </c>
       <c r="B9" t="n">
         <v>93271</v>
@@ -1417,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597670</v>
+        <v>597691</v>
       </c>
       <c r="R9" t="n">
-        <v>7071721</v>
+        <v>7071625</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1452,7 +1492,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1462,7 +1502,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1477,19 +1517,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254935</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135254935</v>
+        <v>135254970</v>
       </c>
       <c r="B10" t="n">
         <v>93271</v>
@@ -1524,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597691</v>
+        <v>597704</v>
       </c>
       <c r="R10" t="n">
-        <v>7071625</v>
+        <v>7071626</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1559,7 +1604,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1569,7 +1614,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1584,19 +1629,24 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254970</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135254970</v>
+        <v>135261210</v>
       </c>
       <c r="B11" t="n">
         <v>93271</v>
@@ -1624,20 +1674,31 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597704</v>
+        <v>597710</v>
       </c>
       <c r="R11" t="n">
-        <v>7071626</v>
+        <v>7071633</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1666,7 +1727,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1676,7 +1737,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,77 +1746,72 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261210</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135261210</v>
+        <v>135253005</v>
       </c>
       <c r="B12" t="n">
-        <v>93271</v>
+        <v>91937</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597710</v>
+        <v>597700</v>
       </c>
       <c r="R12" t="n">
-        <v>7071633</v>
+        <v>7071941</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1782,47 +1838,41 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>17:44</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>17:44</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135253005</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135253005</v>
+        <v>135253624</v>
       </c>
       <c r="B13" t="n">
         <v>91937</v>
@@ -1857,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597700</v>
+        <v>597702</v>
       </c>
       <c r="R13" t="n">
-        <v>7071941</v>
+        <v>7071879</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1916,35 +1966,40 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135253624</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135253624</v>
+        <v>135252916</v>
       </c>
       <c r="B14" t="n">
-        <v>91937</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,13 +2009,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597702</v>
+        <v>597734</v>
       </c>
       <c r="R14" t="n">
-        <v>7071879</v>
+        <v>7071921</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1987,9 +2042,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2004,19 +2069,24 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252916</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135252916</v>
+        <v>135253853</v>
       </c>
       <c r="B15" t="n">
         <v>79373</v>
@@ -2051,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597734</v>
+        <v>597701</v>
       </c>
       <c r="R15" t="n">
-        <v>7071921</v>
+        <v>7071820</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2086,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2096,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2111,19 +2181,24 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135253853</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135253853</v>
+        <v>135253965</v>
       </c>
       <c r="B16" t="n">
         <v>79373</v>
@@ -2158,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597701</v>
+        <v>597732</v>
       </c>
       <c r="R16" t="n">
-        <v>7071820</v>
+        <v>7071814</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2193,7 +2268,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2203,7 +2278,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2218,19 +2293,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135253965</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135253965</v>
+        <v>135254335</v>
       </c>
       <c r="B17" t="n">
         <v>79373</v>
@@ -2265,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597732</v>
+        <v>597680</v>
       </c>
       <c r="R17" t="n">
-        <v>7071814</v>
+        <v>7071698</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2310,7 +2390,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2334,10 +2414,15 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254335</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135254335</v>
+        <v>135254748</v>
       </c>
       <c r="B18" t="n">
         <v>79373</v>
@@ -2372,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597680</v>
+        <v>597695</v>
       </c>
       <c r="R18" t="n">
-        <v>7071698</v>
+        <v>7071733</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2407,7 +2492,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2417,7 +2502,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2432,19 +2517,24 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254748</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135254748</v>
+        <v>135254797</v>
       </c>
       <c r="B19" t="n">
         <v>79373</v>
@@ -2479,13 +2569,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597695</v>
+        <v>597759</v>
       </c>
       <c r="R19" t="n">
-        <v>7071733</v>
+        <v>7071713</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2512,19 +2602,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>17:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2539,19 +2619,24 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254797</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135254797</v>
+        <v>135254865</v>
       </c>
       <c r="B20" t="n">
         <v>79373</v>
@@ -2586,13 +2671,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597759</v>
+        <v>597681</v>
       </c>
       <c r="R20" t="n">
-        <v>7071713</v>
+        <v>7071663</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2619,9 +2704,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2636,19 +2731,24 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254865</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135254865</v>
+        <v>135254896</v>
       </c>
       <c r="B21" t="n">
         <v>79373</v>
@@ -2683,10 +2783,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597681</v>
+        <v>597697</v>
       </c>
       <c r="R21" t="n">
-        <v>7071663</v>
+        <v>7071651</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2718,7 +2818,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2728,7 +2828,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2752,10 +2852,15 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254896</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135254896</v>
+        <v>135254907</v>
       </c>
       <c r="B22" t="n">
         <v>79373</v>
@@ -2790,10 +2895,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597697</v>
+        <v>597691</v>
       </c>
       <c r="R22" t="n">
-        <v>7071651</v>
+        <v>7071625</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2825,7 +2930,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2835,7 +2940,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2850,19 +2955,24 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254907</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135254907</v>
+        <v>135255150</v>
       </c>
       <c r="B23" t="n">
         <v>79373</v>
@@ -2897,10 +3007,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597691</v>
+        <v>597738</v>
       </c>
       <c r="R23" t="n">
-        <v>7071625</v>
+        <v>7071628</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2932,7 +3042,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2942,7 +3052,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2957,19 +3067,24 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255150</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135255150</v>
+        <v>135255347</v>
       </c>
       <c r="B24" t="n">
         <v>79373</v>
@@ -3004,10 +3119,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597738</v>
+        <v>597781</v>
       </c>
       <c r="R24" t="n">
-        <v>7071628</v>
+        <v>7071649</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3039,7 +3154,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3049,7 +3164,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3073,10 +3188,15 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255347</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135255347</v>
+        <v>135255503</v>
       </c>
       <c r="B25" t="n">
         <v>79373</v>
@@ -3111,10 +3231,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597781</v>
+        <v>597801</v>
       </c>
       <c r="R25" t="n">
-        <v>7071649</v>
+        <v>7071656</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3146,7 +3266,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3156,7 +3276,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3180,10 +3300,15 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255503</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135255503</v>
+        <v>135255763</v>
       </c>
       <c r="B26" t="n">
         <v>79373</v>
@@ -3218,10 +3343,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597801</v>
+        <v>597871</v>
       </c>
       <c r="R26" t="n">
-        <v>7071656</v>
+        <v>7071582</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3253,7 +3378,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3263,7 +3388,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3287,10 +3412,15 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255763</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135255763</v>
+        <v>135255809</v>
       </c>
       <c r="B27" t="n">
         <v>79373</v>
@@ -3325,10 +3455,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597871</v>
+        <v>597883</v>
       </c>
       <c r="R27" t="n">
-        <v>7071582</v>
+        <v>7071561</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3360,7 +3490,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3370,7 +3500,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3394,10 +3524,15 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255809</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135255809</v>
+        <v>135256006</v>
       </c>
       <c r="B28" t="n">
         <v>79373</v>
@@ -3432,10 +3567,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>597883</v>
+        <v>597907</v>
       </c>
       <c r="R28" t="n">
-        <v>7071561</v>
+        <v>7071543</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3467,7 +3602,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3477,7 +3612,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3492,19 +3627,24 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135256006</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135256006</v>
+        <v>135261206</v>
       </c>
       <c r="B29" t="n">
         <v>79373</v>
@@ -3533,19 +3673,22 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>597907</v>
+        <v>597650</v>
       </c>
       <c r="R29" t="n">
-        <v>7071543</v>
+        <v>7071766</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3574,7 +3717,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3584,7 +3727,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3593,25 +3736,46 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261206</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135261206</v>
+        <v>135261208</v>
       </c>
       <c r="B30" t="n">
         <v>79373</v>
@@ -3640,19 +3804,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>597650</v>
+        <v>597686</v>
       </c>
       <c r="R30" t="n">
-        <v>7071766</v>
+        <v>7071732</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3684,7 +3845,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3694,7 +3855,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3703,24 +3864,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3734,10 +3879,15 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261208</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135261208</v>
+        <v>135261209</v>
       </c>
       <c r="B31" t="n">
         <v>79373</v>
@@ -3772,10 +3922,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>597686</v>
+        <v>597692</v>
       </c>
       <c r="R31" t="n">
-        <v>7071732</v>
+        <v>7071677</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3807,7 +3957,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3817,7 +3967,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3841,10 +3991,15 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261209</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135261209</v>
+        <v>135261211</v>
       </c>
       <c r="B32" t="n">
         <v>79373</v>
@@ -3879,10 +4034,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>597692</v>
+        <v>597775</v>
       </c>
       <c r="R32" t="n">
-        <v>7071677</v>
+        <v>7071632</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3914,7 +4069,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3924,7 +4079,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3948,10 +4103,15 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261211</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135261211</v>
+        <v>135261212</v>
       </c>
       <c r="B33" t="n">
         <v>79373</v>
@@ -3986,10 +4146,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>597775</v>
+        <v>597811</v>
       </c>
       <c r="R33" t="n">
-        <v>7071632</v>
+        <v>7071636</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4021,7 +4181,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4031,7 +4191,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4055,10 +4215,15 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261212</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135261212</v>
+        <v>135277134</v>
       </c>
       <c r="B34" t="n">
         <v>79373</v>
@@ -4089,17 +4254,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>597811</v>
+        <v>597690</v>
       </c>
       <c r="R34" t="n">
-        <v>7071636</v>
+        <v>7071889</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4128,7 +4293,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4138,7 +4303,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4153,63 +4318,65 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277134</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135261476</v>
+        <v>135277128</v>
       </c>
       <c r="B35" t="n">
-        <v>79373</v>
+        <v>79397</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>597705</v>
+        <v>597652</v>
       </c>
       <c r="R35" t="n">
-        <v>7071935</v>
+        <v>7072022</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4238,7 +4405,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4248,7 +4415,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4257,85 +4424,71 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277128</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135261480</v>
+        <v>135185455</v>
       </c>
       <c r="B36" t="n">
-        <v>79373</v>
+        <v>78776</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>597757</v>
+        <v>597723</v>
       </c>
       <c r="R36" t="n">
-        <v>7071733</v>
+        <v>7071638</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4359,22 +4512,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>17:27</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>17:27</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4383,82 +4526,71 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135185455</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135277134</v>
+        <v>135253692</v>
       </c>
       <c r="B37" t="n">
-        <v>79373</v>
+        <v>83358</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>597690</v>
+        <v>597718</v>
       </c>
       <c r="R37" t="n">
-        <v>7071889</v>
+        <v>7071826</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4485,19 +4617,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4512,44 +4634,49 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135253692</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135277128</v>
+        <v>135277130</v>
       </c>
       <c r="B38" t="n">
-        <v>79397</v>
+        <v>83358</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6434</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4559,10 +4686,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>597652</v>
+        <v>597672</v>
       </c>
       <c r="R38" t="n">
-        <v>7072022</v>
+        <v>7072025</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4594,7 +4721,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4604,7 +4731,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4628,13 +4755,18 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277130</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135185455</v>
+        <v>135277135</v>
       </c>
       <c r="B39" t="n">
-        <v>78776</v>
+        <v>83358</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4642,37 +4774,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>597723</v>
+        <v>597696</v>
       </c>
       <c r="R39" t="n">
-        <v>7071638</v>
+        <v>7071877</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4696,12 +4828,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4716,22 +4858,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277135</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135253692</v>
+        <v>111802223</v>
       </c>
       <c r="B40" t="n">
-        <v>83358</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4739,37 +4886,40 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Kullberg, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>597718</v>
+        <v>597726</v>
       </c>
       <c r="R40" t="n">
-        <v>7071826</v>
+        <v>7071643</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4793,12 +4943,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4807,28 +4957,34 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111802223</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135277130</v>
+        <v>135257132</v>
       </c>
       <c r="B41" t="n">
-        <v>83358</v>
+        <v>79130</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4836,37 +4992,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>597672</v>
+        <v>597810</v>
       </c>
       <c r="R41" t="n">
-        <v>7072025</v>
+        <v>7071731</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4893,19 +5049,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:36</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4920,22 +5066,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135257132</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135277135</v>
+        <v>135257174</v>
       </c>
       <c r="B42" t="n">
-        <v>83358</v>
+        <v>79130</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4943,37 +5094,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>597696</v>
+        <v>597800</v>
       </c>
       <c r="R42" t="n">
-        <v>7071877</v>
+        <v>7071779</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5000,19 +5151,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>16:33</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>16:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5027,22 +5168,27 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135257174</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>111802223</v>
+        <v>135185445</v>
       </c>
       <c r="B43" t="n">
-        <v>79084</v>
+        <v>79992</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5050,40 +5196,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>597726</v>
+        <v>597724</v>
       </c>
       <c r="R43" t="n">
-        <v>7071643</v>
+        <v>7071639</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5107,12 +5250,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5121,67 +5264,71 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135185445</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135257132</v>
+        <v>135261207</v>
       </c>
       <c r="B44" t="n">
-        <v>79130</v>
+        <v>80492</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>597810</v>
+        <v>597651</v>
       </c>
       <c r="R44" t="n">
-        <v>7071731</v>
+        <v>7071773</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5208,9 +5355,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5225,57 +5382,67 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261207</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135257174</v>
+        <v>135253925</v>
       </c>
       <c r="B45" t="n">
-        <v>79130</v>
+        <v>57972</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>597800</v>
+        <v>597717</v>
       </c>
       <c r="R45" t="n">
-        <v>7071779</v>
+        <v>7071813</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5331,13 +5498,18 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135253925</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135261478</v>
+        <v>119352061</v>
       </c>
       <c r="B46" t="n">
-        <v>79130</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5345,37 +5517,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>597690</v>
+        <v>597652</v>
       </c>
       <c r="R46" t="n">
-        <v>7071824</v>
+        <v>7071974</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5399,22 +5576,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5429,22 +5606,27 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119352061</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135185445</v>
+        <v>135185510</v>
       </c>
       <c r="B47" t="n">
-        <v>79992</v>
+        <v>57975</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5452,34 +5634,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>597724</v>
+        <v>597653</v>
       </c>
       <c r="R47" t="n">
-        <v>7071639</v>
+        <v>7071687</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5514,6 +5701,11 @@
           <t>2026-07-16</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5535,51 +5727,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135185510</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135261207</v>
+        <v>135185592</v>
       </c>
       <c r="B48" t="n">
-        <v>80492</v>
+        <v>57975</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>597651</v>
+        <v>597662</v>
       </c>
       <c r="R48" t="n">
-        <v>7071773</v>
+        <v>7071777</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5603,22 +5805,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>17:01</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>17:01</t>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5633,39 +5830,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135185592</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135253925</v>
+        <v>135252357</v>
       </c>
       <c r="B49" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5676,7 +5878,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5685,13 +5887,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>597717</v>
+        <v>597647</v>
       </c>
       <c r="R49" t="n">
-        <v>7071813</v>
+        <v>7072042</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5718,9 +5920,24 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5735,22 +5952,27 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252357</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119352061</v>
+        <v>135252502</v>
       </c>
       <c r="B50" t="n">
-        <v>57953</v>
+        <v>57975</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5787,10 +6009,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>597652</v>
+        <v>597650</v>
       </c>
       <c r="R50" t="n">
-        <v>7071974</v>
+        <v>7071996</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5817,22 +6039,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5856,10 +6083,15 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252502</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135185510</v>
+        <v>135252549</v>
       </c>
       <c r="B51" t="n">
         <v>57975</v>
@@ -5890,7 +6122,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5899,13 +6131,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>597653</v>
+        <v>597648</v>
       </c>
       <c r="R51" t="n">
-        <v>7071687</v>
+        <v>7071988</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5929,17 +6161,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5954,19 +6196,24 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252549</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135185592</v>
+        <v>135252575</v>
       </c>
       <c r="B52" t="n">
         <v>57975</v>
@@ -6006,13 +6253,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>597662</v>
+        <v>597654</v>
       </c>
       <c r="R52" t="n">
-        <v>7071777</v>
+        <v>7071984</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6036,17 +6283,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6061,19 +6318,24 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252575</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135252357</v>
+        <v>135252599</v>
       </c>
       <c r="B53" t="n">
         <v>57975</v>
@@ -6104,7 +6366,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6113,10 +6375,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>597647</v>
+        <v>597652</v>
       </c>
       <c r="R53" t="n">
-        <v>7072042</v>
+        <v>7071981</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6148,7 +6410,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6158,12 +6420,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6178,19 +6440,24 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252599</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135252502</v>
+        <v>135252771</v>
       </c>
       <c r="B54" t="n">
         <v>57975</v>
@@ -6230,10 +6497,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>597650</v>
+        <v>597694</v>
       </c>
       <c r="R54" t="n">
-        <v>7071996</v>
+        <v>7071960</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6265,7 +6532,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6275,7 +6542,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -6304,10 +6571,15 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252771</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135252549</v>
+        <v>135253769</v>
       </c>
       <c r="B55" t="n">
         <v>57975</v>
@@ -6347,10 +6619,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>597648</v>
+        <v>597732</v>
       </c>
       <c r="R55" t="n">
-        <v>7071988</v>
+        <v>7071814</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6382,7 +6654,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6392,7 +6664,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -6412,50 +6684,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135253769</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135252575</v>
+        <v>135254862</v>
       </c>
       <c r="B56" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6464,13 +6746,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>597654</v>
+        <v>597826</v>
       </c>
       <c r="R56" t="n">
-        <v>7071984</v>
+        <v>7071713</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6497,24 +6779,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6529,62 +6796,62 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254862</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135252599</v>
+        <v>135277138</v>
       </c>
       <c r="B57" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>597652</v>
+        <v>597826</v>
       </c>
       <c r="R57" t="n">
-        <v>7071981</v>
+        <v>7071709</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6616,7 +6883,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6626,12 +6893,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6646,22 +6908,27 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277138</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135252771</v>
+        <v>135185420</v>
       </c>
       <c r="B58" t="n">
-        <v>57975</v>
+        <v>58136</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6669,27 +6936,27 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6698,13 +6965,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>597694</v>
+        <v>597731</v>
       </c>
       <c r="R58" t="n">
-        <v>7071960</v>
+        <v>7071656</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6728,27 +6995,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>15:55</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6763,22 +7015,27 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135185420</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135253769</v>
+        <v>135257192</v>
       </c>
       <c r="B59" t="n">
-        <v>57975</v>
+        <v>58136</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6786,27 +7043,27 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6815,13 +7072,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>597732</v>
+        <v>597798</v>
       </c>
       <c r="R59" t="n">
-        <v>7071814</v>
+        <v>7071782</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6848,24 +7105,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>16:36</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6880,22 +7122,27 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135257192</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135254862</v>
+        <v>135277129</v>
       </c>
       <c r="B60" t="n">
-        <v>57162</v>
+        <v>8449</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6903,47 +7150,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>597826</v>
+        <v>597655</v>
       </c>
       <c r="R60" t="n">
-        <v>7071713</v>
+        <v>7072023</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6970,9 +7207,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6987,22 +7234,27 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277129</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135277138</v>
+        <v>135252291</v>
       </c>
       <c r="B61" t="n">
-        <v>57162</v>
+        <v>99112</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7010,37 +7262,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>597826</v>
+        <v>597625</v>
       </c>
       <c r="R61" t="n">
-        <v>7071709</v>
+        <v>7072015</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7067,19 +7319,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>17:32</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>17:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7094,62 +7336,62 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252291</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135185420</v>
+        <v>135253119</v>
       </c>
       <c r="B62" t="n">
-        <v>58136</v>
+        <v>98060</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>597731</v>
+        <v>597685</v>
       </c>
       <c r="R62" t="n">
-        <v>7071656</v>
+        <v>7071950</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7176,12 +7418,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7205,56 +7447,56 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135253119</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135257192</v>
+        <v>135261205</v>
       </c>
       <c r="B63" t="n">
-        <v>58136</v>
+        <v>98060</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>597798</v>
+        <v>597679</v>
       </c>
       <c r="R63" t="n">
-        <v>7071782</v>
+        <v>7071921</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7281,9 +7523,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7298,57 +7550,62 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261205</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135277129</v>
+        <v>135254080</v>
       </c>
       <c r="B64" t="n">
-        <v>8449</v>
+        <v>79131</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106554</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>597655</v>
+        <v>597664</v>
       </c>
       <c r="R64" t="n">
-        <v>7072023</v>
+        <v>7071792</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7380,7 +7637,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7390,7 +7647,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7405,44 +7662,49 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254080</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135252291</v>
+        <v>135254180</v>
       </c>
       <c r="B65" t="n">
-        <v>99112</v>
+        <v>79131</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7452,13 +7714,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>597625</v>
+        <v>597732</v>
       </c>
       <c r="R65" t="n">
-        <v>7072015</v>
+        <v>7071814</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7485,9 +7747,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7502,44 +7774,49 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254180</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135253119</v>
+        <v>135254875</v>
       </c>
       <c r="B66" t="n">
-        <v>98060</v>
+        <v>79131</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7549,13 +7826,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>597685</v>
+        <v>597688</v>
       </c>
       <c r="R66" t="n">
-        <v>7071950</v>
+        <v>7071656</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7582,9 +7859,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7599,60 +7886,65 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254875</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135261205</v>
+        <v>135255066</v>
       </c>
       <c r="B67" t="n">
-        <v>98060</v>
+        <v>79131</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>597679</v>
+        <v>597711</v>
       </c>
       <c r="R67" t="n">
-        <v>7071921</v>
+        <v>7071632</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7681,7 +7973,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7691,7 +7983,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7706,60 +7998,65 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255066</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135261477</v>
+        <v>135255116</v>
       </c>
       <c r="B68" t="n">
-        <v>98060</v>
+        <v>79131</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>597690</v>
+        <v>597691</v>
       </c>
       <c r="R68" t="n">
-        <v>7071861</v>
+        <v>7071625</v>
       </c>
       <c r="S68" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7788,7 +8085,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7798,7 +8095,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7813,19 +8110,24 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255116</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135254080</v>
+        <v>135255849</v>
       </c>
       <c r="B69" t="n">
         <v>79131</v>
@@ -7860,10 +8162,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>597664</v>
+        <v>597894</v>
       </c>
       <c r="R69" t="n">
-        <v>7071792</v>
+        <v>7071564</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7895,7 +8197,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7905,7 +8207,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7929,10 +8231,15 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255849</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135254180</v>
+        <v>135255990</v>
       </c>
       <c r="B70" t="n">
         <v>79131</v>
@@ -7963,14 +8270,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>597732</v>
+        <v>597890</v>
       </c>
       <c r="R70" t="n">
-        <v>7071814</v>
+        <v>7071513</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8002,7 +8309,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8012,7 +8319,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8027,19 +8334,24 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255990</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135254875</v>
+        <v>135256152</v>
       </c>
       <c r="B71" t="n">
         <v>79131</v>
@@ -8074,10 +8386,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>597688</v>
+        <v>597907</v>
       </c>
       <c r="R71" t="n">
-        <v>7071656</v>
+        <v>7071543</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8109,7 +8421,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8119,7 +8431,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8134,22 +8446,27 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135256152</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135255066</v>
+        <v>135277126</v>
       </c>
       <c r="B72" t="n">
-        <v>79131</v>
+        <v>79963</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8157,34 +8474,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>597711</v>
+        <v>597628</v>
       </c>
       <c r="R72" t="n">
-        <v>7071632</v>
+        <v>7072050</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8216,7 +8533,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8226,7 +8543,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8241,659 +8558,95 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>135255116</v>
-      </c>
-      <c r="B73" t="n">
-        <v>79131</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>597691</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7071625</v>
-      </c>
-      <c r="S73" t="n">
-        <v>10</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>17:47</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>17:47</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Johanna Liljegren</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Johanna Liljegren</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>135255849</v>
-      </c>
-      <c r="B74" t="n">
-        <v>79131</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>597894</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7071564</v>
-      </c>
-      <c r="S74" t="n">
-        <v>10</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>18:19</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>18:19</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>135255990</v>
-      </c>
-      <c r="B75" t="n">
-        <v>79131</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>597890</v>
-      </c>
-      <c r="R75" t="n">
-        <v>7071513</v>
-      </c>
-      <c r="S75" t="n">
-        <v>10</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>18:23</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>18:23</t>
-        </is>
-      </c>
-      <c r="AD75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>135256152</v>
-      </c>
-      <c r="B76" t="n">
-        <v>79131</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>597907</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7071543</v>
-      </c>
-      <c r="S76" t="n">
-        <v>10</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Johanna Liljegren</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Johanna Liljegren</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>135261479</v>
-      </c>
-      <c r="B77" t="n">
-        <v>79131</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Lill-kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q77" t="n">
-        <v>597679</v>
-      </c>
-      <c r="R77" t="n">
-        <v>7071753</v>
-      </c>
-      <c r="S77" t="n">
-        <v>3</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>17:13</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>17:13</t>
-        </is>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT77" t="inlineStr"/>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>135277126</v>
-      </c>
-      <c r="B78" t="n">
-        <v>79963</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
-        </is>
-      </c>
-      <c r="Q78" t="n">
-        <v>597628</v>
-      </c>
-      <c r="R78" t="n">
-        <v>7072050</v>
-      </c>
-      <c r="S78" t="n">
-        <v>10</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AD78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT78" t="inlineStr"/>
-      <c r="AW78" t="inlineStr">
-        <is>
-          <t>Anne-Katrin Würthele</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>Anne-Katrin Würthele</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277126</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28113-2026 artfynd.xlsx
+++ b/artfynd/A 28113-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ72"/>
+  <dimension ref="A1:AZ78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135185577</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135254148</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135252944</v>
       </c>
       <c r="B4" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135253662</v>
       </c>
       <c r="B5" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,51 +1098,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111802213</v>
+        <v>135261475</v>
       </c>
       <c r="B6" t="n">
-        <v>93213</v>
+        <v>92016</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597737</v>
+        <v>597668</v>
       </c>
       <c r="R6" t="n">
-        <v>7071647</v>
+        <v>7071982</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1166,12 +1163,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,56 +1187,55 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111802213</t>
+          <t>https://artportalen.se/Sighting/135261475</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111802220</v>
+        <v>111802213</v>
       </c>
       <c r="B7" t="n">
-        <v>93197</v>
+        <v>93213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1242,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597715</v>
+        <v>597737</v>
       </c>
       <c r="R7" t="n">
-        <v>7071639</v>
+        <v>7071647</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1304,16 +1310,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111802220</t>
+          <t>https://artportalen.se/Sighting/111802213</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135254269</v>
+        <v>111802220</v>
       </c>
       <c r="B8" t="n">
-        <v>93271</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1339,19 +1345,22 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Kullberg, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597670</v>
+        <v>597715</v>
       </c>
       <c r="R8" t="n">
-        <v>7071721</v>
+        <v>7071639</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1375,22 +1384,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>17:02</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:02</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,33 +1398,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254269</t>
+          <t>https://artportalen.se/Sighting/111802220</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135254935</v>
+        <v>135254269</v>
       </c>
       <c r="B9" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597691</v>
+        <v>597670</v>
       </c>
       <c r="R9" t="n">
-        <v>7071625</v>
+        <v>7071721</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1517,27 +1517,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254935</t>
+          <t>https://artportalen.se/Sighting/135254269</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135254970</v>
+        <v>135254935</v>
       </c>
       <c r="B10" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597704</v>
+        <v>597691</v>
       </c>
       <c r="R10" t="n">
-        <v>7071626</v>
+        <v>7071625</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,27 +1629,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254970</t>
+          <t>https://artportalen.se/Sighting/135254935</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135261210</v>
+        <v>135254970</v>
       </c>
       <c r="B11" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,31 +1674,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597710</v>
+        <v>597704</v>
       </c>
       <c r="R11" t="n">
-        <v>7071633</v>
+        <v>7071626</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1727,7 +1716,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1737,7 +1726,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,72 +1735,82 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261210</t>
+          <t>https://artportalen.se/Sighting/135254970</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135253005</v>
+        <v>135261210</v>
       </c>
       <c r="B12" t="n">
-        <v>91937</v>
+        <v>93313</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597700</v>
+        <v>597710</v>
       </c>
       <c r="R12" t="n">
-        <v>7071941</v>
+        <v>7071633</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1838,44 +1837,55 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253005</t>
+          <t>https://artportalen.se/Sighting/135261210</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135253624</v>
+        <v>135253005</v>
       </c>
       <c r="B13" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597702</v>
+        <v>597700</v>
       </c>
       <c r="R13" t="n">
-        <v>7071879</v>
+        <v>7071941</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1968,38 +1978,38 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253624</t>
+          <t>https://artportalen.se/Sighting/135253005</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135252916</v>
+        <v>135253624</v>
       </c>
       <c r="B14" t="n">
-        <v>79373</v>
+        <v>91979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2009,13 +2019,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597734</v>
+        <v>597702</v>
       </c>
       <c r="R14" t="n">
-        <v>7071921</v>
+        <v>7071879</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2042,19 +2052,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,27 +2069,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252916</t>
+          <t>https://artportalen.se/Sighting/135253624</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135253853</v>
+        <v>135252916</v>
       </c>
       <c r="B15" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597701</v>
+        <v>597734</v>
       </c>
       <c r="R15" t="n">
-        <v>7071820</v>
+        <v>7071921</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2181,27 +2181,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253853</t>
+          <t>https://artportalen.se/Sighting/135252916</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135253965</v>
+        <v>135253853</v>
       </c>
       <c r="B16" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597732</v>
+        <v>597701</v>
       </c>
       <c r="R16" t="n">
-        <v>7071814</v>
+        <v>7071820</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,27 +2293,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253965</t>
+          <t>https://artportalen.se/Sighting/135253853</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135254335</v>
+        <v>135253965</v>
       </c>
       <c r="B17" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597680</v>
+        <v>597732</v>
       </c>
       <c r="R17" t="n">
-        <v>7071698</v>
+        <v>7071814</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2416,16 +2416,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254335</t>
+          <t>https://artportalen.se/Sighting/135253965</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135254748</v>
+        <v>135254335</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597695</v>
+        <v>597680</v>
       </c>
       <c r="R18" t="n">
-        <v>7071733</v>
+        <v>7071698</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,27 +2517,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254748</t>
+          <t>https://artportalen.se/Sighting/135254335</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135254797</v>
+        <v>135254748</v>
       </c>
       <c r="B19" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2569,13 +2569,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597759</v>
+        <v>597695</v>
       </c>
       <c r="R19" t="n">
-        <v>7071713</v>
+        <v>7071733</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2602,9 +2602,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,27 +2629,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254797</t>
+          <t>https://artportalen.se/Sighting/135254748</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135254865</v>
+        <v>135254797</v>
       </c>
       <c r="B20" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2671,13 +2681,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597681</v>
+        <v>597759</v>
       </c>
       <c r="R20" t="n">
-        <v>7071663</v>
+        <v>7071713</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2704,19 +2714,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>17:33</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2731,27 +2731,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254865</t>
+          <t>https://artportalen.se/Sighting/135254797</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135254896</v>
+        <v>135254865</v>
       </c>
       <c r="B21" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2783,10 +2783,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597697</v>
+        <v>597681</v>
       </c>
       <c r="R21" t="n">
-        <v>7071651</v>
+        <v>7071663</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2854,16 +2854,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254896</t>
+          <t>https://artportalen.se/Sighting/135254865</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135254907</v>
+        <v>135254896</v>
       </c>
       <c r="B22" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,10 +2895,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597691</v>
+        <v>597697</v>
       </c>
       <c r="R22" t="n">
-        <v>7071625</v>
+        <v>7071651</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2955,27 +2955,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254907</t>
+          <t>https://artportalen.se/Sighting/135254896</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135255150</v>
+        <v>135254907</v>
       </c>
       <c r="B23" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3007,10 +3007,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597738</v>
+        <v>597691</v>
       </c>
       <c r="R23" t="n">
-        <v>7071628</v>
+        <v>7071625</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3067,27 +3067,27 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255150</t>
+          <t>https://artportalen.se/Sighting/135254907</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135255347</v>
+        <v>135255150</v>
       </c>
       <c r="B24" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597781</v>
+        <v>597738</v>
       </c>
       <c r="R24" t="n">
-        <v>7071649</v>
+        <v>7071628</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3190,16 +3190,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255347</t>
+          <t>https://artportalen.se/Sighting/135255150</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135255503</v>
+        <v>135255347</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597801</v>
+        <v>597781</v>
       </c>
       <c r="R25" t="n">
-        <v>7071656</v>
+        <v>7071649</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3302,16 +3302,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255503</t>
+          <t>https://artportalen.se/Sighting/135255347</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135255763</v>
+        <v>135255503</v>
       </c>
       <c r="B26" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597871</v>
+        <v>597801</v>
       </c>
       <c r="R26" t="n">
-        <v>7071582</v>
+        <v>7071656</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3414,16 +3414,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255763</t>
+          <t>https://artportalen.se/Sighting/135255503</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135255809</v>
+        <v>135255763</v>
       </c>
       <c r="B27" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597883</v>
+        <v>597871</v>
       </c>
       <c r="R27" t="n">
-        <v>7071561</v>
+        <v>7071582</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3526,16 +3526,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255809</t>
+          <t>https://artportalen.se/Sighting/135255763</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135256006</v>
+        <v>135255809</v>
       </c>
       <c r="B28" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>597907</v>
+        <v>597883</v>
       </c>
       <c r="R28" t="n">
-        <v>7071543</v>
+        <v>7071561</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3627,27 +3627,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135256006</t>
+          <t>https://artportalen.se/Sighting/135255809</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135261206</v>
+        <v>135256006</v>
       </c>
       <c r="B29" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3673,22 +3673,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>597650</v>
+        <v>597907</v>
       </c>
       <c r="R29" t="n">
-        <v>7071766</v>
+        <v>7071543</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3717,7 +3714,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3727,7 +3724,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3736,49 +3733,33 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261206</t>
+          <t>https://artportalen.se/Sighting/135256006</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135261208</v>
+        <v>135261206</v>
       </c>
       <c r="B30" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3804,16 +3785,19 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>597686</v>
+        <v>597650</v>
       </c>
       <c r="R30" t="n">
-        <v>7071732</v>
+        <v>7071766</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3845,7 +3829,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3855,7 +3839,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3864,8 +3848,24 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3881,16 +3881,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261208</t>
+          <t>https://artportalen.se/Sighting/135261206</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135261209</v>
+        <v>135261208</v>
       </c>
       <c r="B31" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>597692</v>
+        <v>597686</v>
       </c>
       <c r="R31" t="n">
-        <v>7071677</v>
+        <v>7071732</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3993,16 +3993,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261209</t>
+          <t>https://artportalen.se/Sighting/135261208</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135261211</v>
+        <v>135261209</v>
       </c>
       <c r="B32" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4034,10 +4034,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>597775</v>
+        <v>597692</v>
       </c>
       <c r="R32" t="n">
-        <v>7071632</v>
+        <v>7071677</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4105,16 +4105,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261211</t>
+          <t>https://artportalen.se/Sighting/135261209</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135261212</v>
+        <v>135261211</v>
       </c>
       <c r="B33" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4146,10 +4146,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>597811</v>
+        <v>597775</v>
       </c>
       <c r="R33" t="n">
-        <v>7071636</v>
+        <v>7071632</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4217,16 +4217,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261212</t>
+          <t>https://artportalen.se/Sighting/135261211</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135277134</v>
+        <v>135261212</v>
       </c>
       <c r="B34" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4254,17 +4254,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>597690</v>
+        <v>597811</v>
       </c>
       <c r="R34" t="n">
-        <v>7071889</v>
+        <v>7071636</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4318,65 +4318,68 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277134</t>
+          <t>https://artportalen.se/Sighting/135261212</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135277128</v>
+        <v>135261476</v>
       </c>
       <c r="B35" t="n">
-        <v>79397</v>
+        <v>79411</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>597652</v>
+        <v>597705</v>
       </c>
       <c r="R35" t="n">
-        <v>7072022</v>
+        <v>7071935</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4405,7 +4408,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4415,7 +4418,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4424,71 +4427,90 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277128</t>
+          <t>https://artportalen.se/Sighting/135261476</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135185455</v>
+        <v>135261480</v>
       </c>
       <c r="B36" t="n">
-        <v>78776</v>
+        <v>79411</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>597723</v>
+        <v>597757</v>
       </c>
       <c r="R36" t="n">
-        <v>7071638</v>
+        <v>7071733</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4512,12 +4534,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4526,71 +4558,87 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135185455</t>
+          <t>https://artportalen.se/Sighting/135261480</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135253692</v>
+        <v>135277134</v>
       </c>
       <c r="B37" t="n">
-        <v>83358</v>
+        <v>79411</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>597718</v>
+        <v>597690</v>
       </c>
       <c r="R37" t="n">
-        <v>7071826</v>
+        <v>7071889</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4617,9 +4665,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4634,49 +4692,49 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253692</t>
+          <t>https://artportalen.se/Sighting/135277134</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135277130</v>
+        <v>135277128</v>
       </c>
       <c r="B38" t="n">
-        <v>83358</v>
+        <v>79435</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6434</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4686,10 +4744,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>597672</v>
+        <v>597652</v>
       </c>
       <c r="R38" t="n">
-        <v>7072025</v>
+        <v>7072022</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4721,7 +4779,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4731,7 +4789,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4757,16 +4815,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277130</t>
+          <t>https://artportalen.se/Sighting/135277128</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135277135</v>
+        <v>135185455</v>
       </c>
       <c r="B39" t="n">
-        <v>83358</v>
+        <v>78814</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4774,37 +4832,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>597696</v>
+        <v>597723</v>
       </c>
       <c r="R39" t="n">
-        <v>7071877</v>
+        <v>7071638</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4828,22 +4886,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>16:33</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>16:33</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4858,27 +4906,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277135</t>
+          <t>https://artportalen.se/Sighting/135185455</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>111802223</v>
+        <v>135253692</v>
       </c>
       <c r="B40" t="n">
-        <v>79084</v>
+        <v>83398</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4886,40 +4934,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>597726</v>
+        <v>597718</v>
       </c>
       <c r="R40" t="n">
-        <v>7071643</v>
+        <v>7071826</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4943,12 +4988,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4957,34 +5002,33 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111802223</t>
+          <t>https://artportalen.se/Sighting/135253692</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135257132</v>
+        <v>135277130</v>
       </c>
       <c r="B41" t="n">
-        <v>79130</v>
+        <v>83398</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4992,37 +5036,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>597810</v>
+        <v>597672</v>
       </c>
       <c r="R41" t="n">
-        <v>7071731</v>
+        <v>7072025</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5049,9 +5093,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5066,27 +5120,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135257132</t>
+          <t>https://artportalen.se/Sighting/135277130</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135257174</v>
+        <v>135277135</v>
       </c>
       <c r="B42" t="n">
-        <v>79130</v>
+        <v>83398</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5094,37 +5148,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>597800</v>
+        <v>597696</v>
       </c>
       <c r="R42" t="n">
-        <v>7071779</v>
+        <v>7071877</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5151,9 +5205,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5168,27 +5232,27 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135257174</t>
+          <t>https://artportalen.se/Sighting/135277135</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135185445</v>
+        <v>111802223</v>
       </c>
       <c r="B43" t="n">
-        <v>79992</v>
+        <v>79084</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5196,37 +5260,40 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Kullberg, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>597724</v>
+        <v>597726</v>
       </c>
       <c r="R43" t="n">
-        <v>7071639</v>
+        <v>7071643</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5250,12 +5317,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5264,71 +5331,72 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135185445</t>
+          <t>https://artportalen.se/Sighting/111802223</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135261207</v>
+        <v>135257132</v>
       </c>
       <c r="B44" t="n">
-        <v>80492</v>
+        <v>79168</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>597651</v>
+        <v>597810</v>
       </c>
       <c r="R44" t="n">
-        <v>7071773</v>
+        <v>7071731</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5355,19 +5423,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>17:01</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>17:01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5382,67 +5440,62 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261207</t>
+          <t>https://artportalen.se/Sighting/135257132</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135253925</v>
+        <v>135257174</v>
       </c>
       <c r="B45" t="n">
-        <v>57972</v>
+        <v>79168</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>597717</v>
+        <v>597800</v>
       </c>
       <c r="R45" t="n">
-        <v>7071813</v>
+        <v>7071779</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5500,16 +5553,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253925</t>
+          <t>https://artportalen.se/Sighting/135257174</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119352061</v>
+        <v>135261478</v>
       </c>
       <c r="B46" t="n">
-        <v>57953</v>
+        <v>79168</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5517,42 +5570,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>597652</v>
+        <v>597690</v>
       </c>
       <c r="R46" t="n">
-        <v>7071974</v>
+        <v>7071824</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5576,22 +5624,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5606,27 +5654,27 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119352061</t>
+          <t>https://artportalen.se/Sighting/135261478</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135185510</v>
+        <v>135185445</v>
       </c>
       <c r="B47" t="n">
-        <v>57975</v>
+        <v>80030</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5634,39 +5682,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>597653</v>
+        <v>597724</v>
       </c>
       <c r="R47" t="n">
-        <v>7071687</v>
+        <v>7071639</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5701,11 +5744,6 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5729,59 +5767,54 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135185510</t>
+          <t>https://artportalen.se/Sighting/135185445</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135185592</v>
+        <v>135261207</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>80530</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>597662</v>
+        <v>597651</v>
       </c>
       <c r="R48" t="n">
-        <v>7071777</v>
+        <v>7071773</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5805,17 +5838,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5830,44 +5868,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135185592</t>
+          <t>https://artportalen.se/Sighting/135261207</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135252357</v>
+        <v>135253925</v>
       </c>
       <c r="B49" t="n">
-        <v>57975</v>
+        <v>57977</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5878,7 +5916,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5887,13 +5925,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>597647</v>
+        <v>597717</v>
       </c>
       <c r="R49" t="n">
-        <v>7072042</v>
+        <v>7071813</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5920,24 +5958,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5952,27 +5975,27 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252357</t>
+          <t>https://artportalen.se/Sighting/135253925</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135252502</v>
+        <v>119352061</v>
       </c>
       <c r="B50" t="n">
-        <v>57975</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6009,10 +6032,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>597650</v>
+        <v>597652</v>
       </c>
       <c r="R50" t="n">
-        <v>7071996</v>
+        <v>7071974</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6039,27 +6062,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6085,16 +6103,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252502</t>
+          <t>https://artportalen.se/Sighting/119352061</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135252549</v>
+        <v>135185510</v>
       </c>
       <c r="B51" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6122,7 +6140,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6131,13 +6149,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>597648</v>
+        <v>597653</v>
       </c>
       <c r="R51" t="n">
-        <v>7071988</v>
+        <v>7071687</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6161,27 +6179,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6196,27 +6204,27 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252549</t>
+          <t>https://artportalen.se/Sighting/135185510</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135252575</v>
+        <v>135185592</v>
       </c>
       <c r="B52" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6253,13 +6261,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>597654</v>
+        <v>597662</v>
       </c>
       <c r="R52" t="n">
-        <v>7071984</v>
+        <v>7071777</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6283,27 +6291,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:41</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:41</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6318,27 +6316,27 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252575</t>
+          <t>https://artportalen.se/Sighting/135185592</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135252599</v>
+        <v>135252357</v>
       </c>
       <c r="B53" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6366,7 +6364,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6375,10 +6373,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>597652</v>
+        <v>597647</v>
       </c>
       <c r="R53" t="n">
-        <v>7071981</v>
+        <v>7072042</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6410,7 +6408,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6420,12 +6418,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6440,27 +6438,27 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252599</t>
+          <t>https://artportalen.se/Sighting/135252357</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135252771</v>
+        <v>135252502</v>
       </c>
       <c r="B54" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6497,10 +6495,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>597694</v>
+        <v>597650</v>
       </c>
       <c r="R54" t="n">
-        <v>7071960</v>
+        <v>7071996</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6532,7 +6530,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6542,7 +6540,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -6573,16 +6571,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252771</t>
+          <t>https://artportalen.se/Sighting/135252502</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135253769</v>
+        <v>135252549</v>
       </c>
       <c r="B55" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6619,10 +6617,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>597732</v>
+        <v>597648</v>
       </c>
       <c r="R55" t="n">
-        <v>7071814</v>
+        <v>7071988</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6654,7 +6652,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6664,7 +6662,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -6684,60 +6682,55 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253769</t>
+          <t>https://artportalen.se/Sighting/135252549</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135254862</v>
+        <v>135252575</v>
       </c>
       <c r="B56" t="n">
-        <v>57162</v>
+        <v>57980</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6746,13 +6739,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>597826</v>
+        <v>597654</v>
       </c>
       <c r="R56" t="n">
-        <v>7071713</v>
+        <v>7071984</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6779,9 +6772,24 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6796,62 +6804,67 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254862</t>
+          <t>https://artportalen.se/Sighting/135252575</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135277138</v>
+        <v>135252599</v>
       </c>
       <c r="B57" t="n">
-        <v>57162</v>
+        <v>57980</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>597826</v>
+        <v>597652</v>
       </c>
       <c r="R57" t="n">
-        <v>7071709</v>
+        <v>7071981</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6883,7 +6896,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6893,7 +6906,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6908,27 +6926,27 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277138</t>
+          <t>https://artportalen.se/Sighting/135252599</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135185420</v>
+        <v>135252771</v>
       </c>
       <c r="B58" t="n">
-        <v>58136</v>
+        <v>57980</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6936,27 +6954,27 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6965,13 +6983,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>597731</v>
+        <v>597694</v>
       </c>
       <c r="R58" t="n">
-        <v>7071656</v>
+        <v>7071960</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6995,12 +7013,27 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7015,27 +7048,27 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135185420</t>
+          <t>https://artportalen.se/Sighting/135252771</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135257192</v>
+        <v>135253769</v>
       </c>
       <c r="B59" t="n">
-        <v>58136</v>
+        <v>57980</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7043,27 +7076,27 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7072,13 +7105,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>597798</v>
+        <v>597732</v>
       </c>
       <c r="R59" t="n">
-        <v>7071782</v>
+        <v>7071814</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7105,9 +7138,24 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7122,27 +7170,27 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135257192</t>
+          <t>https://artportalen.se/Sighting/135253769</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135277129</v>
+        <v>135254862</v>
       </c>
       <c r="B60" t="n">
-        <v>8449</v>
+        <v>57167</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7150,37 +7198,47 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>597655</v>
+        <v>597826</v>
       </c>
       <c r="R60" t="n">
-        <v>7072023</v>
+        <v>7071713</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7207,19 +7265,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>15:32</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7234,27 +7282,27 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277129</t>
+          <t>https://artportalen.se/Sighting/135254862</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135252291</v>
+        <v>135277138</v>
       </c>
       <c r="B61" t="n">
-        <v>99112</v>
+        <v>57167</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7262,37 +7310,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>597625</v>
+        <v>597826</v>
       </c>
       <c r="R61" t="n">
-        <v>7072015</v>
+        <v>7071709</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7319,9 +7367,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7336,62 +7394,67 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252291</t>
+          <t>https://artportalen.se/Sighting/135277138</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135253119</v>
+        <v>135185420</v>
       </c>
       <c r="B62" t="n">
-        <v>98060</v>
+        <v>58141</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>597685</v>
+        <v>597731</v>
       </c>
       <c r="R62" t="n">
-        <v>7071950</v>
+        <v>7071656</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7418,12 +7481,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7449,54 +7512,59 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253119</t>
+          <t>https://artportalen.se/Sighting/135185420</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135261205</v>
+        <v>135257192</v>
       </c>
       <c r="B63" t="n">
-        <v>98060</v>
+        <v>58141</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>597679</v>
+        <v>597798</v>
       </c>
       <c r="R63" t="n">
-        <v>7071921</v>
+        <v>7071782</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7523,19 +7591,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>16:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7550,62 +7608,62 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261205</t>
+          <t>https://artportalen.se/Sighting/135257192</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135254080</v>
+        <v>135277129</v>
       </c>
       <c r="B64" t="n">
-        <v>79131</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>106554</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>597664</v>
+        <v>597655</v>
       </c>
       <c r="R64" t="n">
-        <v>7071792</v>
+        <v>7072023</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7637,7 +7695,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7647,7 +7705,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7662,49 +7720,49 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254080</t>
+          <t>https://artportalen.se/Sighting/135277129</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135254180</v>
+        <v>135252291</v>
       </c>
       <c r="B65" t="n">
-        <v>79131</v>
+        <v>99159</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7714,13 +7772,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>597732</v>
+        <v>597625</v>
       </c>
       <c r="R65" t="n">
-        <v>7071814</v>
+        <v>7072015</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7747,19 +7805,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>16:55</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7774,49 +7822,49 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254180</t>
+          <t>https://artportalen.se/Sighting/135252291</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135254875</v>
+        <v>135253119</v>
       </c>
       <c r="B66" t="n">
-        <v>79131</v>
+        <v>98104</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7826,13 +7874,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>597688</v>
+        <v>597685</v>
       </c>
       <c r="R66" t="n">
-        <v>7071656</v>
+        <v>7071950</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7859,19 +7907,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>17:35</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7886,65 +7924,65 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254875</t>
+          <t>https://artportalen.se/Sighting/135253119</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135255066</v>
+        <v>135261205</v>
       </c>
       <c r="B67" t="n">
-        <v>79131</v>
+        <v>98104</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>597711</v>
+        <v>597679</v>
       </c>
       <c r="R67" t="n">
-        <v>7071632</v>
+        <v>7071921</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7973,7 +8011,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7983,7 +8021,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7998,65 +8036,65 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255066</t>
+          <t>https://artportalen.se/Sighting/135261205</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135255116</v>
+        <v>135261477</v>
       </c>
       <c r="B68" t="n">
-        <v>79131</v>
+        <v>98104</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>597691</v>
+        <v>597690</v>
       </c>
       <c r="R68" t="n">
-        <v>7071625</v>
+        <v>7071861</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8085,7 +8123,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8095,7 +8133,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8110,27 +8148,27 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255116</t>
+          <t>https://artportalen.se/Sighting/135261477</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135255849</v>
+        <v>135254080</v>
       </c>
       <c r="B69" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8162,10 +8200,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>597894</v>
+        <v>597664</v>
       </c>
       <c r="R69" t="n">
-        <v>7071564</v>
+        <v>7071792</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8197,7 +8235,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8207,7 +8245,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8233,16 +8271,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255849</t>
+          <t>https://artportalen.se/Sighting/135254080</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135255990</v>
+        <v>135254180</v>
       </c>
       <c r="B70" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8270,14 +8308,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>597890</v>
+        <v>597732</v>
       </c>
       <c r="R70" t="n">
-        <v>7071513</v>
+        <v>7071814</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8309,7 +8347,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8319,7 +8357,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8334,27 +8372,27 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255990</t>
+          <t>https://artportalen.se/Sighting/135254180</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135256152</v>
+        <v>135254875</v>
       </c>
       <c r="B71" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8386,10 +8424,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>597907</v>
+        <v>597688</v>
       </c>
       <c r="R71" t="n">
-        <v>7071543</v>
+        <v>7071656</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8421,7 +8459,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8431,7 +8469,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8446,27 +8484,27 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135256152</t>
+          <t>https://artportalen.se/Sighting/135254875</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135277126</v>
+        <v>135255066</v>
       </c>
       <c r="B72" t="n">
-        <v>79963</v>
+        <v>79169</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8474,34 +8512,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>597628</v>
+        <v>597711</v>
       </c>
       <c r="R72" t="n">
-        <v>7072050</v>
+        <v>7071632</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8533,7 +8571,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8543,7 +8581,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8558,16 +8596,688 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255066</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135255116</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79169</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>597691</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7071625</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255116</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135255849</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79169</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>597894</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7071564</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255849</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135255990</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79169</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>597890</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7071513</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255990</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135256152</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79169</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>597907</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7071543</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135256152</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135261479</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79169</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>597679</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7071753</v>
+      </c>
+      <c r="S77" t="n">
+        <v>3</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261479</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135277126</v>
+      </c>
+      <c r="B78" t="n">
+        <v>80001</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>597628</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7072050</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135277126</t>
         </is>
@@ -8646,6 +9356,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28113-2026 artfynd.xlsx
+++ b/artfynd/A 28113-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135185577</v>
       </c>
       <c r="B2" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135254148</v>
       </c>
       <c r="B3" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135252944</v>
       </c>
       <c r="B4" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135253662</v>
       </c>
       <c r="B5" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>135261475</v>
       </c>
       <c r="B6" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>135254269</v>
       </c>
       <c r="B9" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>135254935</v>
       </c>
       <c r="B10" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>135254970</v>
       </c>
       <c r="B11" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>135261210</v>
       </c>
       <c r="B12" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>135253005</v>
       </c>
       <c r="B13" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>135253624</v>
       </c>
       <c r="B14" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>135252916</v>
       </c>
       <c r="B15" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>135253853</v>
       </c>
       <c r="B16" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>135253965</v>
       </c>
       <c r="B17" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>135254335</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>135254748</v>
       </c>
       <c r="B19" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>135254797</v>
       </c>
       <c r="B20" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>135254865</v>
       </c>
       <c r="B21" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>135254896</v>
       </c>
       <c r="B22" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>135254907</v>
       </c>
       <c r="B23" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>135255150</v>
       </c>
       <c r="B24" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>135255347</v>
       </c>
       <c r="B25" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>135255503</v>
       </c>
       <c r="B26" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>135255763</v>
       </c>
       <c r="B27" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>135255809</v>
       </c>
       <c r="B28" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>135256006</v>
       </c>
       <c r="B29" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>135261206</v>
       </c>
       <c r="B30" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>135261208</v>
       </c>
       <c r="B31" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>135261209</v>
       </c>
       <c r="B32" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>135261211</v>
       </c>
       <c r="B33" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>135261212</v>
       </c>
       <c r="B34" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>135261476</v>
       </c>
       <c r="B35" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>135261480</v>
       </c>
       <c r="B36" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>135277134</v>
       </c>
       <c r="B37" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>135277128</v>
       </c>
       <c r="B38" t="n">
-        <v>79435</v>
+        <v>79462</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>135185455</v>
       </c>
       <c r="B39" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>135253692</v>
       </c>
       <c r="B40" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>135277130</v>
       </c>
       <c r="B41" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>135277135</v>
       </c>
       <c r="B42" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>135257132</v>
       </c>
       <c r="B44" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>135257174</v>
       </c>
       <c r="B45" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>135261478</v>
       </c>
       <c r="B46" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>135185445</v>
       </c>
       <c r="B47" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>135261207</v>
       </c>
       <c r="B48" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>135252291</v>
       </c>
       <c r="B65" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>135253119</v>
       </c>
       <c r="B66" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>135261205</v>
       </c>
       <c r="B67" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>135261477</v>
       </c>
       <c r="B68" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>135254080</v>
       </c>
       <c r="B69" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>135254180</v>
       </c>
       <c r="B70" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>135254875</v>
       </c>
       <c r="B71" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>135255066</v>
       </c>
       <c r="B72" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>135255116</v>
       </c>
       <c r="B73" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>135255849</v>
       </c>
       <c r="B74" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>135255990</v>
       </c>
       <c r="B75" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>135256152</v>
       </c>
       <c r="B76" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>135261479</v>
       </c>
       <c r="B77" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>135277126</v>
       </c>
       <c r="B78" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 28113-2026 artfynd.xlsx
+++ b/artfynd/A 28113-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,51 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111802213</v>
+        <v>135185577</v>
       </c>
       <c r="B2" t="n">
-        <v>93213</v>
+        <v>79107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597737</v>
+        <v>597658</v>
       </c>
       <c r="R2" t="n">
-        <v>7071647</v>
+        <v>7071784</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,34 +759,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111802213</t>
+          <t>https://artportalen.se/Sighting/135185577</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111802220</v>
+        <v>135254148</v>
       </c>
       <c r="B3" t="n">
-        <v>93197</v>
+        <v>79107</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,40 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597715</v>
+        <v>597655</v>
       </c>
       <c r="R3" t="n">
-        <v>7071639</v>
+        <v>7071781</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -854,12 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,34 +871,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111802220</t>
+          <t>https://artportalen.se/Sighting/135254148</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111802223</v>
+        <v>135252944</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>92048</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,40 +905,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597726</v>
+        <v>597690</v>
       </c>
       <c r="R4" t="n">
-        <v>7071643</v>
+        <v>7071932</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -960,12 +959,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,34 +973,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111802223</t>
+          <t>https://artportalen.se/Sighting/135252944</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119352061</v>
+        <v>135253662</v>
       </c>
       <c r="B5" t="n">
-        <v>57953</v>
+        <v>92048</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,42 +1007,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597652</v>
+        <v>597687</v>
       </c>
       <c r="R5" t="n">
-        <v>7071974</v>
+        <v>7071870</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,22 +1061,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,18 +1081,8205 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135253662</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135261475</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>597668</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7071982</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261475</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>111802213</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93213</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kullberg, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>597737</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7071647</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111802213</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>111802220</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kullberg, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>597715</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7071639</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111802220</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135254269</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>597670</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7071721</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254269</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135254935</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>597691</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7071625</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254935</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135254970</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>597704</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7071626</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254970</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135261210</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>597710</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7071633</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261210</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135253005</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>597700</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7071941</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135253005</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135253624</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>597702</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7071879</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135253624</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135252916</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>597734</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7071921</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252916</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135253853</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>597701</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7071820</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135253853</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135253965</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>597732</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7071814</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135253965</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135254335</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>597680</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7071698</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254335</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135254748</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>597695</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7071733</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254748</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135254797</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>597759</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7071713</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254797</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135254865</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>597681</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7071663</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254865</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135254896</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>597697</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7071651</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254896</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135254907</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>597691</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7071625</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254907</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135255150</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>597738</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7071628</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255150</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135255347</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>597781</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7071649</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255347</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135255503</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>597801</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7071656</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255503</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135255763</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>597871</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7071582</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255763</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135255809</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>597883</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7071561</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255809</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135256006</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>597907</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7071543</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135256006</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135261206</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>597650</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7071766</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261206</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135261208</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>597686</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7071732</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261208</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135261209</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>597692</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7071677</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261209</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135261211</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>597775</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7071632</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261211</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135261212</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>597811</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7071636</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261212</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135261476</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>597705</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7071935</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261476</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135261480</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>597757</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7071733</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261480</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135277134</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>597690</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7071889</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277134</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135277128</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79465</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>597652</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7072022</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277128</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135185455</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>597723</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7071638</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135185455</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135253692</v>
+      </c>
+      <c r="B40" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>597718</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7071826</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135253692</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135277130</v>
+      </c>
+      <c r="B41" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>597672</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7072025</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277130</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135277135</v>
+      </c>
+      <c r="B42" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>597696</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7071877</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277135</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>111802223</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kullberg, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>597726</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7071643</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111802223</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135257132</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>597810</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7071731</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135257132</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135257174</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>597800</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7071779</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135257174</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135261478</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>597690</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7071824</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261478</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135185445</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>597724</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7071639</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135185445</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135261207</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80560</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>597651</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7071773</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261207</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135253925</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>597717</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7071813</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135253925</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>119352061</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>597652</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7071974</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/119352061</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135185510</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>597653</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7071687</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135185510</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135185592</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>597662</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7071777</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135185592</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135252357</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>597647</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7072042</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252357</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135252502</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>597650</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7071996</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252502</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135252549</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>597648</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7071988</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252549</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135252575</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>597654</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7071984</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252575</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135252599</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>597652</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7071981</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252599</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135252771</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>597694</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7071960</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252771</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135253769</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>597732</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7071814</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135253769</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135254862</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>597826</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7071713</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254862</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135277138</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>597826</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7071709</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277138</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135185420</v>
+      </c>
+      <c r="B62" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>597731</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7071656</v>
+      </c>
+      <c r="S62" t="n">
+        <v>15</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135185420</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135257192</v>
+      </c>
+      <c r="B63" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>597798</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7071782</v>
+      </c>
+      <c r="S63" t="n">
+        <v>15</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135257192</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135277129</v>
+      </c>
+      <c r="B64" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>597655</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7072023</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277129</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135252291</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>597625</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7072015</v>
+      </c>
+      <c r="S65" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252291</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135253119</v>
+      </c>
+      <c r="B66" t="n">
+        <v>98136</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>597685</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7071950</v>
+      </c>
+      <c r="S66" t="n">
+        <v>15</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135253119</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135261205</v>
+      </c>
+      <c r="B67" t="n">
+        <v>98136</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>597679</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7071921</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261205</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135261477</v>
+      </c>
+      <c r="B68" t="n">
+        <v>98136</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>597690</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7071861</v>
+      </c>
+      <c r="S68" t="n">
+        <v>3</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261477</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135254080</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>597664</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7071792</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254080</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135254180</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>597732</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7071814</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254180</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135254875</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>597688</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7071656</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254875</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135255066</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>597711</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7071632</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255066</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135255116</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>597691</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7071625</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255116</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135255849</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>597894</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7071564</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255849</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135255990</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>597890</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7071513</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255990</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135256152</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>597907</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7071543</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135256152</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135261479</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>597679</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7071753</v>
+      </c>
+      <c r="S77" t="n">
+        <v>3</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261479</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135277126</v>
+      </c>
+      <c r="B78" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>597628</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7072050</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277126</t>
         </is>
       </c>
     </row>
@@ -1119,6 +9289,79 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28113-2026 artfynd.xlsx
+++ b/artfynd/A 28113-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ78"/>
+  <dimension ref="A1:AZ72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,7 +897,7 @@
         <v>135252944</v>
       </c>
       <c r="B4" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135253662</v>
       </c>
       <c r="B5" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,48 +1098,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135261475</v>
+        <v>111802213</v>
       </c>
       <c r="B6" t="n">
-        <v>92048</v>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Kullberg, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597668</v>
+        <v>597737</v>
       </c>
       <c r="R6" t="n">
-        <v>7071982</v>
+        <v>7071647</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1163,22 +1166,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1187,55 +1180,56 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261475</t>
+          <t>https://artportalen.se/Sighting/111802213</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111802213</v>
+        <v>111802220</v>
       </c>
       <c r="B7" t="n">
-        <v>93213</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597737</v>
+        <v>597715</v>
       </c>
       <c r="R7" t="n">
-        <v>7071647</v>
+        <v>7071639</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,16 +1304,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111802213</t>
+          <t>https://artportalen.se/Sighting/111802220</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111802220</v>
+        <v>135254269</v>
       </c>
       <c r="B8" t="n">
-        <v>93197</v>
+        <v>93347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1345,22 +1339,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597715</v>
+        <v>597670</v>
       </c>
       <c r="R8" t="n">
-        <v>7071639</v>
+        <v>7071721</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1384,12 +1375,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1398,34 +1399,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111802220</t>
+          <t>https://artportalen.se/Sighting/135254269</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135254269</v>
+        <v>135254935</v>
       </c>
       <c r="B9" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597670</v>
+        <v>597691</v>
       </c>
       <c r="R9" t="n">
-        <v>7071721</v>
+        <v>7071625</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1517,27 +1517,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254269</t>
+          <t>https://artportalen.se/Sighting/135254935</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135254935</v>
+        <v>135254970</v>
       </c>
       <c r="B10" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597691</v>
+        <v>597704</v>
       </c>
       <c r="R10" t="n">
-        <v>7071625</v>
+        <v>7071626</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,27 +1629,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254935</t>
+          <t>https://artportalen.se/Sighting/135254970</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135254970</v>
+        <v>135261210</v>
       </c>
       <c r="B11" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,20 +1674,31 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597704</v>
+        <v>597710</v>
       </c>
       <c r="R11" t="n">
-        <v>7071626</v>
+        <v>7071633</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1716,7 +1727,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1726,7 +1737,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,82 +1746,72 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254970</t>
+          <t>https://artportalen.se/Sighting/135261210</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135261210</v>
+        <v>135253005</v>
       </c>
       <c r="B12" t="n">
-        <v>93345</v>
+        <v>92013</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597710</v>
+        <v>597700</v>
       </c>
       <c r="R12" t="n">
-        <v>7071633</v>
+        <v>7071941</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1837,55 +1838,44 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>17:44</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>17:44</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261210</t>
+          <t>https://artportalen.se/Sighting/135253005</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135253005</v>
+        <v>135253624</v>
       </c>
       <c r="B13" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1917,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597700</v>
+        <v>597702</v>
       </c>
       <c r="R13" t="n">
-        <v>7071941</v>
+        <v>7071879</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1978,38 +1968,38 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253005</t>
+          <t>https://artportalen.se/Sighting/135253624</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135253624</v>
+        <v>135252916</v>
       </c>
       <c r="B14" t="n">
-        <v>92011</v>
+        <v>79441</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2019,13 +2009,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597702</v>
+        <v>597734</v>
       </c>
       <c r="R14" t="n">
-        <v>7071879</v>
+        <v>7071921</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2052,9 +2042,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,24 +2069,24 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253624</t>
+          <t>https://artportalen.se/Sighting/135252916</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135252916</v>
+        <v>135253853</v>
       </c>
       <c r="B15" t="n">
         <v>79441</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597734</v>
+        <v>597701</v>
       </c>
       <c r="R15" t="n">
-        <v>7071921</v>
+        <v>7071820</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2181,24 +2181,24 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252916</t>
+          <t>https://artportalen.se/Sighting/135253853</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135253853</v>
+        <v>135253965</v>
       </c>
       <c r="B16" t="n">
         <v>79441</v>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597701</v>
+        <v>597732</v>
       </c>
       <c r="R16" t="n">
-        <v>7071820</v>
+        <v>7071814</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,24 +2293,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253853</t>
+          <t>https://artportalen.se/Sighting/135253965</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135253965</v>
+        <v>135254335</v>
       </c>
       <c r="B17" t="n">
         <v>79441</v>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597732</v>
+        <v>597680</v>
       </c>
       <c r="R17" t="n">
-        <v>7071814</v>
+        <v>7071698</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2416,13 +2416,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253965</t>
+          <t>https://artportalen.se/Sighting/135254335</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135254335</v>
+        <v>135254748</v>
       </c>
       <c r="B18" t="n">
         <v>79441</v>
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597680</v>
+        <v>597695</v>
       </c>
       <c r="R18" t="n">
-        <v>7071698</v>
+        <v>7071733</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,24 +2517,24 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254335</t>
+          <t>https://artportalen.se/Sighting/135254748</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135254748</v>
+        <v>135254797</v>
       </c>
       <c r="B19" t="n">
         <v>79441</v>
@@ -2569,13 +2569,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597695</v>
+        <v>597759</v>
       </c>
       <c r="R19" t="n">
-        <v>7071733</v>
+        <v>7071713</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2602,19 +2602,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>17:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2629,24 +2619,24 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254748</t>
+          <t>https://artportalen.se/Sighting/135254797</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135254797</v>
+        <v>135254865</v>
       </c>
       <c r="B20" t="n">
         <v>79441</v>
@@ -2681,13 +2671,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597759</v>
+        <v>597681</v>
       </c>
       <c r="R20" t="n">
-        <v>7071713</v>
+        <v>7071663</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2714,9 +2704,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2731,24 +2731,24 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254797</t>
+          <t>https://artportalen.se/Sighting/135254865</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135254865</v>
+        <v>135254896</v>
       </c>
       <c r="B21" t="n">
         <v>79441</v>
@@ -2783,10 +2783,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597681</v>
+        <v>597697</v>
       </c>
       <c r="R21" t="n">
-        <v>7071663</v>
+        <v>7071651</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2854,13 +2854,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254865</t>
+          <t>https://artportalen.se/Sighting/135254896</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135254896</v>
+        <v>135254907</v>
       </c>
       <c r="B22" t="n">
         <v>79441</v>
@@ -2895,10 +2895,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597697</v>
+        <v>597691</v>
       </c>
       <c r="R22" t="n">
-        <v>7071651</v>
+        <v>7071625</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2955,24 +2955,24 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254896</t>
+          <t>https://artportalen.se/Sighting/135254907</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135254907</v>
+        <v>135255150</v>
       </c>
       <c r="B23" t="n">
         <v>79441</v>
@@ -3007,10 +3007,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597691</v>
+        <v>597738</v>
       </c>
       <c r="R23" t="n">
-        <v>7071625</v>
+        <v>7071628</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3067,24 +3067,24 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254907</t>
+          <t>https://artportalen.se/Sighting/135255150</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135255150</v>
+        <v>135255347</v>
       </c>
       <c r="B24" t="n">
         <v>79441</v>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597738</v>
+        <v>597781</v>
       </c>
       <c r="R24" t="n">
-        <v>7071628</v>
+        <v>7071649</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3190,13 +3190,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255150</t>
+          <t>https://artportalen.se/Sighting/135255347</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135255347</v>
+        <v>135255503</v>
       </c>
       <c r="B25" t="n">
         <v>79441</v>
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597781</v>
+        <v>597801</v>
       </c>
       <c r="R25" t="n">
-        <v>7071649</v>
+        <v>7071656</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3302,13 +3302,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255347</t>
+          <t>https://artportalen.se/Sighting/135255503</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135255503</v>
+        <v>135255763</v>
       </c>
       <c r="B26" t="n">
         <v>79441</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597801</v>
+        <v>597871</v>
       </c>
       <c r="R26" t="n">
-        <v>7071656</v>
+        <v>7071582</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3414,13 +3414,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255503</t>
+          <t>https://artportalen.se/Sighting/135255763</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135255763</v>
+        <v>135255809</v>
       </c>
       <c r="B27" t="n">
         <v>79441</v>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597871</v>
+        <v>597883</v>
       </c>
       <c r="R27" t="n">
-        <v>7071582</v>
+        <v>7071561</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3526,13 +3526,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255763</t>
+          <t>https://artportalen.se/Sighting/135255809</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135255809</v>
+        <v>135256006</v>
       </c>
       <c r="B28" t="n">
         <v>79441</v>
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>597883</v>
+        <v>597907</v>
       </c>
       <c r="R28" t="n">
-        <v>7071561</v>
+        <v>7071543</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3627,24 +3627,24 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255809</t>
+          <t>https://artportalen.se/Sighting/135256006</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135256006</v>
+        <v>135261206</v>
       </c>
       <c r="B29" t="n">
         <v>79441</v>
@@ -3673,19 +3673,22 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>597907</v>
+        <v>597650</v>
       </c>
       <c r="R29" t="n">
-        <v>7071543</v>
+        <v>7071766</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3714,7 +3717,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3724,7 +3727,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3733,30 +3736,46 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135256006</t>
+          <t>https://artportalen.se/Sighting/135261206</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135261206</v>
+        <v>135261208</v>
       </c>
       <c r="B30" t="n">
         <v>79441</v>
@@ -3785,19 +3804,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>597650</v>
+        <v>597686</v>
       </c>
       <c r="R30" t="n">
-        <v>7071766</v>
+        <v>7071732</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3829,7 +3845,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3839,7 +3855,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3848,24 +3864,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3881,13 +3881,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261206</t>
+          <t>https://artportalen.se/Sighting/135261208</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135261208</v>
+        <v>135261209</v>
       </c>
       <c r="B31" t="n">
         <v>79441</v>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>597686</v>
+        <v>597692</v>
       </c>
       <c r="R31" t="n">
-        <v>7071732</v>
+        <v>7071677</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3993,13 +3993,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261208</t>
+          <t>https://artportalen.se/Sighting/135261209</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135261209</v>
+        <v>135261211</v>
       </c>
       <c r="B32" t="n">
         <v>79441</v>
@@ -4034,10 +4034,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>597692</v>
+        <v>597775</v>
       </c>
       <c r="R32" t="n">
-        <v>7071677</v>
+        <v>7071632</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4105,13 +4105,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261209</t>
+          <t>https://artportalen.se/Sighting/135261211</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135261211</v>
+        <v>135261212</v>
       </c>
       <c r="B33" t="n">
         <v>79441</v>
@@ -4146,10 +4146,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>597775</v>
+        <v>597811</v>
       </c>
       <c r="R33" t="n">
-        <v>7071632</v>
+        <v>7071636</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4217,13 +4217,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261211</t>
+          <t>https://artportalen.se/Sighting/135261212</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135261212</v>
+        <v>135277134</v>
       </c>
       <c r="B34" t="n">
         <v>79441</v>
@@ -4254,17 +4254,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>597811</v>
+        <v>597690</v>
       </c>
       <c r="R34" t="n">
-        <v>7071636</v>
+        <v>7071889</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4318,68 +4318,65 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261212</t>
+          <t>https://artportalen.se/Sighting/135277134</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135261476</v>
+        <v>135277128</v>
       </c>
       <c r="B35" t="n">
-        <v>79441</v>
+        <v>79465</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>597705</v>
+        <v>597652</v>
       </c>
       <c r="R35" t="n">
-        <v>7071935</v>
+        <v>7072022</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4408,7 +4405,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4418,7 +4415,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4427,90 +4424,71 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261476</t>
+          <t>https://artportalen.se/Sighting/135277128</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135261480</v>
+        <v>135185455</v>
       </c>
       <c r="B36" t="n">
-        <v>79441</v>
+        <v>78844</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>597757</v>
+        <v>597723</v>
       </c>
       <c r="R36" t="n">
-        <v>7071733</v>
+        <v>7071638</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4534,22 +4512,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>17:27</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>17:27</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4558,87 +4526,71 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261480</t>
+          <t>https://artportalen.se/Sighting/135185455</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135277134</v>
+        <v>135253692</v>
       </c>
       <c r="B37" t="n">
-        <v>79441</v>
+        <v>83428</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>597690</v>
+        <v>597718</v>
       </c>
       <c r="R37" t="n">
-        <v>7071889</v>
+        <v>7071826</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4665,19 +4617,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4692,49 +4634,49 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277134</t>
+          <t>https://artportalen.se/Sighting/135253692</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135277128</v>
+        <v>135277130</v>
       </c>
       <c r="B38" t="n">
-        <v>79465</v>
+        <v>83428</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6434</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4744,10 +4686,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>597652</v>
+        <v>597672</v>
       </c>
       <c r="R38" t="n">
-        <v>7072022</v>
+        <v>7072025</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4779,7 +4721,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4789,7 +4731,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4815,16 +4757,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277128</t>
+          <t>https://artportalen.se/Sighting/135277130</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135185455</v>
+        <v>135277135</v>
       </c>
       <c r="B39" t="n">
-        <v>78844</v>
+        <v>83428</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4832,37 +4774,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>597723</v>
+        <v>597696</v>
       </c>
       <c r="R39" t="n">
-        <v>7071638</v>
+        <v>7071877</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4886,12 +4828,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4906,27 +4858,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135185455</t>
+          <t>https://artportalen.se/Sighting/135277135</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135253692</v>
+        <v>111802223</v>
       </c>
       <c r="B40" t="n">
-        <v>83428</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4934,37 +4886,40 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Kullberg, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>597718</v>
+        <v>597726</v>
       </c>
       <c r="R40" t="n">
-        <v>7071826</v>
+        <v>7071643</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4988,12 +4943,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5002,33 +4957,34 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253692</t>
+          <t>https://artportalen.se/Sighting/111802223</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135277130</v>
+        <v>135257132</v>
       </c>
       <c r="B41" t="n">
-        <v>83428</v>
+        <v>79198</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5036,37 +4992,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>597672</v>
+        <v>597810</v>
       </c>
       <c r="R41" t="n">
-        <v>7072025</v>
+        <v>7071731</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5093,19 +5049,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:36</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5120,27 +5066,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277130</t>
+          <t>https://artportalen.se/Sighting/135257132</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135277135</v>
+        <v>135257174</v>
       </c>
       <c r="B42" t="n">
-        <v>83428</v>
+        <v>79198</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5148,37 +5094,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>597696</v>
+        <v>597800</v>
       </c>
       <c r="R42" t="n">
-        <v>7071877</v>
+        <v>7071779</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5205,19 +5151,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>16:33</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>16:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5232,27 +5168,27 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277135</t>
+          <t>https://artportalen.se/Sighting/135257174</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>111802223</v>
+        <v>135185445</v>
       </c>
       <c r="B43" t="n">
-        <v>79084</v>
+        <v>80060</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5260,40 +5196,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>597726</v>
+        <v>597724</v>
       </c>
       <c r="R43" t="n">
-        <v>7071643</v>
+        <v>7071639</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5317,12 +5250,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5331,72 +5264,71 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111802223</t>
+          <t>https://artportalen.se/Sighting/135185445</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135257132</v>
+        <v>135261207</v>
       </c>
       <c r="B44" t="n">
-        <v>79198</v>
+        <v>80560</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>597810</v>
+        <v>597651</v>
       </c>
       <c r="R44" t="n">
-        <v>7071731</v>
+        <v>7071773</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5423,9 +5355,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5440,62 +5382,67 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135257132</t>
+          <t>https://artportalen.se/Sighting/135261207</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135257174</v>
+        <v>135253925</v>
       </c>
       <c r="B45" t="n">
-        <v>79198</v>
+        <v>57977</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>597800</v>
+        <v>597717</v>
       </c>
       <c r="R45" t="n">
-        <v>7071779</v>
+        <v>7071813</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5553,16 +5500,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135257174</t>
+          <t>https://artportalen.se/Sighting/135253925</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135261478</v>
+        <v>119352061</v>
       </c>
       <c r="B46" t="n">
-        <v>79198</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5570,37 +5517,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>597690</v>
+        <v>597652</v>
       </c>
       <c r="R46" t="n">
-        <v>7071824</v>
+        <v>7071974</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5624,22 +5576,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5654,27 +5606,27 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261478</t>
+          <t>https://artportalen.se/Sighting/119352061</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135185445</v>
+        <v>135185510</v>
       </c>
       <c r="B47" t="n">
-        <v>80060</v>
+        <v>57980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5682,34 +5634,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>597724</v>
+        <v>597653</v>
       </c>
       <c r="R47" t="n">
-        <v>7071639</v>
+        <v>7071687</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5744,6 +5701,11 @@
           <t>2026-07-16</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5767,54 +5729,59 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135185445</t>
+          <t>https://artportalen.se/Sighting/135185510</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135261207</v>
+        <v>135185592</v>
       </c>
       <c r="B48" t="n">
-        <v>80560</v>
+        <v>57980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>597651</v>
+        <v>597662</v>
       </c>
       <c r="R48" t="n">
-        <v>7071773</v>
+        <v>7071777</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5838,22 +5805,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>17:01</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>17:01</t>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5868,44 +5830,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261207</t>
+          <t>https://artportalen.se/Sighting/135185592</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135253925</v>
+        <v>135252357</v>
       </c>
       <c r="B49" t="n">
-        <v>57977</v>
+        <v>57980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5916,7 +5878,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5925,13 +5887,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>597717</v>
+        <v>597647</v>
       </c>
       <c r="R49" t="n">
-        <v>7071813</v>
+        <v>7072042</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5958,9 +5920,24 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5975,27 +5952,27 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253925</t>
+          <t>https://artportalen.se/Sighting/135252357</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119352061</v>
+        <v>135252502</v>
       </c>
       <c r="B50" t="n">
-        <v>57953</v>
+        <v>57980</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6032,10 +6009,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>597652</v>
+        <v>597650</v>
       </c>
       <c r="R50" t="n">
-        <v>7071974</v>
+        <v>7071996</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6062,22 +6039,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6103,13 +6085,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119352061</t>
+          <t>https://artportalen.se/Sighting/135252502</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135185510</v>
+        <v>135252549</v>
       </c>
       <c r="B51" t="n">
         <v>57980</v>
@@ -6140,7 +6122,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6149,13 +6131,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>597653</v>
+        <v>597648</v>
       </c>
       <c r="R51" t="n">
-        <v>7071687</v>
+        <v>7071988</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6179,17 +6161,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6204,24 +6196,24 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135185510</t>
+          <t>https://artportalen.se/Sighting/135252549</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135185592</v>
+        <v>135252575</v>
       </c>
       <c r="B52" t="n">
         <v>57980</v>
@@ -6261,13 +6253,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>597662</v>
+        <v>597654</v>
       </c>
       <c r="R52" t="n">
-        <v>7071777</v>
+        <v>7071984</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6291,17 +6283,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6316,24 +6318,24 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135185592</t>
+          <t>https://artportalen.se/Sighting/135252575</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135252357</v>
+        <v>135252599</v>
       </c>
       <c r="B53" t="n">
         <v>57980</v>
@@ -6364,7 +6366,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6373,10 +6375,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>597647</v>
+        <v>597652</v>
       </c>
       <c r="R53" t="n">
-        <v>7072042</v>
+        <v>7071981</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6408,7 +6410,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6418,12 +6420,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6438,24 +6440,24 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252357</t>
+          <t>https://artportalen.se/Sighting/135252599</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135252502</v>
+        <v>135252771</v>
       </c>
       <c r="B54" t="n">
         <v>57980</v>
@@ -6495,10 +6497,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>597650</v>
+        <v>597694</v>
       </c>
       <c r="R54" t="n">
-        <v>7071996</v>
+        <v>7071960</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6530,7 +6532,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6540,7 +6542,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -6571,13 +6573,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252502</t>
+          <t>https://artportalen.se/Sighting/135252771</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135252549</v>
+        <v>135253769</v>
       </c>
       <c r="B55" t="n">
         <v>57980</v>
@@ -6617,10 +6619,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>597648</v>
+        <v>597732</v>
       </c>
       <c r="R55" t="n">
-        <v>7071988</v>
+        <v>7071814</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6652,7 +6654,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6662,7 +6664,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -6682,55 +6684,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252549</t>
+          <t>https://artportalen.se/Sighting/135253769</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135252575</v>
+        <v>135254862</v>
       </c>
       <c r="B56" t="n">
-        <v>57980</v>
+        <v>57167</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6739,13 +6746,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>597654</v>
+        <v>597826</v>
       </c>
       <c r="R56" t="n">
-        <v>7071984</v>
+        <v>7071713</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6772,24 +6779,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6804,67 +6796,62 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252575</t>
+          <t>https://artportalen.se/Sighting/135254862</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135252599</v>
+        <v>135277138</v>
       </c>
       <c r="B57" t="n">
-        <v>57980</v>
+        <v>57167</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>597652</v>
+        <v>597826</v>
       </c>
       <c r="R57" t="n">
-        <v>7071981</v>
+        <v>7071709</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6896,7 +6883,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6906,12 +6893,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6926,27 +6908,27 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252599</t>
+          <t>https://artportalen.se/Sighting/135277138</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135252771</v>
+        <v>135185420</v>
       </c>
       <c r="B58" t="n">
-        <v>57980</v>
+        <v>58141</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6954,27 +6936,27 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6983,13 +6965,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>597694</v>
+        <v>597731</v>
       </c>
       <c r="R58" t="n">
-        <v>7071960</v>
+        <v>7071656</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7013,27 +6995,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>15:55</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7048,27 +7015,27 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252771</t>
+          <t>https://artportalen.se/Sighting/135185420</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135253769</v>
+        <v>135257192</v>
       </c>
       <c r="B59" t="n">
-        <v>57980</v>
+        <v>58141</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7076,27 +7043,27 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7105,13 +7072,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>597732</v>
+        <v>597798</v>
       </c>
       <c r="R59" t="n">
-        <v>7071814</v>
+        <v>7071782</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7138,24 +7105,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>16:36</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7170,27 +7122,27 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253769</t>
+          <t>https://artportalen.se/Sighting/135257192</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135254862</v>
+        <v>135277129</v>
       </c>
       <c r="B60" t="n">
-        <v>57167</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7198,47 +7150,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>597826</v>
+        <v>597655</v>
       </c>
       <c r="R60" t="n">
-        <v>7071713</v>
+        <v>7072023</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7265,9 +7207,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7282,27 +7234,27 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254862</t>
+          <t>https://artportalen.se/Sighting/135277129</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135277138</v>
+        <v>135252291</v>
       </c>
       <c r="B61" t="n">
-        <v>57167</v>
+        <v>99193</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7310,37 +7262,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>597826</v>
+        <v>597625</v>
       </c>
       <c r="R61" t="n">
-        <v>7071709</v>
+        <v>7072015</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7367,19 +7319,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>17:32</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>17:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7394,67 +7336,62 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277138</t>
+          <t>https://artportalen.se/Sighting/135252291</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135185420</v>
+        <v>135253119</v>
       </c>
       <c r="B62" t="n">
-        <v>58141</v>
+        <v>98138</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>597731</v>
+        <v>597685</v>
       </c>
       <c r="R62" t="n">
-        <v>7071656</v>
+        <v>7071950</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7481,12 +7418,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7512,59 +7449,54 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135185420</t>
+          <t>https://artportalen.se/Sighting/135253119</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135257192</v>
+        <v>135261205</v>
       </c>
       <c r="B63" t="n">
-        <v>58141</v>
+        <v>98138</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>597798</v>
+        <v>597679</v>
       </c>
       <c r="R63" t="n">
-        <v>7071782</v>
+        <v>7071921</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7591,9 +7523,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7608,62 +7550,62 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135257192</t>
+          <t>https://artportalen.se/Sighting/135261205</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135277129</v>
+        <v>135254080</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>79199</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106554</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>597655</v>
+        <v>597664</v>
       </c>
       <c r="R64" t="n">
-        <v>7072023</v>
+        <v>7071792</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7695,7 +7637,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7705,7 +7647,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7720,49 +7662,49 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277129</t>
+          <t>https://artportalen.se/Sighting/135254080</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135252291</v>
+        <v>135254180</v>
       </c>
       <c r="B65" t="n">
-        <v>99191</v>
+        <v>79199</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7772,13 +7714,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>597625</v>
+        <v>597732</v>
       </c>
       <c r="R65" t="n">
-        <v>7072015</v>
+        <v>7071814</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7805,9 +7747,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7822,49 +7774,49 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252291</t>
+          <t>https://artportalen.se/Sighting/135254180</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135253119</v>
+        <v>135254875</v>
       </c>
       <c r="B66" t="n">
-        <v>98136</v>
+        <v>79199</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7874,13 +7826,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>597685</v>
+        <v>597688</v>
       </c>
       <c r="R66" t="n">
-        <v>7071950</v>
+        <v>7071656</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7907,9 +7859,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7924,65 +7886,65 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253119</t>
+          <t>https://artportalen.se/Sighting/135254875</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135261205</v>
+        <v>135255066</v>
       </c>
       <c r="B67" t="n">
-        <v>98136</v>
+        <v>79199</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>597679</v>
+        <v>597711</v>
       </c>
       <c r="R67" t="n">
-        <v>7071921</v>
+        <v>7071632</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8011,7 +7973,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8021,7 +7983,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8036,65 +7998,65 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261205</t>
+          <t>https://artportalen.se/Sighting/135255066</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135261477</v>
+        <v>135255116</v>
       </c>
       <c r="B68" t="n">
-        <v>98136</v>
+        <v>79199</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>597690</v>
+        <v>597691</v>
       </c>
       <c r="R68" t="n">
-        <v>7071861</v>
+        <v>7071625</v>
       </c>
       <c r="S68" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8123,7 +8085,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8133,7 +8095,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8148,24 +8110,24 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261477</t>
+          <t>https://artportalen.se/Sighting/135255116</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135254080</v>
+        <v>135255849</v>
       </c>
       <c r="B69" t="n">
         <v>79199</v>
@@ -8200,10 +8162,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>597664</v>
+        <v>597894</v>
       </c>
       <c r="R69" t="n">
-        <v>7071792</v>
+        <v>7071564</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8235,7 +8197,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8245,7 +8207,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8271,13 +8233,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254080</t>
+          <t>https://artportalen.se/Sighting/135255849</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135254180</v>
+        <v>135255990</v>
       </c>
       <c r="B70" t="n">
         <v>79199</v>
@@ -8308,14 +8270,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>597732</v>
+        <v>597890</v>
       </c>
       <c r="R70" t="n">
-        <v>7071814</v>
+        <v>7071513</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8347,7 +8309,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8357,7 +8319,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8372,24 +8334,24 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254180</t>
+          <t>https://artportalen.se/Sighting/135255990</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135254875</v>
+        <v>135256152</v>
       </c>
       <c r="B71" t="n">
         <v>79199</v>
@@ -8424,10 +8386,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>597688</v>
+        <v>597907</v>
       </c>
       <c r="R71" t="n">
-        <v>7071656</v>
+        <v>7071543</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8459,7 +8421,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8469,7 +8431,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8484,27 +8446,27 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254875</t>
+          <t>https://artportalen.se/Sighting/135256152</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135255066</v>
+        <v>135277126</v>
       </c>
       <c r="B72" t="n">
-        <v>79199</v>
+        <v>80031</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8512,34 +8474,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>597711</v>
+        <v>597628</v>
       </c>
       <c r="R72" t="n">
-        <v>7071632</v>
+        <v>7072050</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8571,7 +8533,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8581,7 +8543,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8596,688 +8558,16 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135255066</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>135255116</v>
-      </c>
-      <c r="B73" t="n">
-        <v>79199</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>597691</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7071625</v>
-      </c>
-      <c r="S73" t="n">
-        <v>10</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>17:47</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>17:47</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Johanna Liljegren</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Johanna Liljegren</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135255116</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>135255849</v>
-      </c>
-      <c r="B74" t="n">
-        <v>79199</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>597894</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7071564</v>
-      </c>
-      <c r="S74" t="n">
-        <v>10</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>18:19</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>18:19</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135255849</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>135255990</v>
-      </c>
-      <c r="B75" t="n">
-        <v>79199</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>597890</v>
-      </c>
-      <c r="R75" t="n">
-        <v>7071513</v>
-      </c>
-      <c r="S75" t="n">
-        <v>10</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>18:23</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>18:23</t>
-        </is>
-      </c>
-      <c r="AD75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135255990</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>135256152</v>
-      </c>
-      <c r="B76" t="n">
-        <v>79199</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>597907</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7071543</v>
-      </c>
-      <c r="S76" t="n">
-        <v>10</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Johanna Liljegren</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Johanna Liljegren</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135256152</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>135261479</v>
-      </c>
-      <c r="B77" t="n">
-        <v>79199</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Lill-kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q77" t="n">
-        <v>597679</v>
-      </c>
-      <c r="R77" t="n">
-        <v>7071753</v>
-      </c>
-      <c r="S77" t="n">
-        <v>3</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>17:13</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>17:13</t>
-        </is>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT77" t="inlineStr"/>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135261479</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>135277126</v>
-      </c>
-      <c r="B78" t="n">
-        <v>80031</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
-        </is>
-      </c>
-      <c r="Q78" t="n">
-        <v>597628</v>
-      </c>
-      <c r="R78" t="n">
-        <v>7072050</v>
-      </c>
-      <c r="S78" t="n">
-        <v>10</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AD78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT78" t="inlineStr"/>
-      <c r="AW78" t="inlineStr">
-        <is>
-          <t>Anne-Katrin Würthele</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>Anne-Katrin Würthele</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
-      <c r="AZ78" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135277126</t>
         </is>
@@ -9356,12 +8646,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28113-2026 artfynd.xlsx
+++ b/artfynd/A 28113-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ72"/>
+  <dimension ref="A1:AZ78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,51 +1098,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111802213</v>
+        <v>135261475</v>
       </c>
       <c r="B6" t="n">
-        <v>93213</v>
+        <v>92050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597737</v>
+        <v>597668</v>
       </c>
       <c r="R6" t="n">
-        <v>7071647</v>
+        <v>7071982</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1166,12 +1163,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,56 +1187,55 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111802213</t>
+          <t>https://artportalen.se/Sighting/135261475</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111802220</v>
+        <v>111802213</v>
       </c>
       <c r="B7" t="n">
-        <v>93197</v>
+        <v>93213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1242,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597715</v>
+        <v>597737</v>
       </c>
       <c r="R7" t="n">
-        <v>7071639</v>
+        <v>7071647</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1304,16 +1310,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111802220</t>
+          <t>https://artportalen.se/Sighting/111802213</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135254269</v>
+        <v>111802220</v>
       </c>
       <c r="B8" t="n">
-        <v>93347</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1339,19 +1345,22 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Kullberg, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597670</v>
+        <v>597715</v>
       </c>
       <c r="R8" t="n">
-        <v>7071721</v>
+        <v>7071639</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1375,22 +1384,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>17:02</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:02</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,30 +1398,31 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254269</t>
+          <t>https://artportalen.se/Sighting/111802220</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135254935</v>
+        <v>135254269</v>
       </c>
       <c r="B9" t="n">
         <v>93347</v>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597691</v>
+        <v>597670</v>
       </c>
       <c r="R9" t="n">
-        <v>7071625</v>
+        <v>7071721</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1517,24 +1517,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254935</t>
+          <t>https://artportalen.se/Sighting/135254269</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135254970</v>
+        <v>135254935</v>
       </c>
       <c r="B10" t="n">
         <v>93347</v>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597704</v>
+        <v>597691</v>
       </c>
       <c r="R10" t="n">
-        <v>7071626</v>
+        <v>7071625</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,24 +1629,24 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254970</t>
+          <t>https://artportalen.se/Sighting/135254935</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135261210</v>
+        <v>135254970</v>
       </c>
       <c r="B11" t="n">
         <v>93347</v>
@@ -1674,31 +1674,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597710</v>
+        <v>597704</v>
       </c>
       <c r="R11" t="n">
-        <v>7071633</v>
+        <v>7071626</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1727,7 +1716,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1737,7 +1726,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,72 +1735,82 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261210</t>
+          <t>https://artportalen.se/Sighting/135254970</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135253005</v>
+        <v>135261210</v>
       </c>
       <c r="B12" t="n">
-        <v>92013</v>
+        <v>93347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597700</v>
+        <v>597710</v>
       </c>
       <c r="R12" t="n">
-        <v>7071941</v>
+        <v>7071633</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1838,41 +1837,52 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253005</t>
+          <t>https://artportalen.se/Sighting/135261210</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135253624</v>
+        <v>135253005</v>
       </c>
       <c r="B13" t="n">
         <v>92013</v>
@@ -1907,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597702</v>
+        <v>597700</v>
       </c>
       <c r="R13" t="n">
-        <v>7071879</v>
+        <v>7071941</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1968,38 +1978,38 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253624</t>
+          <t>https://artportalen.se/Sighting/135253005</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135252916</v>
+        <v>135253624</v>
       </c>
       <c r="B14" t="n">
-        <v>79441</v>
+        <v>92013</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2009,13 +2019,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597734</v>
+        <v>597702</v>
       </c>
       <c r="R14" t="n">
-        <v>7071921</v>
+        <v>7071879</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2042,19 +2052,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,24 +2069,24 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252916</t>
+          <t>https://artportalen.se/Sighting/135253624</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135253853</v>
+        <v>135252916</v>
       </c>
       <c r="B15" t="n">
         <v>79441</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597701</v>
+        <v>597734</v>
       </c>
       <c r="R15" t="n">
-        <v>7071820</v>
+        <v>7071921</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2181,24 +2181,24 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253853</t>
+          <t>https://artportalen.se/Sighting/135252916</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135253965</v>
+        <v>135253853</v>
       </c>
       <c r="B16" t="n">
         <v>79441</v>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597732</v>
+        <v>597701</v>
       </c>
       <c r="R16" t="n">
-        <v>7071814</v>
+        <v>7071820</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,24 +2293,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253965</t>
+          <t>https://artportalen.se/Sighting/135253853</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135254335</v>
+        <v>135253965</v>
       </c>
       <c r="B17" t="n">
         <v>79441</v>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597680</v>
+        <v>597732</v>
       </c>
       <c r="R17" t="n">
-        <v>7071698</v>
+        <v>7071814</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2416,13 +2416,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254335</t>
+          <t>https://artportalen.se/Sighting/135253965</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135254748</v>
+        <v>135254335</v>
       </c>
       <c r="B18" t="n">
         <v>79441</v>
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597695</v>
+        <v>597680</v>
       </c>
       <c r="R18" t="n">
-        <v>7071733</v>
+        <v>7071698</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,24 +2517,24 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254748</t>
+          <t>https://artportalen.se/Sighting/135254335</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135254797</v>
+        <v>135254748</v>
       </c>
       <c r="B19" t="n">
         <v>79441</v>
@@ -2569,13 +2569,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597759</v>
+        <v>597695</v>
       </c>
       <c r="R19" t="n">
-        <v>7071713</v>
+        <v>7071733</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2602,9 +2602,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,24 +2629,24 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254797</t>
+          <t>https://artportalen.se/Sighting/135254748</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135254865</v>
+        <v>135254797</v>
       </c>
       <c r="B20" t="n">
         <v>79441</v>
@@ -2671,13 +2681,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597681</v>
+        <v>597759</v>
       </c>
       <c r="R20" t="n">
-        <v>7071663</v>
+        <v>7071713</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2704,19 +2714,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>17:33</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2731,24 +2731,24 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254865</t>
+          <t>https://artportalen.se/Sighting/135254797</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135254896</v>
+        <v>135254865</v>
       </c>
       <c r="B21" t="n">
         <v>79441</v>
@@ -2783,10 +2783,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597697</v>
+        <v>597681</v>
       </c>
       <c r="R21" t="n">
-        <v>7071651</v>
+        <v>7071663</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2854,13 +2854,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254896</t>
+          <t>https://artportalen.se/Sighting/135254865</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135254907</v>
+        <v>135254896</v>
       </c>
       <c r="B22" t="n">
         <v>79441</v>
@@ -2895,10 +2895,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597691</v>
+        <v>597697</v>
       </c>
       <c r="R22" t="n">
-        <v>7071625</v>
+        <v>7071651</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2955,24 +2955,24 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254907</t>
+          <t>https://artportalen.se/Sighting/135254896</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135255150</v>
+        <v>135254907</v>
       </c>
       <c r="B23" t="n">
         <v>79441</v>
@@ -3007,10 +3007,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597738</v>
+        <v>597691</v>
       </c>
       <c r="R23" t="n">
-        <v>7071628</v>
+        <v>7071625</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3067,24 +3067,24 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255150</t>
+          <t>https://artportalen.se/Sighting/135254907</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135255347</v>
+        <v>135255150</v>
       </c>
       <c r="B24" t="n">
         <v>79441</v>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597781</v>
+        <v>597738</v>
       </c>
       <c r="R24" t="n">
-        <v>7071649</v>
+        <v>7071628</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3190,13 +3190,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255347</t>
+          <t>https://artportalen.se/Sighting/135255150</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135255503</v>
+        <v>135255347</v>
       </c>
       <c r="B25" t="n">
         <v>79441</v>
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597801</v>
+        <v>597781</v>
       </c>
       <c r="R25" t="n">
-        <v>7071656</v>
+        <v>7071649</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3302,13 +3302,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255503</t>
+          <t>https://artportalen.se/Sighting/135255347</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135255763</v>
+        <v>135255503</v>
       </c>
       <c r="B26" t="n">
         <v>79441</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597871</v>
+        <v>597801</v>
       </c>
       <c r="R26" t="n">
-        <v>7071582</v>
+        <v>7071656</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3414,13 +3414,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255763</t>
+          <t>https://artportalen.se/Sighting/135255503</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135255809</v>
+        <v>135255763</v>
       </c>
       <c r="B27" t="n">
         <v>79441</v>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597883</v>
+        <v>597871</v>
       </c>
       <c r="R27" t="n">
-        <v>7071561</v>
+        <v>7071582</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3526,13 +3526,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255809</t>
+          <t>https://artportalen.se/Sighting/135255763</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135256006</v>
+        <v>135255809</v>
       </c>
       <c r="B28" t="n">
         <v>79441</v>
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>597907</v>
+        <v>597883</v>
       </c>
       <c r="R28" t="n">
-        <v>7071543</v>
+        <v>7071561</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3627,24 +3627,24 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135256006</t>
+          <t>https://artportalen.se/Sighting/135255809</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135261206</v>
+        <v>135256006</v>
       </c>
       <c r="B29" t="n">
         <v>79441</v>
@@ -3673,22 +3673,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>597650</v>
+        <v>597907</v>
       </c>
       <c r="R29" t="n">
-        <v>7071766</v>
+        <v>7071543</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3717,7 +3714,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3727,7 +3724,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3736,46 +3733,30 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261206</t>
+          <t>https://artportalen.se/Sighting/135256006</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135261208</v>
+        <v>135261206</v>
       </c>
       <c r="B30" t="n">
         <v>79441</v>
@@ -3804,16 +3785,19 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>597686</v>
+        <v>597650</v>
       </c>
       <c r="R30" t="n">
-        <v>7071732</v>
+        <v>7071766</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3845,7 +3829,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3855,7 +3839,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3864,8 +3848,24 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3881,13 +3881,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261208</t>
+          <t>https://artportalen.se/Sighting/135261206</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135261209</v>
+        <v>135261208</v>
       </c>
       <c r="B31" t="n">
         <v>79441</v>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>597692</v>
+        <v>597686</v>
       </c>
       <c r="R31" t="n">
-        <v>7071677</v>
+        <v>7071732</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3993,13 +3993,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261209</t>
+          <t>https://artportalen.se/Sighting/135261208</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135261211</v>
+        <v>135261209</v>
       </c>
       <c r="B32" t="n">
         <v>79441</v>
@@ -4034,10 +4034,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>597775</v>
+        <v>597692</v>
       </c>
       <c r="R32" t="n">
-        <v>7071632</v>
+        <v>7071677</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4105,13 +4105,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261211</t>
+          <t>https://artportalen.se/Sighting/135261209</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135261212</v>
+        <v>135261211</v>
       </c>
       <c r="B33" t="n">
         <v>79441</v>
@@ -4146,10 +4146,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>597811</v>
+        <v>597775</v>
       </c>
       <c r="R33" t="n">
-        <v>7071636</v>
+        <v>7071632</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4217,13 +4217,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261212</t>
+          <t>https://artportalen.se/Sighting/135261211</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135277134</v>
+        <v>135261212</v>
       </c>
       <c r="B34" t="n">
         <v>79441</v>
@@ -4254,17 +4254,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>597690</v>
+        <v>597811</v>
       </c>
       <c r="R34" t="n">
-        <v>7071889</v>
+        <v>7071636</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4318,65 +4318,68 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277134</t>
+          <t>https://artportalen.se/Sighting/135261212</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135277128</v>
+        <v>135261476</v>
       </c>
       <c r="B35" t="n">
-        <v>79465</v>
+        <v>79441</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>597652</v>
+        <v>597705</v>
       </c>
       <c r="R35" t="n">
-        <v>7072022</v>
+        <v>7071935</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4405,7 +4408,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4415,7 +4418,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4424,71 +4427,90 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277128</t>
+          <t>https://artportalen.se/Sighting/135261476</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135185455</v>
+        <v>135261480</v>
       </c>
       <c r="B36" t="n">
-        <v>78844</v>
+        <v>79441</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>597723</v>
+        <v>597757</v>
       </c>
       <c r="R36" t="n">
-        <v>7071638</v>
+        <v>7071733</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4512,12 +4534,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4526,71 +4558,87 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135185455</t>
+          <t>https://artportalen.se/Sighting/135261480</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135253692</v>
+        <v>135277134</v>
       </c>
       <c r="B37" t="n">
-        <v>83428</v>
+        <v>79441</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>597718</v>
+        <v>597690</v>
       </c>
       <c r="R37" t="n">
-        <v>7071826</v>
+        <v>7071889</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4617,9 +4665,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4634,49 +4692,49 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253692</t>
+          <t>https://artportalen.se/Sighting/135277134</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135277130</v>
+        <v>135277128</v>
       </c>
       <c r="B38" t="n">
-        <v>83428</v>
+        <v>79465</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6434</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4686,10 +4744,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>597672</v>
+        <v>597652</v>
       </c>
       <c r="R38" t="n">
-        <v>7072025</v>
+        <v>7072022</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4721,7 +4779,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4731,7 +4789,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4757,16 +4815,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277130</t>
+          <t>https://artportalen.se/Sighting/135277128</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135277135</v>
+        <v>135185455</v>
       </c>
       <c r="B39" t="n">
-        <v>83428</v>
+        <v>78844</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4774,37 +4832,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>597696</v>
+        <v>597723</v>
       </c>
       <c r="R39" t="n">
-        <v>7071877</v>
+        <v>7071638</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4828,22 +4886,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>16:33</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>16:33</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4858,27 +4906,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277135</t>
+          <t>https://artportalen.se/Sighting/135185455</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>111802223</v>
+        <v>135253692</v>
       </c>
       <c r="B40" t="n">
-        <v>79084</v>
+        <v>83428</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4886,40 +4934,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>597726</v>
+        <v>597718</v>
       </c>
       <c r="R40" t="n">
-        <v>7071643</v>
+        <v>7071826</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4943,12 +4988,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4957,34 +5002,33 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111802223</t>
+          <t>https://artportalen.se/Sighting/135253692</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135257132</v>
+        <v>135277130</v>
       </c>
       <c r="B41" t="n">
-        <v>79198</v>
+        <v>83428</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4992,37 +5036,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>597810</v>
+        <v>597672</v>
       </c>
       <c r="R41" t="n">
-        <v>7071731</v>
+        <v>7072025</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5049,9 +5093,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5066,27 +5120,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135257132</t>
+          <t>https://artportalen.se/Sighting/135277130</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135257174</v>
+        <v>135277135</v>
       </c>
       <c r="B42" t="n">
-        <v>79198</v>
+        <v>83428</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5094,37 +5148,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>597800</v>
+        <v>597696</v>
       </c>
       <c r="R42" t="n">
-        <v>7071779</v>
+        <v>7071877</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5151,9 +5205,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5168,27 +5232,27 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135257174</t>
+          <t>https://artportalen.se/Sighting/135277135</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135185445</v>
+        <v>111802223</v>
       </c>
       <c r="B43" t="n">
-        <v>80060</v>
+        <v>79084</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5196,37 +5260,40 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Kullberg, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>597724</v>
+        <v>597726</v>
       </c>
       <c r="R43" t="n">
-        <v>7071639</v>
+        <v>7071643</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5250,12 +5317,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5264,71 +5331,72 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135185445</t>
+          <t>https://artportalen.se/Sighting/111802223</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135261207</v>
+        <v>135257132</v>
       </c>
       <c r="B44" t="n">
-        <v>80560</v>
+        <v>79198</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>597651</v>
+        <v>597810</v>
       </c>
       <c r="R44" t="n">
-        <v>7071773</v>
+        <v>7071731</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5355,19 +5423,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>17:01</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>17:01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5382,67 +5440,62 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261207</t>
+          <t>https://artportalen.se/Sighting/135257132</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135253925</v>
+        <v>135257174</v>
       </c>
       <c r="B45" t="n">
-        <v>57977</v>
+        <v>79198</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>597717</v>
+        <v>597800</v>
       </c>
       <c r="R45" t="n">
-        <v>7071813</v>
+        <v>7071779</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5500,16 +5553,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253925</t>
+          <t>https://artportalen.se/Sighting/135257174</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119352061</v>
+        <v>135261478</v>
       </c>
       <c r="B46" t="n">
-        <v>57953</v>
+        <v>79198</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5517,42 +5570,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>597652</v>
+        <v>597690</v>
       </c>
       <c r="R46" t="n">
-        <v>7071974</v>
+        <v>7071824</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5576,22 +5624,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5606,27 +5654,27 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119352061</t>
+          <t>https://artportalen.se/Sighting/135261478</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135185510</v>
+        <v>135185445</v>
       </c>
       <c r="B47" t="n">
-        <v>57980</v>
+        <v>80060</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5634,39 +5682,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>597653</v>
+        <v>597724</v>
       </c>
       <c r="R47" t="n">
-        <v>7071687</v>
+        <v>7071639</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5701,11 +5744,6 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5729,59 +5767,54 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135185510</t>
+          <t>https://artportalen.se/Sighting/135185445</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135185592</v>
+        <v>135261207</v>
       </c>
       <c r="B48" t="n">
-        <v>57980</v>
+        <v>80560</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>597662</v>
+        <v>597651</v>
       </c>
       <c r="R48" t="n">
-        <v>7071777</v>
+        <v>7071773</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5805,17 +5838,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5830,44 +5868,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135185592</t>
+          <t>https://artportalen.se/Sighting/135261207</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135252357</v>
+        <v>135253925</v>
       </c>
       <c r="B49" t="n">
-        <v>57980</v>
+        <v>57977</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5878,7 +5916,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5887,13 +5925,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>597647</v>
+        <v>597717</v>
       </c>
       <c r="R49" t="n">
-        <v>7072042</v>
+        <v>7071813</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5920,24 +5958,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5952,27 +5975,27 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252357</t>
+          <t>https://artportalen.se/Sighting/135253925</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135252502</v>
+        <v>119352061</v>
       </c>
       <c r="B50" t="n">
-        <v>57980</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6009,10 +6032,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>597650</v>
+        <v>597652</v>
       </c>
       <c r="R50" t="n">
-        <v>7071996</v>
+        <v>7071974</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6039,27 +6062,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6085,13 +6103,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252502</t>
+          <t>https://artportalen.se/Sighting/119352061</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135252549</v>
+        <v>135185510</v>
       </c>
       <c r="B51" t="n">
         <v>57980</v>
@@ -6122,7 +6140,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6131,13 +6149,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>597648</v>
+        <v>597653</v>
       </c>
       <c r="R51" t="n">
-        <v>7071988</v>
+        <v>7071687</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6161,27 +6179,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6196,24 +6204,24 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252549</t>
+          <t>https://artportalen.se/Sighting/135185510</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135252575</v>
+        <v>135185592</v>
       </c>
       <c r="B52" t="n">
         <v>57980</v>
@@ -6253,13 +6261,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>597654</v>
+        <v>597662</v>
       </c>
       <c r="R52" t="n">
-        <v>7071984</v>
+        <v>7071777</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6283,27 +6291,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:41</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:41</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6318,24 +6316,24 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252575</t>
+          <t>https://artportalen.se/Sighting/135185592</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135252599</v>
+        <v>135252357</v>
       </c>
       <c r="B53" t="n">
         <v>57980</v>
@@ -6366,7 +6364,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6375,10 +6373,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>597652</v>
+        <v>597647</v>
       </c>
       <c r="R53" t="n">
-        <v>7071981</v>
+        <v>7072042</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6410,7 +6408,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6420,12 +6418,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6440,24 +6438,24 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252599</t>
+          <t>https://artportalen.se/Sighting/135252357</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135252771</v>
+        <v>135252502</v>
       </c>
       <c r="B54" t="n">
         <v>57980</v>
@@ -6497,10 +6495,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>597694</v>
+        <v>597650</v>
       </c>
       <c r="R54" t="n">
-        <v>7071960</v>
+        <v>7071996</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6532,7 +6530,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6542,7 +6540,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -6573,13 +6571,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252771</t>
+          <t>https://artportalen.se/Sighting/135252502</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135253769</v>
+        <v>135252549</v>
       </c>
       <c r="B55" t="n">
         <v>57980</v>
@@ -6619,10 +6617,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>597732</v>
+        <v>597648</v>
       </c>
       <c r="R55" t="n">
-        <v>7071814</v>
+        <v>7071988</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6654,7 +6652,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6664,7 +6662,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -6684,60 +6682,55 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253769</t>
+          <t>https://artportalen.se/Sighting/135252549</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135254862</v>
+        <v>135252575</v>
       </c>
       <c r="B56" t="n">
-        <v>57167</v>
+        <v>57980</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6746,13 +6739,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>597826</v>
+        <v>597654</v>
       </c>
       <c r="R56" t="n">
-        <v>7071713</v>
+        <v>7071984</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6779,9 +6772,24 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6796,62 +6804,67 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254862</t>
+          <t>https://artportalen.se/Sighting/135252575</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135277138</v>
+        <v>135252599</v>
       </c>
       <c r="B57" t="n">
-        <v>57167</v>
+        <v>57980</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>597826</v>
+        <v>597652</v>
       </c>
       <c r="R57" t="n">
-        <v>7071709</v>
+        <v>7071981</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6883,7 +6896,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6893,7 +6906,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6908,27 +6926,27 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277138</t>
+          <t>https://artportalen.se/Sighting/135252599</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135185420</v>
+        <v>135252771</v>
       </c>
       <c r="B58" t="n">
-        <v>58141</v>
+        <v>57980</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6936,27 +6954,27 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6965,13 +6983,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>597731</v>
+        <v>597694</v>
       </c>
       <c r="R58" t="n">
-        <v>7071656</v>
+        <v>7071960</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6995,12 +7013,27 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7015,27 +7048,27 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135185420</t>
+          <t>https://artportalen.se/Sighting/135252771</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135257192</v>
+        <v>135253769</v>
       </c>
       <c r="B59" t="n">
-        <v>58141</v>
+        <v>57980</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7043,27 +7076,27 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7072,13 +7105,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>597798</v>
+        <v>597732</v>
       </c>
       <c r="R59" t="n">
-        <v>7071782</v>
+        <v>7071814</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7105,9 +7138,24 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7122,27 +7170,27 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135257192</t>
+          <t>https://artportalen.se/Sighting/135253769</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135277129</v>
+        <v>135254862</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>57167</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7150,37 +7198,47 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>597655</v>
+        <v>597826</v>
       </c>
       <c r="R60" t="n">
-        <v>7072023</v>
+        <v>7071713</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7207,19 +7265,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>15:32</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7234,27 +7282,27 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277129</t>
+          <t>https://artportalen.se/Sighting/135254862</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135252291</v>
+        <v>135277138</v>
       </c>
       <c r="B61" t="n">
-        <v>99193</v>
+        <v>57167</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7262,37 +7310,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>597625</v>
+        <v>597826</v>
       </c>
       <c r="R61" t="n">
-        <v>7072015</v>
+        <v>7071709</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7319,9 +7367,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7336,62 +7394,67 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252291</t>
+          <t>https://artportalen.se/Sighting/135277138</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135253119</v>
+        <v>135185420</v>
       </c>
       <c r="B62" t="n">
-        <v>98138</v>
+        <v>58141</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>597685</v>
+        <v>597731</v>
       </c>
       <c r="R62" t="n">
-        <v>7071950</v>
+        <v>7071656</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7418,12 +7481,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7449,54 +7512,59 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253119</t>
+          <t>https://artportalen.se/Sighting/135185420</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135261205</v>
+        <v>135257192</v>
       </c>
       <c r="B63" t="n">
-        <v>98138</v>
+        <v>58141</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>597679</v>
+        <v>597798</v>
       </c>
       <c r="R63" t="n">
-        <v>7071921</v>
+        <v>7071782</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7523,19 +7591,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>16:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7550,62 +7608,62 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261205</t>
+          <t>https://artportalen.se/Sighting/135257192</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135254080</v>
+        <v>135277129</v>
       </c>
       <c r="B64" t="n">
-        <v>79199</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>106554</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>597664</v>
+        <v>597655</v>
       </c>
       <c r="R64" t="n">
-        <v>7071792</v>
+        <v>7072023</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7637,7 +7695,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7647,7 +7705,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7662,49 +7720,49 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254080</t>
+          <t>https://artportalen.se/Sighting/135277129</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135254180</v>
+        <v>135252291</v>
       </c>
       <c r="B65" t="n">
-        <v>79199</v>
+        <v>99193</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7714,13 +7772,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>597732</v>
+        <v>597625</v>
       </c>
       <c r="R65" t="n">
-        <v>7071814</v>
+        <v>7072015</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7747,19 +7805,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>16:55</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7774,49 +7822,49 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254180</t>
+          <t>https://artportalen.se/Sighting/135252291</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135254875</v>
+        <v>135253119</v>
       </c>
       <c r="B66" t="n">
-        <v>79199</v>
+        <v>98138</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7826,13 +7874,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>597688</v>
+        <v>597685</v>
       </c>
       <c r="R66" t="n">
-        <v>7071656</v>
+        <v>7071950</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7859,19 +7907,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>17:35</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7886,65 +7924,65 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254875</t>
+          <t>https://artportalen.se/Sighting/135253119</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135255066</v>
+        <v>135261205</v>
       </c>
       <c r="B67" t="n">
-        <v>79199</v>
+        <v>98138</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>597711</v>
+        <v>597679</v>
       </c>
       <c r="R67" t="n">
-        <v>7071632</v>
+        <v>7071921</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7973,7 +8011,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7983,7 +8021,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7998,65 +8036,65 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255066</t>
+          <t>https://artportalen.se/Sighting/135261205</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135255116</v>
+        <v>135261477</v>
       </c>
       <c r="B68" t="n">
-        <v>79199</v>
+        <v>98138</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>597691</v>
+        <v>597690</v>
       </c>
       <c r="R68" t="n">
-        <v>7071625</v>
+        <v>7071861</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8085,7 +8123,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8095,7 +8133,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8110,24 +8148,24 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255116</t>
+          <t>https://artportalen.se/Sighting/135261477</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135255849</v>
+        <v>135254080</v>
       </c>
       <c r="B69" t="n">
         <v>79199</v>
@@ -8162,10 +8200,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>597894</v>
+        <v>597664</v>
       </c>
       <c r="R69" t="n">
-        <v>7071564</v>
+        <v>7071792</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8197,7 +8235,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8207,7 +8245,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8233,13 +8271,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255849</t>
+          <t>https://artportalen.se/Sighting/135254080</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135255990</v>
+        <v>135254180</v>
       </c>
       <c r="B70" t="n">
         <v>79199</v>
@@ -8270,14 +8308,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>597890</v>
+        <v>597732</v>
       </c>
       <c r="R70" t="n">
-        <v>7071513</v>
+        <v>7071814</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8309,7 +8347,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8319,7 +8357,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8334,24 +8372,24 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255990</t>
+          <t>https://artportalen.se/Sighting/135254180</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135256152</v>
+        <v>135254875</v>
       </c>
       <c r="B71" t="n">
         <v>79199</v>
@@ -8386,10 +8424,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>597907</v>
+        <v>597688</v>
       </c>
       <c r="R71" t="n">
-        <v>7071543</v>
+        <v>7071656</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8421,7 +8459,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8431,7 +8469,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8446,27 +8484,27 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135256152</t>
+          <t>https://artportalen.se/Sighting/135254875</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135277126</v>
+        <v>135255066</v>
       </c>
       <c r="B72" t="n">
-        <v>80031</v>
+        <v>79199</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8474,34 +8512,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>597628</v>
+        <v>597711</v>
       </c>
       <c r="R72" t="n">
-        <v>7072050</v>
+        <v>7071632</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8533,7 +8571,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8543,7 +8581,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8558,16 +8596,688 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255066</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135255116</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>597691</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7071625</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255116</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135255849</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>597894</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7071564</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255849</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135255990</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>597890</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7071513</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255990</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135256152</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>597907</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7071543</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135256152</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135261479</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>597679</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7071753</v>
+      </c>
+      <c r="S77" t="n">
+        <v>3</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261479</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135277126</v>
+      </c>
+      <c r="B78" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>597628</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7072050</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135277126</t>
         </is>
@@ -8646,6 +9356,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
